--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -974,7 +974,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1859,11 +1859,13 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>12200000000</v>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1874,7 +1876,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1886,11 +1888,13 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>830000000</v>
+      </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -1901,7 +1905,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -1913,11 +1917,13 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>610000000</v>
+      </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AH11" t="n">
@@ -2240,7 +2246,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2269,7 +2275,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -2298,7 +2304,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -2373,7 +2379,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2402,7 +2408,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -2431,7 +2437,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -2772,7 +2778,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2801,7 +2807,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2830,7 +2836,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2905,7 +2911,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2934,7 +2940,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2963,7 +2969,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3038,7 +3044,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -3067,7 +3073,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -3096,7 +3102,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -3171,7 +3177,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3200,7 +3206,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -3229,7 +3235,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -3304,7 +3310,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -3566,7 +3572,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -3595,7 +3601,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -3624,7 +3630,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB24" t="n">
@@ -3832,7 +3838,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -3861,7 +3867,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3890,7 +3896,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -3965,7 +3971,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -3994,7 +4000,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -4023,7 +4029,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB27" t="n">
@@ -4098,7 +4104,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -4125,7 +4131,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -4152,7 +4158,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB28" t="n">
@@ -4225,7 +4231,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -4254,7 +4260,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -4283,7 +4289,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB29" t="n">
@@ -4381,7 +4387,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -4410,7 +4416,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB30" t="n">
@@ -4485,7 +4491,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -4514,7 +4520,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -4543,7 +4549,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -4995,7 +5001,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -5024,7 +5030,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -5053,7 +5059,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5128,7 +5134,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -5157,7 +5163,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -5186,7 +5192,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -5384,7 +5390,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -5413,7 +5419,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -5442,7 +5448,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -5517,7 +5523,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -5544,7 +5550,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -5571,7 +5577,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -5644,7 +5650,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -5906,7 +5912,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -5935,7 +5941,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -5964,7 +5970,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6039,7 +6045,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -6066,7 +6072,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -6093,7 +6099,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -6432,7 +6438,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -6461,7 +6467,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -6490,7 +6496,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -6565,7 +6571,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -6594,7 +6600,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -6623,7 +6629,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -6698,7 +6704,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -6727,7 +6733,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -6756,7 +6762,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -6831,7 +6837,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -6860,7 +6866,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -6889,7 +6895,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -6964,7 +6970,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -6993,7 +6999,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -7022,7 +7028,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -7093,7 +7099,7 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -7118,7 +7124,7 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -7143,7 +7149,7 @@
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -8107,7 +8113,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -8136,7 +8142,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -8165,7 +8171,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB59" t="n">
@@ -8506,7 +8512,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -8535,7 +8541,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -8564,7 +8570,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB62" t="n">
@@ -8905,7 +8911,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -8934,7 +8940,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -8963,7 +8969,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB65" t="n">
@@ -9554,7 +9560,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -9583,7 +9589,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -9612,7 +9618,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB70" t="n">
@@ -10422,7 +10428,7 @@
         <v>131573900</v>
       </c>
       <c r="AL76" t="n">
-        <v>131414750</v>
+        <v>131879450</v>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
@@ -10588,7 +10594,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -10617,7 +10623,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -10646,7 +10652,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB78" t="n">
@@ -10721,7 +10727,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -10750,7 +10756,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -10779,7 +10785,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB79" t="n">
@@ -10854,7 +10860,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -10883,7 +10889,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -10912,7 +10918,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB80" t="n">
@@ -10985,7 +10991,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -11014,7 +11020,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -11043,7 +11049,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB81" t="n">
@@ -11118,7 +11124,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -11147,7 +11153,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -11176,7 +11182,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB82" t="n">
@@ -11634,7 +11640,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -11663,7 +11669,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -11692,7 +11698,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB86" t="n">
@@ -11994,7 +12000,7 @@
         <v>1853500</v>
       </c>
       <c r="AL88" t="n">
-        <v>1847500</v>
+        <v>1853500</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
@@ -12033,7 +12039,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -12062,7 +12068,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S89" t="n">
@@ -12091,7 +12097,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB89" t="n">
@@ -12510,7 +12516,7 @@
         <v>1452825</v>
       </c>
       <c r="AL92" t="n">
-        <v>1452825</v>
+        <v>2905650</v>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
@@ -14167,7 +14173,7 @@
         <v>1359600</v>
       </c>
       <c r="AL105" t="n">
-        <v>1359000</v>
+        <v>2718000</v>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
@@ -15948,7 +15954,7 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -15973,7 +15979,7 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S120" t="n">
@@ -15998,7 +16004,7 @@
       <c r="Z120" t="inlineStr"/>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB120" t="n">
@@ -16069,7 +16075,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -16094,7 +16100,7 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S121" t="n">
@@ -16119,7 +16125,7 @@
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB121" t="n">
@@ -16436,7 +16442,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -16465,7 +16471,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S124" t="n">
@@ -16494,7 +16500,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB124" t="n">
@@ -17407,7 +17413,7 @@
         <v>5529204</v>
       </c>
       <c r="AL131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
@@ -17446,7 +17452,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -17475,7 +17481,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S132" t="n">
@@ -17504,7 +17510,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB132" t="n">
@@ -18026,7 +18032,7 @@
         <v>41894177</v>
       </c>
       <c r="AL136" t="n">
-        <v>40717160</v>
+        <v>203585800</v>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
@@ -18329,7 +18335,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -18358,7 +18364,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S139" t="n">
@@ -18387,7 +18393,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB139" t="n">
@@ -18462,7 +18468,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -18491,7 +18497,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S140" t="n">
@@ -18520,7 +18526,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB140" t="n">
@@ -18849,7 +18855,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -18878,7 +18884,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S143" t="n">
@@ -18907,7 +18913,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB143" t="n">
@@ -18982,7 +18988,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -19011,7 +19017,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S144" t="n">
@@ -19040,7 +19046,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB144" t="n">
@@ -19494,7 +19500,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -19523,7 +19529,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S148" t="n">
@@ -19552,7 +19558,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB148" t="n">
@@ -19627,7 +19633,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -19639,11 +19645,13 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" t="n">
+        <v>11413000000</v>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -19654,7 +19662,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S149" t="n">
@@ -19666,11 +19674,13 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr"/>
+      <c r="V149" t="n">
+        <v>739000000</v>
+      </c>
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="Y149" t="n">
@@ -19681,7 +19691,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB149" t="n">
@@ -19693,11 +19703,13 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AE149" t="inlineStr"/>
+      <c r="AE149" t="n">
+        <v>552000000</v>
+      </c>
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AH149" t="n">
@@ -20631,7 +20643,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -20660,7 +20672,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S157" t="n">
@@ -20689,7 +20701,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB157" t="n">
@@ -21012,7 +21024,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -21041,7 +21053,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S160" t="n">
@@ -21070,7 +21082,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB160" t="n">
@@ -21145,7 +21157,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -21174,7 +21186,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S161" t="n">
@@ -21203,7 +21215,7 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB161" t="n">
@@ -21411,7 +21423,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -21440,7 +21452,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S163" t="n">
@@ -21469,7 +21481,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB163" t="n">
@@ -21774,7 +21786,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -21801,7 +21813,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="S166" t="n">
@@ -21828,7 +21840,7 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AB166" t="n">
@@ -21903,7 +21915,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -21932,7 +21944,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S167" t="n">
@@ -21961,7 +21973,7 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB167" t="n">
@@ -22268,7 +22280,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -22295,7 +22307,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="S170" t="n">
@@ -22322,7 +22334,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AB170" t="n">
@@ -24093,7 +24105,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -24122,7 +24134,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S185" t="n">
@@ -24151,7 +24163,7 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB185" t="n">
@@ -24609,7 +24621,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -24638,7 +24650,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S189" t="n">
@@ -24667,7 +24679,7 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB189" t="n">
@@ -24871,7 +24883,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -24900,7 +24912,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S191" t="n">
@@ -24929,7 +24941,7 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB191" t="n">
@@ -25246,7 +25258,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -25275,7 +25287,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S194" t="n">
@@ -25304,7 +25316,7 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB194" t="n">
@@ -25379,7 +25391,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -25408,7 +25420,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S195" t="n">
@@ -25437,7 +25449,7 @@
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB195" t="n">
@@ -25778,7 +25790,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J198" t="n">
@@ -25807,7 +25819,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S198" t="n">
@@ -25836,7 +25848,7 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB198" t="n">
@@ -26042,7 +26054,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -26069,7 +26081,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S200" t="n">
@@ -26096,7 +26108,7 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB200" t="n">
@@ -26169,7 +26181,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -26198,7 +26210,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S201" t="n">
@@ -26227,7 +26239,7 @@
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB201" t="n">
@@ -26562,7 +26574,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -26591,7 +26603,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S204" t="n">
@@ -26620,7 +26632,7 @@
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB204" t="n">
@@ -26656,7 +26668,7 @@
         <v>48366400</v>
       </c>
       <c r="AL204" t="n">
-        <v>45476535</v>
+        <v>44776025</v>
       </c>
       <c r="AM204" t="inlineStr">
         <is>
@@ -26828,7 +26840,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -26857,7 +26869,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S206" t="n">
@@ -26886,7 +26898,7 @@
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB206" t="n">
@@ -26961,7 +26973,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -26990,7 +27002,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S207" t="n">
@@ -27019,7 +27031,7 @@
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB207" t="n">
@@ -27354,7 +27366,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -27381,7 +27393,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S210" t="n">
@@ -27408,7 +27420,7 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB210" t="n">
@@ -27614,7 +27626,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -27643,7 +27655,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S212" t="n">
@@ -27672,7 +27684,7 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB212" t="n">
@@ -27747,7 +27759,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -27776,7 +27788,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S213" t="n">
@@ -27805,7 +27817,7 @@
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB213" t="n">
@@ -27880,7 +27892,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -27909,7 +27921,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S214" t="n">
@@ -27938,7 +27950,7 @@
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB214" t="n">
@@ -28013,7 +28025,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -28042,7 +28054,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S215" t="n">
@@ -28071,7 +28083,7 @@
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB215" t="n">
@@ -28146,7 +28158,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -28175,7 +28187,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S216" t="n">
@@ -28204,7 +28216,7 @@
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB216" t="n">
@@ -28279,7 +28291,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J217" t="n">
@@ -28308,7 +28320,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S217" t="n">
@@ -28337,7 +28349,7 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB217" t="n">
@@ -28811,7 +28823,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J221" t="n">
@@ -28840,7 +28852,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S221" t="n">
@@ -28869,7 +28881,7 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB221" t="n">
@@ -28944,7 +28956,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J222" t="n">
@@ -28973,7 +28985,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S222" t="n">
@@ -29002,7 +29014,7 @@
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB222" t="n">
@@ -29077,7 +29089,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J223" t="n">
@@ -29104,7 +29116,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S223" t="n">
@@ -29131,7 +29143,7 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB223" t="n">
@@ -29204,7 +29216,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J224" t="n">
@@ -29233,7 +29245,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S224" t="n">
@@ -29262,7 +29274,7 @@
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB224" t="n">
@@ -29470,7 +29482,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J226" t="n">
@@ -29499,7 +29511,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S226" t="n">
@@ -29528,7 +29540,7 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB226" t="n">
@@ -29603,7 +29615,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J227" t="n">
@@ -29632,7 +29644,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S227" t="n">
@@ -29661,7 +29673,7 @@
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB227" t="n">
@@ -29736,7 +29748,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J228" t="n">
@@ -29765,7 +29777,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S228" t="n">
@@ -29794,7 +29806,7 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB228" t="n">
@@ -30389,7 +30401,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J233" t="n">
@@ -30418,7 +30430,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S233" t="n">
@@ -30447,7 +30459,7 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB233" t="n">
@@ -30522,7 +30534,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J234" t="n">
@@ -30551,7 +30563,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S234" t="n">
@@ -30580,7 +30592,7 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB234" t="n">
@@ -30655,7 +30667,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J235" t="n">
@@ -30684,7 +30696,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S235" t="n">
@@ -30713,7 +30725,7 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB235" t="n">
@@ -30788,7 +30800,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J236" t="n">
@@ -30817,7 +30829,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S236" t="n">
@@ -30846,7 +30858,7 @@
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB236" t="n">
@@ -30921,7 +30933,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J237" t="n">
@@ -30950,7 +30962,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S237" t="n">
@@ -30979,7 +30991,7 @@
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB237" t="n">
@@ -31054,7 +31066,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J238" t="n">
@@ -31083,7 +31095,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S238" t="n">
@@ -31112,7 +31124,7 @@
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB238" t="n">
@@ -31314,7 +31326,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J240" t="n">
@@ -31343,7 +31355,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S240" t="n">
@@ -31372,7 +31384,7 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB240" t="n">
@@ -31447,7 +31459,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J241" t="n">
@@ -31476,7 +31488,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S241" t="n">
@@ -31505,7 +31517,7 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB241" t="n">
@@ -31713,7 +31725,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J243" t="n">
@@ -31742,7 +31754,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S243" t="n">
@@ -31771,7 +31783,7 @@
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB243" t="n">
@@ -31846,7 +31858,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J244" t="n">
@@ -31875,7 +31887,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S244" t="n">
@@ -31904,7 +31916,7 @@
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB244" t="n">
@@ -31979,7 +31991,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J245" t="n">
@@ -32008,7 +32020,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S245" t="n">
@@ -32037,7 +32049,7 @@
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB245" t="n">
@@ -32112,7 +32124,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J246" t="n">
@@ -32141,7 +32153,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S246" t="n">
@@ -32170,7 +32182,7 @@
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB246" t="n">
@@ -32245,7 +32257,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J247" t="n">
@@ -32274,7 +32286,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S247" t="n">
@@ -32303,7 +32315,7 @@
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB247" t="n">
@@ -32505,7 +32517,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J249" t="n">
@@ -32534,7 +32546,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S249" t="n">
@@ -32563,7 +32575,7 @@
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB249" t="n">
@@ -32638,7 +32650,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -32667,7 +32679,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S250" t="n">
@@ -32696,7 +32708,7 @@
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB250" t="n">
@@ -33303,7 +33315,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J255" t="n">
@@ -33332,7 +33344,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S255" t="n">
@@ -33361,7 +33373,7 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB255" t="n">
@@ -33397,7 +33409,7 @@
         <v>11226000</v>
       </c>
       <c r="AL255" t="n">
-        <v>11222904</v>
+        <v>11116878</v>
       </c>
       <c r="AM255" t="inlineStr">
         <is>
@@ -33569,7 +33581,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J257" t="n">
@@ -33598,7 +33610,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S257" t="n">
@@ -33627,7 +33639,7 @@
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB257" t="n">
@@ -34095,7 +34107,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J261" t="n">
@@ -34124,7 +34136,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S261" t="n">
@@ -34153,7 +34165,7 @@
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB261" t="n">
@@ -34577,7 +34589,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J265" t="n">
@@ -34606,7 +34618,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S265" t="n">
@@ -34635,7 +34647,7 @@
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB265" t="n">
@@ -34671,7 +34683,7 @@
         <v>7926800</v>
       </c>
       <c r="AL265" t="n">
-        <v>7920726</v>
+        <v>15841452</v>
       </c>
       <c r="AM265" t="inlineStr">
         <is>
@@ -35194,7 +35206,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J270" t="n">
@@ -35223,7 +35235,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S270" t="n">
@@ -35252,7 +35264,7 @@
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB270" t="n">
@@ -35327,7 +35339,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J271" t="n">
@@ -35356,7 +35368,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S271" t="n">
@@ -35385,7 +35397,7 @@
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB271" t="n">
@@ -35554,7 +35566,7 @@
         <v>3148100</v>
       </c>
       <c r="AL272" t="n">
-        <v>3040433</v>
+        <v>3136022</v>
       </c>
       <c r="AM272" t="inlineStr">
         <is>
@@ -35726,7 +35738,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J274" t="n">
@@ -35755,7 +35767,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S274" t="n">
@@ -35784,7 +35796,7 @@
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB274" t="n">
@@ -35859,7 +35871,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J275" t="n">
@@ -35888,7 +35900,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S275" t="n">
@@ -35917,7 +35929,7 @@
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB275" t="n">
@@ -36252,7 +36264,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J278" t="n">
@@ -36281,7 +36293,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S278" t="n">
@@ -36310,7 +36322,7 @@
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB278" t="n">
@@ -36784,7 +36796,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J282" t="n">
@@ -36813,7 +36825,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S282" t="n">
@@ -36842,7 +36854,7 @@
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB282" t="n">
@@ -36917,7 +36929,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J283" t="n">
@@ -36946,7 +36958,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S283" t="n">
@@ -36975,7 +36987,7 @@
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB283" t="n">
@@ -37183,7 +37195,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J285" t="n">
@@ -37212,7 +37224,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S285" t="n">
@@ -37241,7 +37253,7 @@
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB285" t="n">
@@ -37316,7 +37328,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J286" t="n">
@@ -37345,7 +37357,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S286" t="n">
@@ -37374,7 +37386,7 @@
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB286" t="n">
@@ -37576,7 +37588,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J288" t="n">
@@ -37605,7 +37617,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S288" t="n">
@@ -37634,7 +37646,7 @@
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB288" t="n">
@@ -37709,7 +37721,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J289" t="n">
@@ -37738,7 +37750,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S289" t="n">
@@ -37767,7 +37779,7 @@
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB289" t="n">
@@ -37842,7 +37854,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J290" t="n">
@@ -37871,7 +37883,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S290" t="n">
@@ -37900,7 +37912,7 @@
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB290" t="n">
@@ -37975,7 +37987,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J291" t="n">
@@ -38004,7 +38016,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S291" t="n">
@@ -38033,7 +38045,7 @@
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB291" t="n">
@@ -38108,7 +38120,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J292" t="n">
@@ -38137,7 +38149,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S292" t="n">
@@ -38166,7 +38178,7 @@
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB292" t="n">
@@ -38374,7 +38386,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J294" t="n">
@@ -38403,7 +38415,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S294" t="n">
@@ -38432,7 +38444,7 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB294" t="n">
@@ -38640,7 +38652,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J296" t="n">
@@ -38669,7 +38681,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S296" t="n">
@@ -38698,7 +38710,7 @@
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB296" t="n">
@@ -38906,7 +38918,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J298" t="n">
@@ -38935,7 +38947,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S298" t="n">
@@ -38964,7 +38976,7 @@
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB298" t="n">
@@ -39039,7 +39051,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J299" t="n">
@@ -39068,7 +39080,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S299" t="n">
@@ -39097,7 +39109,7 @@
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB299" t="n">
@@ -39305,7 +39317,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J301" t="n">
@@ -39334,7 +39346,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S301" t="n">
@@ -39363,7 +39375,7 @@
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB301" t="n">
@@ -39438,7 +39450,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J302" t="n">
@@ -39467,7 +39479,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S302" t="n">
@@ -39496,7 +39508,7 @@
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB302" t="n">
@@ -39571,7 +39583,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J303" t="n">
@@ -39600,7 +39612,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S303" t="n">
@@ -39629,7 +39641,7 @@
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB303" t="n">
@@ -39704,7 +39716,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J304" t="n">
@@ -39733,7 +39745,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S304" t="n">
@@ -39762,7 +39774,7 @@
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB304" t="n">
@@ -39837,7 +39849,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J305" t="n">
@@ -39866,7 +39878,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S305" t="n">
@@ -39895,7 +39907,7 @@
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB305" t="n">
@@ -39970,7 +39982,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J306" t="n">
@@ -39999,7 +40011,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S306" t="n">
@@ -40028,7 +40040,7 @@
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB306" t="n">
@@ -40103,7 +40115,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J307" t="n">
@@ -40132,7 +40144,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S307" t="n">
@@ -40161,7 +40173,7 @@
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB307" t="n">
@@ -40236,7 +40248,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J308" t="n">
@@ -40263,7 +40275,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S308" t="n">
@@ -40290,7 +40302,7 @@
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB308" t="n">
@@ -40363,7 +40375,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J309" t="n">
@@ -40392,7 +40404,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S309" t="n">
@@ -40421,7 +40433,7 @@
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB309" t="n">
@@ -40496,7 +40508,7 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J310" t="n">
@@ -40525,7 +40537,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S310" t="n">
@@ -40554,7 +40566,7 @@
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB310" t="n">
@@ -40629,7 +40641,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J311" t="n">
@@ -40658,7 +40670,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S311" t="n">
@@ -40687,7 +40699,7 @@
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB311" t="n">
@@ -40723,7 +40735,7 @@
         <v>1419740</v>
       </c>
       <c r="AL311" t="n">
-        <v>1412253</v>
+        <v>4236759</v>
       </c>
       <c r="AM311" t="inlineStr">
         <is>
@@ -40762,7 +40774,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J312" t="n">
@@ -40791,7 +40803,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S312" t="n">
@@ -40820,7 +40832,7 @@
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB312" t="n">
@@ -41014,7 +41026,7 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J314" t="n">
@@ -41043,7 +41055,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S314" t="n">
@@ -41072,7 +41084,7 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB314" t="n">
@@ -41147,7 +41159,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J315" t="n">
@@ -41176,7 +41188,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S315" t="n">
@@ -41205,7 +41217,7 @@
       </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB315" t="n">
@@ -41280,7 +41292,7 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J316" t="n">
@@ -41309,7 +41321,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S316" t="n">
@@ -41338,7 +41350,7 @@
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB316" t="n">
@@ -41413,7 +41425,7 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J317" t="n">
@@ -41473,11 +41485,13 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="AE317" t="inlineStr"/>
+      <c r="AE317" t="n">
+        <v>1957000000</v>
+      </c>
       <c r="AF317" t="inlineStr"/>
       <c r="AG317" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AH317" t="n">
@@ -41534,7 +41548,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J318" t="n">
@@ -41563,7 +41577,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S318" t="n">
@@ -41592,7 +41606,7 @@
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB318" t="n">
@@ -41667,7 +41681,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J319" t="n">
@@ -41696,7 +41710,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S319" t="n">
@@ -41725,7 +41739,7 @@
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB319" t="n">
@@ -41800,7 +41814,7 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J320" t="n">
@@ -41829,7 +41843,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S320" t="n">
@@ -41858,7 +41872,7 @@
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB320" t="n">
@@ -41933,7 +41947,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J321" t="n">
@@ -41962,7 +41976,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S321" t="n">
@@ -41991,7 +42005,7 @@
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB321" t="n">
@@ -42193,7 +42207,7 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J323" t="n">
@@ -42222,7 +42236,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S323" t="n">
@@ -42251,7 +42265,7 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB323" t="n">
@@ -42326,7 +42340,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J324" t="n">
@@ -42355,7 +42369,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S324" t="n">
@@ -42384,7 +42398,7 @@
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB324" t="n">
@@ -42713,7 +42727,7 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J327" t="n">
@@ -42742,7 +42756,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S327" t="n">
@@ -42771,7 +42785,7 @@
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB327" t="n">
@@ -43106,7 +43120,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J330" t="n">
@@ -43135,7 +43149,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S330" t="n">
@@ -43164,7 +43178,7 @@
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB330" t="n">
@@ -43239,7 +43253,7 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J331" t="n">
@@ -43251,11 +43265,13 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr"/>
+      <c r="M331" t="n">
+        <v>111000000000</v>
+      </c>
       <c r="N331" t="inlineStr"/>
       <c r="O331" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -43266,7 +43282,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S331" t="n">
@@ -43295,7 +43311,7 @@
       </c>
       <c r="AA331" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB331" t="n">
@@ -43769,7 +43785,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J335" t="n">
@@ -43798,7 +43814,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S335" t="n">
@@ -43827,7 +43843,7 @@
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB335" t="n">
@@ -43902,7 +43918,7 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J336" t="n">
@@ -43931,7 +43947,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S336" t="n">
@@ -43960,7 +43976,7 @@
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB336" t="n">
@@ -44162,7 +44178,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J338" t="n">
@@ -44191,7 +44207,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S338" t="n">
@@ -44220,7 +44236,7 @@
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB338" t="n">
@@ -44295,7 +44311,7 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J339" t="n">
@@ -44324,7 +44340,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S339" t="n">
@@ -44353,7 +44369,7 @@
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB339" t="n">
@@ -44428,7 +44444,7 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J340" t="n">
@@ -44457,7 +44473,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S340" t="n">
@@ -44486,7 +44502,7 @@
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB340" t="n">
@@ -44561,7 +44577,7 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J341" t="n">
@@ -44590,7 +44606,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S341" t="n">
@@ -44619,7 +44635,7 @@
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB341" t="n">
@@ -44694,7 +44710,7 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J342" t="n">
@@ -44723,7 +44739,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S342" t="n">
@@ -44752,7 +44768,7 @@
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB342" t="n">
@@ -44960,7 +44976,7 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J344" t="n">
@@ -44989,7 +45005,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S344" t="n">
@@ -45018,7 +45034,7 @@
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB344" t="n">
@@ -45093,7 +45109,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J345" t="n">
@@ -45122,7 +45138,7 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S345" t="n">
@@ -45151,7 +45167,7 @@
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB345" t="n">
@@ -45226,7 +45242,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J346" t="n">
@@ -45255,7 +45271,7 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S346" t="n">
@@ -45284,7 +45300,7 @@
       </c>
       <c r="AA346" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB346" t="n">
@@ -45359,7 +45375,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J347" t="n">
@@ -45388,7 +45404,7 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S347" t="n">
@@ -45417,7 +45433,7 @@
       </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB347" t="n">
@@ -45492,7 +45508,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J348" t="n">
@@ -45521,7 +45537,7 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S348" t="n">
@@ -45550,7 +45566,7 @@
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB348" t="n">
@@ -45625,7 +45641,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J349" t="n">
@@ -45654,7 +45670,7 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S349" t="n">
@@ -45683,7 +45699,7 @@
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB349" t="n">
@@ -45758,7 +45774,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J350" t="n">
@@ -45787,7 +45803,7 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S350" t="n">
@@ -45816,7 +45832,7 @@
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB350" t="n">
@@ -46024,7 +46040,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J352" t="n">
@@ -46053,7 +46069,7 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S352" t="n">
@@ -46082,7 +46098,7 @@
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB352" t="n">
@@ -46157,7 +46173,7 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J353" t="n">
@@ -46186,7 +46202,7 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S353" t="n">
@@ -46215,7 +46231,7 @@
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB353" t="n">
@@ -46290,7 +46306,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J354" t="n">
@@ -46319,7 +46335,7 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S354" t="n">
@@ -46348,7 +46364,7 @@
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB354" t="n">
@@ -46423,7 +46439,7 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J355" t="n">
@@ -46452,7 +46468,7 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S355" t="n">
@@ -46481,7 +46497,7 @@
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB355" t="n">
@@ -46556,7 +46572,7 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J356" t="n">
@@ -46585,7 +46601,7 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S356" t="n">
@@ -46614,7 +46630,7 @@
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB356" t="n">
@@ -46689,7 +46705,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J357" t="n">
@@ -46718,7 +46734,7 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S357" t="n">
@@ -46747,7 +46763,7 @@
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB357" t="n">
@@ -46822,7 +46838,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J358" t="n">
@@ -46851,7 +46867,7 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S358" t="n">
@@ -46880,7 +46896,7 @@
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB358" t="n">
@@ -46955,7 +46971,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J359" t="n">
@@ -46984,7 +47000,7 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S359" t="n">
@@ -47013,7 +47029,7 @@
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB359" t="n">
@@ -47348,7 +47364,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J362" t="n">
@@ -47377,7 +47393,7 @@
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S362" t="n">
@@ -47406,7 +47422,7 @@
       </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB362" t="n">
@@ -47481,7 +47497,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J363" t="n">
@@ -47510,7 +47526,7 @@
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S363" t="n">
@@ -47539,7 +47555,7 @@
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB363" t="n">
@@ -47747,7 +47763,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J365" t="n">
@@ -47776,7 +47792,7 @@
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S365" t="n">
@@ -47805,7 +47821,7 @@
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB365" t="n">
@@ -48013,7 +48029,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J367" t="n">
@@ -48042,7 +48058,7 @@
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S367" t="n">
@@ -48071,7 +48087,7 @@
       </c>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB367" t="n">
@@ -48146,7 +48162,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J368" t="n">
@@ -48175,7 +48191,7 @@
       </c>
       <c r="R368" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S368" t="n">
@@ -48204,7 +48220,7 @@
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB368" t="n">
@@ -48279,7 +48295,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J369" t="n">
@@ -48308,7 +48324,7 @@
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S369" t="n">
@@ -48337,7 +48353,7 @@
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB369" t="n">
@@ -48412,7 +48428,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J370" t="n">
@@ -48441,7 +48457,7 @@
       </c>
       <c r="R370" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S370" t="n">
@@ -48470,7 +48486,7 @@
       </c>
       <c r="AA370" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB370" t="n">
@@ -48545,7 +48561,7 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J371" t="n">
@@ -48574,7 +48590,7 @@
       </c>
       <c r="R371" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S371" t="n">
@@ -48603,7 +48619,7 @@
       </c>
       <c r="AA371" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB371" t="n">
@@ -48678,7 +48694,7 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J372" t="n">
@@ -48707,7 +48723,7 @@
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S372" t="n">
@@ -48736,7 +48752,7 @@
       </c>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB372" t="n">
@@ -48938,7 +48954,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J374" t="n">
@@ -48967,7 +48983,7 @@
       </c>
       <c r="R374" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S374" t="n">
@@ -48996,7 +49012,7 @@
       </c>
       <c r="AA374" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB374" t="n">
@@ -49071,7 +49087,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J375" t="n">
@@ -49100,7 +49116,7 @@
       </c>
       <c r="R375" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S375" t="n">
@@ -49129,7 +49145,7 @@
       </c>
       <c r="AA375" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB375" t="n">
@@ -49204,7 +49220,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J376" t="n">
@@ -49233,7 +49249,7 @@
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S376" t="n">
@@ -49262,7 +49278,7 @@
       </c>
       <c r="AA376" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB376" t="n">
@@ -49603,7 +49619,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J379" t="n">
@@ -49632,7 +49648,7 @@
       </c>
       <c r="R379" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S379" t="n">
@@ -49661,7 +49677,7 @@
       </c>
       <c r="AA379" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB379" t="n">
@@ -49736,7 +49752,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J380" t="n">
@@ -49765,7 +49781,7 @@
       </c>
       <c r="R380" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S380" t="n">
@@ -49794,7 +49810,7 @@
       </c>
       <c r="AA380" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB380" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -652,11 +652,11 @@
         <v>235018000</v>
       </c>
       <c r="H2" t="n">
-        <v>194643000</v>
+        <v>91140000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -679,11 +679,11 @@
         <v>-212000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-212850000</v>
+        <v>-396748000</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -708,11 +708,11 @@
         <v>-236000000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-236442000</v>
+        <v>-425671000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -737,7 +737,7 @@
         <v>0.946</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9824758843873473</v>
+        <v>0.9463974976020101</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -1577,11 +1577,11 @@
         <v>1594000000</v>
       </c>
       <c r="H9" t="n">
-        <v>1594038000</v>
+        <v>2132680000</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1606,11 +1606,11 @@
         <v>47000000</v>
       </c>
       <c r="Q9" t="n">
-        <v>77143000</v>
+        <v>169142000</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1635,11 +1635,11 @@
         <v>13000000</v>
       </c>
       <c r="Z9" t="n">
-        <v>42941000</v>
+        <v>138852000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -1664,7 +1664,7 @@
         <v>0.539</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.6309998209297989</v>
+        <v>0.5393850710997311</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1710,11 +1710,11 @@
         <v>20981000000</v>
       </c>
       <c r="H10" t="n">
-        <v>20981000000</v>
+        <v>37084000000</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1739,11 +1739,11 @@
         <v>3892000000</v>
       </c>
       <c r="Q10" t="n">
-        <v>3893000000</v>
+        <v>6029000000</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1768,11 +1768,11 @@
         <v>2238000000</v>
       </c>
       <c r="Z10" t="n">
-        <v>2238000000</v>
+        <v>3464000000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -1797,7 +1797,7 @@
         <v>0.261</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.2318437895220941</v>
+        <v>0.2605080969541098</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2374,9 +2374,7 @@
       <c r="G15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="H15" t="n">
-        <v>13781848000</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2403,9 +2401,7 @@
       <c r="P15" t="n">
         <v>542000000</v>
       </c>
-      <c r="Q15" t="n">
-        <v>755967000</v>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2432,9 +2428,7 @@
       <c r="Y15" t="n">
         <v>320000000</v>
       </c>
-      <c r="Z15" t="n">
-        <v>454620000</v>
-      </c>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2462,7 +2456,7 @@
         <v>0.512</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2641,11 +2635,11 @@
         <v>5847000000</v>
       </c>
       <c r="H17" t="n">
-        <v>5847966000</v>
+        <v>8019568000</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -2670,11 +2664,11 @@
         <v>413000000</v>
       </c>
       <c r="Q17" t="n">
-        <v>413119000</v>
+        <v>553165000</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2699,11 +2693,11 @@
         <v>273000000</v>
       </c>
       <c r="Z17" t="n">
-        <v>273173000</v>
+        <v>304310000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2728,7 +2722,7 @@
         <v>0.427</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.6224297830439212</v>
+        <v>0.4271421292686969</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2906,9 +2900,7 @@
       <c r="G19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="H19" t="n">
-        <v>2006859000</v>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2935,9 +2927,7 @@
       <c r="P19" t="n">
         <v>231000000</v>
       </c>
-      <c r="Q19" t="n">
-        <v>123675000</v>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2964,9 +2954,7 @@
       <c r="Y19" t="n">
         <v>156000000</v>
       </c>
-      <c r="Z19" t="n">
-        <v>32652000</v>
-      </c>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2993,12 +2981,10 @@
       <c r="AH19" t="n">
         <v>0.785</v>
       </c>
-      <c r="AI19" t="n">
-        <v>0.785581548809497</v>
-      </c>
+      <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -3701,11 +3687,11 @@
         <v>512000000</v>
       </c>
       <c r="H25" t="n">
-        <v>1085861000</v>
+        <v>805211000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -3730,11 +3716,11 @@
         <v>-227000000</v>
       </c>
       <c r="Q25" t="n">
-        <v>36125000</v>
+        <v>-283087000</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -3759,11 +3745,11 @@
         <v>-223000000</v>
       </c>
       <c r="Z25" t="n">
-        <v>27104000</v>
+        <v>-415606000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -3788,7 +3774,7 @@
         <v>0.007</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.624429691222611</v>
+        <v>0.007279642631564494</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -4991,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>18434000000</v>
@@ -6301,11 +6287,11 @@
         <v>3026500000</v>
       </c>
       <c r="H45" t="n">
-        <v>873610000</v>
+        <v>3026500000</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -6330,11 +6316,11 @@
         <v>726442000</v>
       </c>
       <c r="Q45" t="n">
-        <v>-1038802000</v>
+        <v>272157000</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -6359,11 +6345,11 @@
         <v>592496000</v>
       </c>
       <c r="Z45" t="n">
-        <v>-812725000</v>
+        <v>190608000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -6388,7 +6374,7 @@
         <v>0.9370000000000001</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.9371290993795059</v>
+        <v>0.9373562111007017</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -7347,11 +7333,11 @@
         <v>908000000</v>
       </c>
       <c r="H53" t="n">
-        <v>908174000</v>
+        <v>1157139000</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -7376,11 +7362,11 @@
         <v>169000000</v>
       </c>
       <c r="Q53" t="n">
-        <v>169032000</v>
+        <v>248411000</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -7405,11 +7391,11 @@
         <v>104000000</v>
       </c>
       <c r="Z53" t="n">
-        <v>104916000</v>
+        <v>157967000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -7434,7 +7420,7 @@
         <v>0.84</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.8348863344341269</v>
+        <v>0.8406616004212384</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -7601,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
@@ -8242,11 +8228,11 @@
         <v>23533000000</v>
       </c>
       <c r="H60" t="n">
-        <v>23533494000</v>
+        <v>24413727000</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -8271,11 +8257,11 @@
         <v>2176000000</v>
       </c>
       <c r="Q60" t="n">
-        <v>2176648000</v>
+        <v>2379975000</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -8300,11 +8286,11 @@
         <v>1491000000</v>
       </c>
       <c r="Z60" t="n">
-        <v>1491884000</v>
+        <v>1730727000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB60" t="n">
@@ -8329,7 +8315,7 @@
         <v>0.598</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.6195884627545886</v>
+        <v>0.5977518816535092</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -8375,11 +8361,11 @@
         <v>44845000000</v>
       </c>
       <c r="H61" t="n">
-        <v>44845000000</v>
+        <v>50151000000</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -8404,11 +8390,11 @@
         <v>5012000000</v>
       </c>
       <c r="Q61" t="n">
-        <v>5012000000</v>
+        <v>5991000000</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -8433,11 +8419,11 @@
         <v>3515000000</v>
       </c>
       <c r="Z61" t="n">
-        <v>3515000000</v>
+        <v>4119000000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB61" t="n">
@@ -8462,7 +8448,7 @@
         <v>0.412</v>
       </c>
       <c r="AI61" t="n">
-        <v>0.6617587968543711</v>
+        <v>0.4124571101791841</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -8641,11 +8627,11 @@
         <v>946000000</v>
       </c>
       <c r="H63" t="n">
-        <v>946358000</v>
+        <v>1112224000</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -8670,11 +8656,11 @@
         <v>94000000</v>
       </c>
       <c r="Q63" t="n">
-        <v>94799000</v>
+        <v>38574000</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -8699,11 +8685,11 @@
         <v>96000000</v>
       </c>
       <c r="Z63" t="n">
-        <v>96118000</v>
+        <v>18515000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB63" t="n">
@@ -8728,7 +8714,7 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="AI63" t="n">
-        <v>0.9064888300999412</v>
+        <v>0.8071088594183294</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -8774,11 +8760,11 @@
         <v>90652000000</v>
       </c>
       <c r="H64" t="n">
-        <v>90652000000</v>
+        <v>94193000000</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -8803,11 +8789,11 @@
         <v>18367000000</v>
       </c>
       <c r="Q64" t="n">
-        <v>18367000000</v>
+        <v>16709000000</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -8832,11 +8818,11 @@
         <v>13615000000</v>
       </c>
       <c r="Z64" t="n">
-        <v>13615000000</v>
+        <v>11401000000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB64" t="n">
@@ -8861,7 +8847,7 @@
         <v>0.477</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.4605484744884453</v>
+        <v>0.4772770221749483</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -10330,11 +10316,11 @@
         <v>2316000000</v>
       </c>
       <c r="H76" t="n">
-        <v>2316649000</v>
+        <v>2376506000</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -10359,11 +10345,11 @@
         <v>-3070000000</v>
       </c>
       <c r="Q76" t="n">
-        <v>-3070206000</v>
+        <v>-4137639000</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -10388,11 +10374,11 @@
         <v>-3592000000</v>
       </c>
       <c r="Z76" t="n">
-        <v>-3592954000</v>
+        <v>-371162000</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB76" t="n">
@@ -10417,7 +10403,7 @@
         <v>0.762</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.7048307564059531</v>
+        <v>0.7857106357045343</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -11769,11 +11755,11 @@
         <v>1165000000</v>
       </c>
       <c r="H87" t="n">
-        <v>1165421000</v>
+        <v>1483813000</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -11798,11 +11784,11 @@
         <v>-523000000</v>
       </c>
       <c r="Q87" t="n">
-        <v>-523669000</v>
+        <v>-302218000</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S87" t="n">
@@ -11827,11 +11813,11 @@
         <v>-532000000</v>
       </c>
       <c r="Z87" t="n">
-        <v>-532379000</v>
+        <v>-315590000</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB87" t="n">
@@ -11856,7 +11842,7 @@
         <v>0.175</v>
       </c>
       <c r="AI87" t="n">
-        <v>0.4656515477323135</v>
+        <v>0.2006878047451718</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -16698,11 +16684,11 @@
         <v>61256000000</v>
       </c>
       <c r="H126" t="n">
-        <v>61256000000</v>
+        <v>68131000000</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -16727,11 +16713,11 @@
         <v>2311000000</v>
       </c>
       <c r="Q126" t="n">
-        <v>2312000000</v>
+        <v>3625000000</v>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S126" t="n">
@@ -16756,11 +16742,11 @@
         <v>1850000000</v>
       </c>
       <c r="Z126" t="n">
-        <v>1850000000</v>
+        <v>2896000000</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB126" t="n">
@@ -16785,7 +16771,7 @@
         <v>0.356</v>
       </c>
       <c r="AI126" t="n">
-        <v>0.3576206131471975</v>
+        <v>0.3564648686190531</v>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
@@ -17319,7 +17305,7 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>1983989000</v>
+        <v>2459803000</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -17346,7 +17332,7 @@
       </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="n">
-        <v>348734000</v>
+        <v>523639000</v>
       </c>
       <c r="R131" t="inlineStr">
         <is>
@@ -17373,7 +17359,7 @@
       </c>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="n">
-        <v>218251000</v>
+        <v>342790000</v>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
@@ -17402,7 +17388,7 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="AI131" t="n">
-        <v>0.2940907008703619</v>
+        <v>0.6874392685180875</v>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
@@ -17413,7 +17399,7 @@
         <v>5529204</v>
       </c>
       <c r="AL131" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
@@ -17706,7 +17692,7 @@
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>6868000000</v>
+        <v>6923000000</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -17733,7 +17719,7 @@
       </c>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="n">
-        <v>899000000</v>
+        <v>520000000</v>
       </c>
       <c r="R134" t="inlineStr">
         <is>
@@ -17760,7 +17746,7 @@
       </c>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="n">
-        <v>669000000</v>
+        <v>1539000000</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
@@ -17789,7 +17775,7 @@
         <v>0.699</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.4412721358872425</v>
+        <v>0.6983406113537118</v>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
@@ -18067,11 +18053,11 @@
         <v>34057000000</v>
       </c>
       <c r="H137" t="n">
-        <v>34057000000</v>
+        <v>43737000000</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -18096,11 +18082,11 @@
         <v>1981000000</v>
       </c>
       <c r="Q137" t="n">
-        <v>1981000000</v>
+        <v>2976000000</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S137" t="n">
@@ -18125,11 +18111,11 @@
         <v>2927000000</v>
       </c>
       <c r="Z137" t="n">
-        <v>2927000000</v>
+        <v>2558000000</v>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB137" t="n">
@@ -18154,7 +18140,7 @@
         <v>0.614</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.7687568609001501</v>
+        <v>0.6140635072813528</v>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
@@ -18200,11 +18186,11 @@
         <v>4072000000</v>
       </c>
       <c r="H138" t="n">
-        <v>4072136000</v>
+        <v>4895537000</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -18229,11 +18215,11 @@
         <v>-519000000</v>
       </c>
       <c r="Q138" t="n">
-        <v>-519193000</v>
+        <v>-10899000</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S138" t="n">
@@ -18258,11 +18244,11 @@
         <v>-771000000</v>
       </c>
       <c r="Z138" t="n">
-        <v>-771659000</v>
+        <v>-17357000</v>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB138" t="n">
@@ -18285,7 +18271,7 @@
         <v>0.64</v>
       </c>
       <c r="AI138" t="n">
-        <v>0.6282305898666971</v>
+        <v>0.639592797631532</v>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
@@ -18595,7 +18581,7 @@
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>2387925000</v>
+        <v>3799672000</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -18622,7 +18608,7 @@
       </c>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="n">
-        <v>861588000</v>
+        <v>1763190000</v>
       </c>
       <c r="R141" t="inlineStr">
         <is>
@@ -18649,7 +18635,7 @@
       </c>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="n">
-        <v>575761000</v>
+        <v>1153447000</v>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
@@ -18678,7 +18664,7 @@
         <v>0.769</v>
       </c>
       <c r="AI141" t="n">
-        <v>0.7601601139942905</v>
+        <v>0.7694385524471903</v>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
@@ -21286,11 +21272,11 @@
         <v>4697000000</v>
       </c>
       <c r="H162" t="n">
-        <v>4697147000</v>
+        <v>7413568000</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -21315,11 +21301,11 @@
         <v>738000000</v>
       </c>
       <c r="Q162" t="n">
-        <v>738693000</v>
+        <v>977808000</v>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S162" t="n">
@@ -21344,11 +21330,11 @@
         <v>346000000</v>
       </c>
       <c r="Z162" t="n">
-        <v>346004000</v>
+        <v>416997000</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB162" t="n">
@@ -21373,7 +21359,7 @@
         <v>0.151</v>
       </c>
       <c r="AI162" t="n">
-        <v>0.1518821415369631</v>
+        <v>0.1511154907678367</v>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
@@ -22760,7 +22746,7 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>26348000000</v>
+        <v>29826000000</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -22787,7 +22773,7 @@
       </c>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="n">
-        <v>8818000000</v>
+        <v>9873000000</v>
       </c>
       <c r="R174" t="inlineStr">
         <is>
@@ -22814,7 +22800,7 @@
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="n">
-        <v>5681000000</v>
+        <v>6325000000</v>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
@@ -22843,7 +22829,7 @@
         <v>0.379</v>
       </c>
       <c r="AI174" t="n">
-        <v>0.3846547797140123</v>
+        <v>0.3793488396527495</v>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
@@ -23347,7 +23333,7 @@
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>602796000</v>
+        <v>1256503000</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -23374,7 +23360,7 @@
       </c>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="n">
-        <v>-69074000</v>
+        <v>396535000</v>
       </c>
       <c r="R179" t="inlineStr">
         <is>
@@ -23401,7 +23387,7 @@
       </c>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="n">
-        <v>-23042000</v>
+        <v>304479000</v>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
@@ -23430,7 +23416,7 @@
         <v>0.879</v>
       </c>
       <c r="AI179" t="n">
-        <v>0.6576903484664582</v>
+        <v>0.879069133556994</v>
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
@@ -23474,7 +23460,7 @@
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>2197804000</v>
+        <v>3233597000</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -23501,7 +23487,7 @@
       </c>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="n">
-        <v>-384242000</v>
+        <v>369720000</v>
       </c>
       <c r="R180" t="inlineStr">
         <is>
@@ -23528,7 +23514,7 @@
       </c>
       <c r="Y180" t="inlineStr"/>
       <c r="Z180" t="n">
-        <v>-270464000</v>
+        <v>533582000</v>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
@@ -23557,7 +23543,7 @@
         <v>0.474</v>
       </c>
       <c r="AI180" t="n">
-        <v>0.3743763752485185</v>
+        <v>0.486475520531177</v>
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
@@ -23601,7 +23587,7 @@
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>4976878000</v>
+        <v>6109227000</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -23628,7 +23614,7 @@
       </c>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="n">
-        <v>408444000</v>
+        <v>839165000</v>
       </c>
       <c r="R181" t="inlineStr">
         <is>
@@ -23655,7 +23641,7 @@
       </c>
       <c r="Y181" t="inlineStr"/>
       <c r="Z181" t="n">
-        <v>272343000</v>
+        <v>510979000</v>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
@@ -23684,7 +23670,7 @@
         <v>0.76</v>
       </c>
       <c r="AI181" t="n">
-        <v>0.6218947334433191</v>
+        <v>0.760168739284192</v>
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
@@ -23976,7 +23962,7 @@
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>6161000000</v>
+        <v>19306000000</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -24003,7 +23989,7 @@
       </c>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="n">
-        <v>-4943000000</v>
+        <v>-677000000</v>
       </c>
       <c r="R184" t="inlineStr">
         <is>
@@ -24028,7 +24014,7 @@
       </c>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="n">
-        <v>-8013000000</v>
+        <v>-1646000000</v>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
@@ -24055,7 +24041,7 @@
         <v>0.237</v>
       </c>
       <c r="AI184" t="n">
-        <v>0.1541089566020314</v>
+        <v>0.2533541698429639</v>
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
@@ -24490,11 +24476,11 @@
         <v>7000000</v>
       </c>
       <c r="H188" t="n">
-        <v>7587000</v>
+        <v>5000000</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -24517,11 +24503,11 @@
         <v>-1069000000</v>
       </c>
       <c r="Q188" t="n">
-        <v>-1069182000</v>
+        <v>-797254000</v>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S188" t="n">
@@ -24544,11 +24530,11 @@
         <v>-964000000</v>
       </c>
       <c r="Z188" t="n">
-        <v>-964455000</v>
+        <v>-793536000</v>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB188" t="n">
@@ -24571,7 +24557,7 @@
         <v>0.978</v>
       </c>
       <c r="AI188" t="n">
-        <v>0.9844432657829761</v>
+        <v>0.9801477173950707</v>
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
@@ -24775,11 +24761,11 @@
         <v>-836000000</v>
       </c>
       <c r="Q190" t="n">
-        <v>-836346000</v>
+        <v>-916056000</v>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S190" t="n">
@@ -24804,11 +24790,11 @@
         <v>-846000000</v>
       </c>
       <c r="Z190" t="n">
-        <v>-846455000</v>
+        <v>-993227000</v>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB190" t="n">
@@ -24833,7 +24819,7 @@
         <v>0.431</v>
       </c>
       <c r="AI190" t="n">
-        <v>0.9597292561684232</v>
+        <v>0.4305342914106464</v>
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
@@ -25520,11 +25506,11 @@
         <v>50713000000</v>
       </c>
       <c r="H196" t="n">
-        <v>50713000000</v>
+        <v>57300000000</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -25549,11 +25535,11 @@
         <v>2558000000</v>
       </c>
       <c r="Q196" t="n">
-        <v>2567000000</v>
+        <v>1877000000</v>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S196" t="n">
@@ -25578,11 +25564,11 @@
         <v>2335000000</v>
       </c>
       <c r="Z196" t="n">
-        <v>2335000000</v>
+        <v>927000000</v>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB196" t="n">
@@ -25607,7 +25593,7 @@
         <v>0.374</v>
       </c>
       <c r="AI196" t="n">
-        <v>0.4855687606112054</v>
+        <v>0.3740336264758656</v>
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
@@ -25653,11 +25639,11 @@
         <v>1141000000</v>
       </c>
       <c r="H197" t="n">
-        <v>1141098000</v>
+        <v>1436294000</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -25682,11 +25668,11 @@
         <v>159000000</v>
       </c>
       <c r="Q197" t="n">
-        <v>159888000</v>
+        <v>171141000</v>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S197" t="n">
@@ -25711,11 +25697,11 @@
         <v>116000000</v>
       </c>
       <c r="Z197" t="n">
-        <v>116768000</v>
+        <v>121748000</v>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB197" t="n">
@@ -25740,7 +25726,7 @@
         <v>0.763</v>
       </c>
       <c r="AI197" t="n">
-        <v>0.76471345854999</v>
+        <v>0.7625485156616533</v>
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
@@ -26703,11 +26689,11 @@
         <v>2571000000</v>
       </c>
       <c r="H205" t="n">
-        <v>2571852000</v>
+        <v>3392422000</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -26732,11 +26718,11 @@
         <v>1135000000</v>
       </c>
       <c r="Q205" t="n">
-        <v>1135933000</v>
+        <v>1537470000</v>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S205" t="n">
@@ -26761,11 +26747,11 @@
         <v>808000000</v>
       </c>
       <c r="Z205" t="n">
-        <v>808261000</v>
+        <v>1088240000</v>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB205" t="n">
@@ -26790,7 +26776,7 @@
         <v>0.788</v>
       </c>
       <c r="AI205" t="n">
-        <v>0.7845737639089855</v>
+        <v>0.7879216516092161</v>
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
@@ -27229,11 +27215,11 @@
         <v>1923000000</v>
       </c>
       <c r="H209" t="n">
-        <v>1923000000</v>
+        <v>2137000000</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -27258,11 +27244,11 @@
         <v>391000000</v>
       </c>
       <c r="Q209" t="n">
-        <v>392000000</v>
+        <v>359000000</v>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S209" t="n">
@@ -27287,11 +27273,11 @@
         <v>268000000</v>
       </c>
       <c r="Z209" t="n">
-        <v>268000000</v>
+        <v>129000000</v>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB209" t="n">
@@ -27316,7 +27302,7 @@
         <v>0.735</v>
       </c>
       <c r="AI209" t="n">
-        <v>0.8082274652147611</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
@@ -28420,11 +28406,11 @@
         <v>3542000000</v>
       </c>
       <c r="H218" t="n">
-        <v>3542027000</v>
+        <v>4653739000</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -28449,11 +28435,11 @@
         <v>1026000000</v>
       </c>
       <c r="Q218" t="n">
-        <v>1026173000</v>
+        <v>1199337000</v>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S218" t="n">
@@ -28478,11 +28464,11 @@
         <v>757000000</v>
       </c>
       <c r="Z218" t="n">
-        <v>757427000</v>
+        <v>837093000</v>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB218" t="n">
@@ -28507,7 +28493,7 @@
         <v>0.8169999999999999</v>
       </c>
       <c r="AI218" t="n">
-        <v>0.8918752100112954</v>
+        <v>0.8171048552803526</v>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
@@ -30264,11 +30250,11 @@
         <v>6461000000</v>
       </c>
       <c r="H232" t="n">
-        <v>6461829000</v>
+        <v>6716189000</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J232" t="n">
@@ -30293,11 +30279,11 @@
         <v>528000000</v>
       </c>
       <c r="Q232" t="n">
-        <v>528186000</v>
+        <v>324762000</v>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S232" t="n">
@@ -30322,11 +30308,11 @@
         <v>394000000</v>
       </c>
       <c r="Z232" t="n">
-        <v>394676000</v>
+        <v>234059000</v>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB232" t="n">
@@ -30351,7 +30337,7 @@
         <v>0.624</v>
       </c>
       <c r="AI232" t="n">
-        <v>0.5988463140648463</v>
+        <v>0.6242990512452803</v>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
@@ -32912,11 +32898,11 @@
         <v>6287000000</v>
       </c>
       <c r="H252" t="n">
-        <v>6287105000</v>
+        <v>6462582000</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J252" t="n">
@@ -32941,11 +32927,11 @@
         <v>2493000000</v>
       </c>
       <c r="Q252" t="n">
-        <v>2493848000</v>
+        <v>2384768000</v>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S252" t="n">
@@ -32970,11 +32956,11 @@
         <v>1562000000</v>
       </c>
       <c r="Z252" t="n">
-        <v>1562679000</v>
+        <v>1498112000</v>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB252" t="n">
@@ -32999,7 +32985,7 @@
         <v>0.641</v>
       </c>
       <c r="AI252" t="n">
-        <v>0.6598943451748985</v>
+        <v>0.6414642909054467</v>
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
@@ -33045,11 +33031,11 @@
         <v>3902000000</v>
       </c>
       <c r="H253" t="n">
-        <v>3902046000</v>
+        <v>4788117000</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J253" t="n">
@@ -33074,11 +33060,11 @@
         <v>-84000000</v>
       </c>
       <c r="Q253" t="n">
-        <v>-84306000</v>
+        <v>293083000</v>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S253" t="n">
@@ -33103,11 +33089,11 @@
         <v>-37000000</v>
       </c>
       <c r="Z253" t="n">
-        <v>-37617000</v>
+        <v>485016000</v>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB253" t="n">
@@ -33132,7 +33118,7 @@
         <v>0.199</v>
       </c>
       <c r="AI253" t="n">
-        <v>0.1988514912686683</v>
+        <v>0.1990152784085578</v>
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
@@ -34835,11 +34821,11 @@
         <v>31230000000</v>
       </c>
       <c r="H267" t="n">
-        <v>21821000000</v>
+        <v>9333000000</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J267" t="n">
@@ -34862,11 +34848,11 @@
         <v>26017000000</v>
       </c>
       <c r="Q267" t="n">
-        <v>26015000000</v>
+        <v>9253000000</v>
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S267" t="n">
@@ -34889,11 +34875,11 @@
         <v>18106000000</v>
       </c>
       <c r="Z267" t="n">
-        <v>18106000000</v>
+        <v>6077000000</v>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB267" t="n">
@@ -34916,7 +34902,7 @@
         <v>0.749</v>
       </c>
       <c r="AI267" t="n">
-        <v>0.7289563567362429</v>
+        <v>0.7493367585801232</v>
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
@@ -35468,11 +35454,11 @@
         <v>2950000000</v>
       </c>
       <c r="H272" t="n">
-        <v>2950803000</v>
+        <v>3418693000</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J272" t="n">
@@ -35497,11 +35483,11 @@
         <v>302000000</v>
       </c>
       <c r="Q272" t="n">
-        <v>302095000</v>
+        <v>306286000</v>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S272" t="n">
@@ -35526,11 +35512,11 @@
         <v>301000000</v>
       </c>
       <c r="Z272" t="n">
-        <v>301663000</v>
+        <v>217536000</v>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB272" t="n">
@@ -35555,7 +35541,7 @@
         <v>0.651</v>
       </c>
       <c r="AI272" t="n">
-        <v>0.659165676638236</v>
+        <v>0.6520866796081811</v>
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
@@ -35601,11 +35587,11 @@
         <v>7803000000</v>
       </c>
       <c r="H273" t="n">
-        <v>7803013000</v>
+        <v>9189733000</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J273" t="n">
@@ -35630,11 +35616,11 @@
         <v>426000000</v>
       </c>
       <c r="Q273" t="n">
-        <v>426985000</v>
+        <v>525175000</v>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S273" t="n">
@@ -35659,11 +35645,11 @@
         <v>278000000</v>
       </c>
       <c r="Z273" t="n">
-        <v>278018000</v>
+        <v>317729000</v>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB273" t="n">
@@ -35688,7 +35674,7 @@
         <v>0.592</v>
       </c>
       <c r="AI273" t="n">
-        <v>0.6334792092297983</v>
+        <v>0.5923204553212793</v>
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
@@ -36000,11 +35986,11 @@
         <v>22713000000</v>
       </c>
       <c r="H276" t="n">
-        <v>22713000000</v>
+        <v>25779000000</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J276" t="n">
@@ -36029,11 +36015,11 @@
         <v>455000000</v>
       </c>
       <c r="Q276" t="n">
-        <v>456000000</v>
+        <v>86000000</v>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S276" t="n">
@@ -36058,11 +36044,11 @@
         <v>254000000</v>
       </c>
       <c r="Z276" t="n">
-        <v>254000000</v>
+        <v>-36000000</v>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB276" t="n">
@@ -36087,7 +36073,7 @@
         <v>0.722</v>
       </c>
       <c r="AI276" t="n">
-        <v>0.7428793371310202</v>
+        <v>0.7215109242626919</v>
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
@@ -36659,11 +36645,11 @@
         <v>12272000000</v>
       </c>
       <c r="H281" t="n">
-        <v>12272583000</v>
+        <v>14721631000</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J281" t="n">
@@ -36688,11 +36674,11 @@
         <v>860000000</v>
       </c>
       <c r="Q281" t="n">
-        <v>860266000</v>
+        <v>764871000</v>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S281" t="n">
@@ -36717,11 +36703,11 @@
         <v>535000000</v>
       </c>
       <c r="Z281" t="n">
-        <v>535590000</v>
+        <v>297445000</v>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB281" t="n">
@@ -36746,7 +36732,7 @@
         <v>0.533</v>
       </c>
       <c r="AI281" t="n">
-        <v>0.6142180487117909</v>
+        <v>0.5332888766977967</v>
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
@@ -37456,7 +37442,9 @@
       <c r="G287" t="n">
         <v>15924000000</v>
       </c>
-      <c r="H287" t="inlineStr"/>
+      <c r="H287" t="n">
+        <v>17454000000</v>
+      </c>
       <c r="I287" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -37483,7 +37471,9 @@
       <c r="P287" t="n">
         <v>3939000000</v>
       </c>
-      <c r="Q287" t="inlineStr"/>
+      <c r="Q287" t="n">
+        <v>4624000000</v>
+      </c>
       <c r="R287" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -37510,7 +37500,9 @@
       <c r="Y287" t="n">
         <v>3252000000</v>
       </c>
-      <c r="Z287" t="inlineStr"/>
+      <c r="Z287" t="n">
+        <v>2992000000</v>
+      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -37538,7 +37530,7 @@
         <v>0.828</v>
       </c>
       <c r="AI287" t="n">
-        <v>0.8167619578859294</v>
+        <v>0.8276775309862636</v>
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
@@ -38515,11 +38507,11 @@
         <v>4863000000</v>
       </c>
       <c r="H295" t="n">
-        <v>4863766000</v>
+        <v>4863553000</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J295" t="n">
@@ -38544,11 +38536,11 @@
         <v>166000000</v>
       </c>
       <c r="Q295" t="n">
-        <v>166053000</v>
+        <v>59325000</v>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S295" t="n">
@@ -38573,11 +38565,11 @@
         <v>108000000</v>
       </c>
       <c r="Z295" t="n">
-        <v>108774000</v>
+        <v>34847000</v>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB295" t="n">
@@ -38602,7 +38594,7 @@
         <v>0.877</v>
       </c>
       <c r="AI295" t="n">
-        <v>0.8311309442072088</v>
+        <v>0.8766014621307782</v>
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
@@ -38781,11 +38773,11 @@
         <v>55952000000</v>
       </c>
       <c r="H297" t="n">
-        <v>55952804000</v>
+        <v>58922469000</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J297" t="n">
@@ -38810,11 +38802,11 @@
         <v>1242000000</v>
       </c>
       <c r="Q297" t="n">
-        <v>1242400000</v>
+        <v>1468544000</v>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S297" t="n">
@@ -38839,11 +38831,11 @@
         <v>865000000</v>
       </c>
       <c r="Z297" t="n">
-        <v>865914000</v>
+        <v>1031264000</v>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB297" t="n">
@@ -38868,7 +38860,7 @@
         <v>0.34</v>
       </c>
       <c r="AI297" t="n">
-        <v>0.3303178148906977</v>
+        <v>0.3396123172545712</v>
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
@@ -40370,9 +40362,7 @@
       <c r="G309" t="n">
         <v>10348000000</v>
       </c>
-      <c r="H309" t="n">
-        <v>13007061000</v>
-      </c>
+      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -40399,9 +40389,7 @@
       <c r="P309" t="n">
         <v>147000000</v>
       </c>
-      <c r="Q309" t="n">
-        <v>472174000</v>
-      </c>
+      <c r="Q309" t="inlineStr"/>
       <c r="R309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -40428,9 +40416,7 @@
       <c r="Y309" t="n">
         <v>-88000000</v>
       </c>
-      <c r="Z309" t="n">
-        <v>168261000</v>
-      </c>
+      <c r="Z309" t="inlineStr"/>
       <c r="AA309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -40457,12 +40443,10 @@
       <c r="AH309" t="n">
         <v>0.331</v>
       </c>
-      <c r="AI309" t="n">
-        <v>0.3313848937891653</v>
-      </c>
+      <c r="AI309" t="inlineStr"/>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AK309" t="n">
@@ -42335,9 +42319,7 @@
       <c r="G324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="H324" t="n">
-        <v>3925672000</v>
-      </c>
+      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -42364,9 +42346,7 @@
       <c r="P324" t="n">
         <v>508000000</v>
       </c>
-      <c r="Q324" t="n">
-        <v>351613000</v>
-      </c>
+      <c r="Q324" t="inlineStr"/>
       <c r="R324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -42393,9 +42373,7 @@
       <c r="Y324" t="n">
         <v>327000000</v>
       </c>
-      <c r="Z324" t="n">
-        <v>173070000</v>
-      </c>
+      <c r="Z324" t="inlineStr"/>
       <c r="AA324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -42422,12 +42400,10 @@
       <c r="AH324" t="n">
         <v>0.608</v>
       </c>
-      <c r="AI324" t="n">
-        <v>0.6076252752798235</v>
-      </c>
+      <c r="AI324" t="inlineStr"/>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AK324" t="n">
@@ -42469,11 +42445,11 @@
         <v>19299000000</v>
       </c>
       <c r="H325" t="n">
-        <v>19299719000</v>
+        <v>22039886000</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J325" t="n">
@@ -42498,11 +42474,11 @@
         <v>1337000000</v>
       </c>
       <c r="Q325" t="n">
-        <v>1337550000</v>
+        <v>2247951000</v>
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S325" t="n">
@@ -42527,11 +42503,11 @@
         <v>663000000</v>
       </c>
       <c r="Z325" t="n">
-        <v>663900000</v>
+        <v>1256581000</v>
       </c>
       <c r="AA325" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB325" t="n">
@@ -42556,7 +42532,7 @@
         <v>0.275</v>
       </c>
       <c r="AI325" t="n">
-        <v>0.2547134535945298</v>
+        <v>0.2745278369958499</v>
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
@@ -47100,11 +47076,11 @@
         <v>3642000000</v>
       </c>
       <c r="H360" t="n">
-        <v>3642692000</v>
+        <v>3501884000</v>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J360" t="n">
@@ -47129,11 +47105,11 @@
         <v>155000000</v>
       </c>
       <c r="Q360" t="n">
-        <v>155242000</v>
+        <v>211817000</v>
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S360" t="n">
@@ -47158,11 +47134,11 @@
         <v>111000000</v>
       </c>
       <c r="Z360" t="n">
-        <v>111115000</v>
+        <v>98819000</v>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB360" t="n">
@@ -47187,7 +47163,7 @@
         <v>0.711</v>
       </c>
       <c r="AI360" t="n">
-        <v>0.7054981761415569</v>
+        <v>0.7113536589213938</v>
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
@@ -47626,11 +47602,11 @@
         <v>4625000000</v>
       </c>
       <c r="H364" t="n">
-        <v>4625427000</v>
+        <v>5005091000</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J364" t="n">
@@ -47655,11 +47631,11 @@
         <v>1155000000</v>
       </c>
       <c r="Q364" t="n">
-        <v>1155364000</v>
+        <v>1201982000</v>
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S364" t="n">
@@ -47684,11 +47660,11 @@
         <v>839000000</v>
       </c>
       <c r="Z364" t="n">
-        <v>839294000</v>
+        <v>848969000</v>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB364" t="n">
@@ -47713,7 +47689,7 @@
         <v>0.678</v>
       </c>
       <c r="AI364" t="n">
-        <v>0.6653704946384902</v>
+        <v>0.6923452567269976</v>
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
@@ -49482,11 +49458,11 @@
         <v>2120000000</v>
       </c>
       <c r="H378" t="n">
-        <v>2120772000</v>
+        <v>2280860000</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="J378" t="n">
@@ -49511,11 +49487,11 @@
         <v>-382000000</v>
       </c>
       <c r="Q378" t="n">
-        <v>-382641000</v>
+        <v>9169000</v>
       </c>
       <c r="R378" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S378" t="n">
@@ -49540,11 +49516,11 @@
         <v>-852000000</v>
       </c>
       <c r="Z378" t="n">
-        <v>-852052000</v>
+        <v>22550000</v>
       </c>
       <c r="AA378" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AB378" t="n">
@@ -49569,7 +49545,7 @@
         <v>0.863</v>
       </c>
       <c r="AI378" t="n">
-        <v>0.8537787002057914</v>
+        <v>0.8630595477582084</v>
       </c>
       <c r="AJ378" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -710,11 +710,11 @@
         <v>235018000</v>
       </c>
       <c r="I2" t="n">
-        <v>194643000</v>
+        <v>91140000</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -744,11 +744,11 @@
         <v>-212000000</v>
       </c>
       <c r="U2" t="n">
-        <v>-212850000</v>
+        <v>-396748000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -782,11 +782,11 @@
         <v>-236000000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-236442000</v>
+        <v>-425671000</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI2" t="n">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9824758843873473</v>
+        <v>0.9463974976020101</v>
       </c>
       <c r="AR2" t="n">
         <v>0.946</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.9824758843873473</v>
+        <v>0.9463974976020101</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -1860,11 +1860,11 @@
         <v>1594000000</v>
       </c>
       <c r="I9" t="n">
-        <v>1594038000</v>
+        <v>2132680000</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1898,11 +1898,11 @@
         <v>47000000</v>
       </c>
       <c r="U9" t="n">
-        <v>77143000</v>
+        <v>169142000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -1936,11 +1936,11 @@
         <v>13000000</v>
       </c>
       <c r="AG9" t="n">
-        <v>42941000</v>
+        <v>138852000</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI9" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.6309998209297989</v>
+        <v>0.5393850710997311</v>
       </c>
       <c r="AR9" t="n">
         <v>0.539</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.6309998209297989</v>
+        <v>0.5393850710997311</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -2026,11 +2026,11 @@
         <v>20981000000</v>
       </c>
       <c r="I10" t="n">
-        <v>20981000000</v>
+        <v>37084000000</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2064,11 +2064,11 @@
         <v>3892000000</v>
       </c>
       <c r="U10" t="n">
-        <v>3893000000</v>
+        <v>6029000000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -2102,11 +2102,11 @@
         <v>2238000000</v>
       </c>
       <c r="AG10" t="n">
-        <v>2238000000</v>
+        <v>3464000000</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI10" t="n">
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.2318437895220941</v>
+        <v>0.2605080969541098</v>
       </c>
       <c r="AR10" t="n">
         <v>0.261</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.2318437895220941</v>
+        <v>0.2605080969541098</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -3188,11 +3188,11 @@
         <v>5847000000</v>
       </c>
       <c r="I17" t="n">
-        <v>5847966000</v>
+        <v>8019568000</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -3226,11 +3226,11 @@
         <v>413000000</v>
       </c>
       <c r="U17" t="n">
-        <v>413119000</v>
+        <v>553165000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -3264,11 +3264,11 @@
         <v>273000000</v>
       </c>
       <c r="AG17" t="n">
-        <v>273173000</v>
+        <v>304310000</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI17" t="n">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>0.6224297830439212</v>
+        <v>0.4271421292686969</v>
       </c>
       <c r="AR17" t="n">
         <v>0.427</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.6224297830439212</v>
+        <v>0.4271421292686969</v>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
@@ -4512,11 +4512,11 @@
         <v>512000000</v>
       </c>
       <c r="I25" t="n">
-        <v>1085861000</v>
+        <v>805211000</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -4550,11 +4550,11 @@
         <v>-227000000</v>
       </c>
       <c r="U25" t="n">
-        <v>36125000</v>
+        <v>-283087000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -4588,11 +4588,11 @@
         <v>-223000000</v>
       </c>
       <c r="AG25" t="n">
-        <v>27104000</v>
+        <v>-415606000</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI25" t="n">
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>0.624429691222611</v>
+        <v>0.007279642631564494</v>
       </c>
       <c r="AR25" t="n">
         <v>0.007</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.624429691222611</v>
+        <v>0.007279642631564494</v>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
@@ -5803,12 +5803,14 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>2374756000</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>2986723000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2986000000</v>
+      </c>
       <c r="I33" t="n">
         <v>2986723000</v>
       </c>
@@ -5818,10 +5820,10 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2986000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L33" t="n">
-        <v>2986000000</v>
+        <v>4100000000</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
@@ -5830,10 +5832,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>4470000000</v>
+        <v>3887000000</v>
       </c>
       <c r="P33" t="n">
-        <v>4470000000</v>
+        <v>3887000000</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -5842,9 +5844,11 @@
         </is>
       </c>
       <c r="S33" t="n">
-        <v>87987000</v>
-      </c>
-      <c r="T33" t="inlineStr"/>
+        <v>88007000</v>
+      </c>
+      <c r="T33" t="n">
+        <v>88000000</v>
+      </c>
       <c r="U33" t="n">
         <v>88007000</v>
       </c>
@@ -5853,16 +5857,12 @@
           <t>YF</t>
         </is>
       </c>
-      <c r="W33" t="n">
-        <v>88000000</v>
-      </c>
-      <c r="X33" t="n">
-        <v>88000000</v>
-      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr"/>
@@ -5874,9 +5874,11 @@
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>109979000</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
+        <v>112934000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>112000000</v>
+      </c>
       <c r="AG33" t="n">
         <v>112934000</v>
       </c>
@@ -5885,16 +5887,12 @@
           <t>YF</t>
         </is>
       </c>
-      <c r="AI33" t="n">
-        <v>112000000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>112000000</v>
-      </c>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr"/>
@@ -7736,11 +7734,11 @@
         <v>3026500000</v>
       </c>
       <c r="I45" t="n">
-        <v>873610000</v>
+        <v>3026500000</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -7774,11 +7772,11 @@
         <v>726442000</v>
       </c>
       <c r="U45" t="n">
-        <v>-1038802000</v>
+        <v>272157000</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W45" t="n">
@@ -7812,11 +7810,11 @@
         <v>592496000</v>
       </c>
       <c r="AG45" t="n">
-        <v>-812725000</v>
+        <v>190608000</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI45" t="n">
@@ -7844,13 +7842,13 @@
         </is>
       </c>
       <c r="AQ45" t="n">
-        <v>0.9371290993795059</v>
+        <v>0.9373562111007017</v>
       </c>
       <c r="AR45" t="n">
         <v>0.9370000000000001</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.9371290993795059</v>
+        <v>0.9373562111007017</v>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
@@ -9046,11 +9044,11 @@
         <v>908000000</v>
       </c>
       <c r="I53" t="n">
-        <v>908174000</v>
+        <v>1157139000</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -9084,11 +9082,11 @@
         <v>169000000</v>
       </c>
       <c r="U53" t="n">
-        <v>169032000</v>
+        <v>248411000</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W53" t="n">
@@ -9122,11 +9120,11 @@
         <v>104000000</v>
       </c>
       <c r="AG53" t="n">
-        <v>104916000</v>
+        <v>157967000</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI53" t="n">
@@ -9154,13 +9152,13 @@
         </is>
       </c>
       <c r="AQ53" t="n">
-        <v>0.8348863344341269</v>
+        <v>0.8406616004212384</v>
       </c>
       <c r="AR53" t="n">
         <v>0.84</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.8348863344341269</v>
+        <v>0.8406616004212384</v>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
@@ -10166,11 +10164,11 @@
         <v>23533000000</v>
       </c>
       <c r="I60" t="n">
-        <v>23533494000</v>
+        <v>24413727000</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -10204,11 +10202,11 @@
         <v>2176000000</v>
       </c>
       <c r="U60" t="n">
-        <v>2176648000</v>
+        <v>2379975000</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W60" t="n">
@@ -10242,11 +10240,11 @@
         <v>1491000000</v>
       </c>
       <c r="AG60" t="n">
-        <v>1491884000</v>
+        <v>1730727000</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI60" t="n">
@@ -10274,13 +10272,13 @@
         </is>
       </c>
       <c r="AQ60" t="n">
-        <v>0.6195884627545886</v>
+        <v>0.5977518816535092</v>
       </c>
       <c r="AR60" t="n">
         <v>0.598</v>
       </c>
       <c r="AS60" t="n">
-        <v>0.6195884627545886</v>
+        <v>0.5977518816535092</v>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
@@ -10332,11 +10330,11 @@
         <v>44845000000</v>
       </c>
       <c r="I61" t="n">
-        <v>44845000000</v>
+        <v>50151000000</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -10370,11 +10368,11 @@
         <v>5012000000</v>
       </c>
       <c r="U61" t="n">
-        <v>5012000000</v>
+        <v>5991000000</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W61" t="n">
@@ -10408,11 +10406,11 @@
         <v>3515000000</v>
       </c>
       <c r="AG61" t="n">
-        <v>3515000000</v>
+        <v>4119000000</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI61" t="n">
@@ -10440,13 +10438,13 @@
         </is>
       </c>
       <c r="AQ61" t="n">
-        <v>0.6617587968543711</v>
+        <v>0.4124571101791841</v>
       </c>
       <c r="AR61" t="n">
         <v>0.412</v>
       </c>
       <c r="AS61" t="n">
-        <v>0.6617587968543711</v>
+        <v>0.4124571101791841</v>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
@@ -10664,11 +10662,11 @@
         <v>946000000</v>
       </c>
       <c r="I63" t="n">
-        <v>946358000</v>
+        <v>1112224000</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -10702,11 +10700,11 @@
         <v>94000000</v>
       </c>
       <c r="U63" t="n">
-        <v>94799000</v>
+        <v>38574000</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -10740,11 +10738,11 @@
         <v>96000000</v>
       </c>
       <c r="AG63" t="n">
-        <v>96118000</v>
+        <v>18515000</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI63" t="n">
@@ -10772,13 +10770,13 @@
         </is>
       </c>
       <c r="AQ63" t="n">
-        <v>0.9064888300999412</v>
+        <v>0.8071088594183294</v>
       </c>
       <c r="AR63" t="n">
         <v>0.8070000000000001</v>
       </c>
       <c r="AS63" t="n">
-        <v>0.9064888300999412</v>
+        <v>0.8071088594183294</v>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
@@ -10830,11 +10828,11 @@
         <v>90652000000</v>
       </c>
       <c r="I64" t="n">
-        <v>90652000000</v>
+        <v>94193000000</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -10868,11 +10866,11 @@
         <v>18367000000</v>
       </c>
       <c r="U64" t="n">
-        <v>18367000000</v>
+        <v>16709000000</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W64" t="n">
@@ -10906,11 +10904,11 @@
         <v>13615000000</v>
       </c>
       <c r="AG64" t="n">
-        <v>13615000000</v>
+        <v>11401000000</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI64" t="n">
@@ -10938,13 +10936,13 @@
         </is>
       </c>
       <c r="AQ64" t="n">
-        <v>0.4605484744884453</v>
+        <v>0.4772770221749483</v>
       </c>
       <c r="AR64" t="n">
         <v>0.477</v>
       </c>
       <c r="AS64" t="n">
-        <v>0.4605484744884453</v>
+        <v>0.4772770221749483</v>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
@@ -12772,11 +12770,11 @@
         <v>2316000000</v>
       </c>
       <c r="I76" t="n">
-        <v>2316649000</v>
+        <v>2376506000</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -12810,11 +12808,11 @@
         <v>-3070000000</v>
       </c>
       <c r="U76" t="n">
-        <v>-3070206000</v>
+        <v>-4137639000</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W76" t="n">
@@ -12848,11 +12846,11 @@
         <v>-3592000000</v>
       </c>
       <c r="AG76" t="n">
-        <v>-3592954000</v>
+        <v>-371162000</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI76" t="n">
@@ -12880,13 +12878,13 @@
         </is>
       </c>
       <c r="AQ76" t="n">
-        <v>0.7048307564059531</v>
+        <v>0.7857106357045343</v>
       </c>
       <c r="AR76" t="n">
         <v>0.762</v>
       </c>
       <c r="AS76" t="n">
-        <v>0.7048307564059531</v>
+        <v>0.7857106357045343</v>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
@@ -14568,11 +14566,11 @@
         <v>1165000000</v>
       </c>
       <c r="I87" t="n">
-        <v>1165421000</v>
+        <v>1483813000</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -14606,11 +14604,11 @@
         <v>-523000000</v>
       </c>
       <c r="U87" t="n">
-        <v>-523669000</v>
+        <v>-302218000</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W87" t="n">
@@ -14644,11 +14642,11 @@
         <v>-532000000</v>
       </c>
       <c r="AG87" t="n">
-        <v>-532379000</v>
+        <v>-315590000</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI87" t="n">
@@ -14676,13 +14674,13 @@
         </is>
       </c>
       <c r="AQ87" t="n">
-        <v>0.4656515477323135</v>
+        <v>0.2006878047451718</v>
       </c>
       <c r="AR87" t="n">
         <v>0.175</v>
       </c>
       <c r="AS87" t="n">
-        <v>0.4656515477323135</v>
+        <v>0.2006878047451718</v>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
@@ -20724,11 +20722,11 @@
         <v>61256000000</v>
       </c>
       <c r="I126" t="n">
-        <v>61256000000</v>
+        <v>68131000000</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -20762,11 +20760,11 @@
         <v>2311000000</v>
       </c>
       <c r="U126" t="n">
-        <v>2312000000</v>
+        <v>3625000000</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W126" t="n">
@@ -20800,11 +20798,11 @@
         <v>1850000000</v>
       </c>
       <c r="AG126" t="n">
-        <v>1850000000</v>
+        <v>2896000000</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI126" t="n">
@@ -20832,13 +20830,13 @@
         </is>
       </c>
       <c r="AQ126" t="n">
-        <v>0.3576206131471975</v>
+        <v>0.3564648686190531</v>
       </c>
       <c r="AR126" t="n">
         <v>0.356</v>
       </c>
       <c r="AS126" t="n">
-        <v>0.3576206131471975</v>
+        <v>0.3564648686190531</v>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
@@ -22410,11 +22408,11 @@
         <v>34057000000</v>
       </c>
       <c r="I137" t="n">
-        <v>34057000000</v>
+        <v>43737000000</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -22448,11 +22446,11 @@
         <v>1981000000</v>
       </c>
       <c r="U137" t="n">
-        <v>1981000000</v>
+        <v>2976000000</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W137" t="n">
@@ -22486,11 +22484,11 @@
         <v>2927000000</v>
       </c>
       <c r="AG137" t="n">
-        <v>2927000000</v>
+        <v>2558000000</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI137" t="n">
@@ -22518,13 +22516,13 @@
         </is>
       </c>
       <c r="AQ137" t="n">
-        <v>0.7687568609001501</v>
+        <v>0.6140635072813528</v>
       </c>
       <c r="AR137" t="n">
         <v>0.614</v>
       </c>
       <c r="AS137" t="n">
-        <v>0.7687568609001501</v>
+        <v>0.6140635072813528</v>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
@@ -22576,11 +22574,11 @@
         <v>4072000000</v>
       </c>
       <c r="I138" t="n">
-        <v>4072136000</v>
+        <v>4895537000</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -22614,11 +22612,11 @@
         <v>-519000000</v>
       </c>
       <c r="U138" t="n">
-        <v>-519193000</v>
+        <v>-10899000</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W138" t="n">
@@ -22652,11 +22650,11 @@
         <v>-771000000</v>
       </c>
       <c r="AG138" t="n">
-        <v>-771659000</v>
+        <v>-17357000</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI138" t="n">
@@ -22680,13 +22678,13 @@
         </is>
       </c>
       <c r="AQ138" t="n">
-        <v>0.6282305898666971</v>
+        <v>0.639592797631532</v>
       </c>
       <c r="AR138" t="n">
         <v>0.64</v>
       </c>
       <c r="AS138" t="n">
-        <v>0.6282305898666971</v>
+        <v>0.639592797631532</v>
       </c>
       <c r="AT138" t="inlineStr">
         <is>
@@ -23068,7 +23066,7 @@
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>2387925000</v>
+        <v>3799672000</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -23104,7 +23102,7 @@
       </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="n">
-        <v>861588000</v>
+        <v>1763190000</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -23140,7 +23138,7 @@
       </c>
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="n">
-        <v>575761000</v>
+        <v>1153447000</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23172,13 +23170,13 @@
         </is>
       </c>
       <c r="AQ141" t="n">
-        <v>0.7601601139942905</v>
+        <v>0.7694385524471903</v>
       </c>
       <c r="AR141" t="n">
         <v>0.769</v>
       </c>
       <c r="AS141" t="n">
-        <v>0.7601601139942905</v>
+        <v>0.7694385524471903</v>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
@@ -26406,11 +26404,11 @@
         <v>4697000000</v>
       </c>
       <c r="I162" t="n">
-        <v>4697147000</v>
+        <v>7413568000</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -26444,11 +26442,11 @@
         <v>738000000</v>
       </c>
       <c r="U162" t="n">
-        <v>738693000</v>
+        <v>977808000</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W162" t="n">
@@ -26482,11 +26480,11 @@
         <v>346000000</v>
       </c>
       <c r="AG162" t="n">
-        <v>346004000</v>
+        <v>416997000</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI162" t="n">
@@ -26514,13 +26512,13 @@
         </is>
       </c>
       <c r="AQ162" t="n">
-        <v>0.1518821415369631</v>
+        <v>0.1511154907678367</v>
       </c>
       <c r="AR162" t="n">
         <v>0.151</v>
       </c>
       <c r="AS162" t="n">
-        <v>0.1518821415369631</v>
+        <v>0.1511154907678367</v>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
@@ -28928,7 +28926,7 @@
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
-        <v>602796000</v>
+        <v>1256503000</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -28964,7 +28962,7 @@
       </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="n">
-        <v>-69074000</v>
+        <v>396535000</v>
       </c>
       <c r="V179" t="inlineStr">
         <is>
@@ -29000,7 +28998,7 @@
       </c>
       <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="n">
-        <v>-23042000</v>
+        <v>304479000</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29032,13 +29030,13 @@
         </is>
       </c>
       <c r="AQ179" t="n">
-        <v>0.6576903484664582</v>
+        <v>0.879069133556994</v>
       </c>
       <c r="AR179" t="n">
         <v>0.879</v>
       </c>
       <c r="AS179" t="n">
-        <v>0.6576903484664582</v>
+        <v>0.879069133556994</v>
       </c>
       <c r="AT179" t="inlineStr">
         <is>
@@ -29088,7 +29086,7 @@
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
-        <v>2197804000</v>
+        <v>3233597000</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -29124,7 +29122,7 @@
       </c>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="n">
-        <v>-384242000</v>
+        <v>369720000</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
@@ -29160,7 +29158,7 @@
       </c>
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="n">
-        <v>-270464000</v>
+        <v>533582000</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29192,13 +29190,13 @@
         </is>
       </c>
       <c r="AQ180" t="n">
-        <v>0.3743763752485185</v>
+        <v>0.486475520531177</v>
       </c>
       <c r="AR180" t="n">
         <v>0.474</v>
       </c>
       <c r="AS180" t="n">
-        <v>0.3743763752485185</v>
+        <v>0.486475520531177</v>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
@@ -29248,7 +29246,7 @@
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
-        <v>4976878000</v>
+        <v>6109227000</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -29284,7 +29282,7 @@
       </c>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="n">
-        <v>408444000</v>
+        <v>839165000</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
@@ -29320,7 +29318,7 @@
       </c>
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="n">
-        <v>272343000</v>
+        <v>510979000</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29352,13 +29350,13 @@
         </is>
       </c>
       <c r="AQ181" t="n">
-        <v>0.6218947334433191</v>
+        <v>0.760168739284192</v>
       </c>
       <c r="AR181" t="n">
         <v>0.76</v>
       </c>
       <c r="AS181" t="n">
-        <v>0.6218947334433191</v>
+        <v>0.760168739284192</v>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
@@ -29710,7 +29708,7 @@
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
-        <v>6161000000</v>
+        <v>19306000000</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -29746,7 +29744,7 @@
       </c>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="n">
-        <v>-4943000000</v>
+        <v>-677000000</v>
       </c>
       <c r="V184" t="inlineStr">
         <is>
@@ -29778,7 +29776,7 @@
       </c>
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="n">
-        <v>-8013000000</v>
+        <v>-1646000000</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -29806,13 +29804,13 @@
         </is>
       </c>
       <c r="AQ184" t="n">
-        <v>0.1541089566020314</v>
+        <v>0.2533541698429639</v>
       </c>
       <c r="AR184" t="n">
         <v>0.237</v>
       </c>
       <c r="AS184" t="n">
-        <v>0.1541089566020314</v>
+        <v>0.2533541698429639</v>
       </c>
       <c r="AT184" t="inlineStr">
         <is>
@@ -29820,13 +29818,13 @@
         </is>
       </c>
       <c r="AU184" t="n">
-        <v>37599800</v>
+        <v>37924300</v>
       </c>
       <c r="AV184" t="n">
         <v>36353600</v>
       </c>
       <c r="AW184" t="n">
-        <v>37599800</v>
+        <v>37924300</v>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
@@ -30344,11 +30342,11 @@
         <v>7000000</v>
       </c>
       <c r="I188" t="n">
-        <v>7587000</v>
+        <v>5000000</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K188" t="n">
@@ -30378,11 +30376,11 @@
         <v>-1069000000</v>
       </c>
       <c r="U188" t="n">
-        <v>-1069182000</v>
+        <v>-797254000</v>
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W188" t="n">
@@ -30412,11 +30410,11 @@
         <v>-964000000</v>
       </c>
       <c r="AG188" t="n">
-        <v>-964455000</v>
+        <v>-793536000</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI188" t="n">
@@ -30440,13 +30438,13 @@
         </is>
       </c>
       <c r="AQ188" t="n">
-        <v>0.9844432657829761</v>
+        <v>0.9801477173950707</v>
       </c>
       <c r="AR188" t="n">
         <v>0.978</v>
       </c>
       <c r="AS188" t="n">
-        <v>0.9844432657829761</v>
+        <v>0.9801477173950707</v>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
@@ -30694,11 +30692,11 @@
         <v>-836000000</v>
       </c>
       <c r="U190" t="n">
-        <v>-836346000</v>
+        <v>-916056000</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W190" t="n">
@@ -30732,11 +30730,11 @@
         <v>-846000000</v>
       </c>
       <c r="AG190" t="n">
-        <v>-846455000</v>
+        <v>-993227000</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI190" t="n">
@@ -30764,13 +30762,13 @@
         </is>
       </c>
       <c r="AQ190" t="n">
-        <v>0.9597292561684232</v>
+        <v>0.4305342914106464</v>
       </c>
       <c r="AR190" t="n">
         <v>0.431</v>
       </c>
       <c r="AS190" t="n">
-        <v>0.9597292561684232</v>
+        <v>0.4305342914106464</v>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
@@ -31616,11 +31614,11 @@
         <v>50713000000</v>
       </c>
       <c r="I196" t="n">
-        <v>50713000000</v>
+        <v>57300000000</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K196" t="n">
@@ -31654,11 +31652,11 @@
         <v>2558000000</v>
       </c>
       <c r="U196" t="n">
-        <v>2567000000</v>
+        <v>1877000000</v>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W196" t="n">
@@ -31692,11 +31690,11 @@
         <v>2335000000</v>
       </c>
       <c r="AG196" t="n">
-        <v>2335000000</v>
+        <v>927000000</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI196" t="n">
@@ -31724,13 +31722,13 @@
         </is>
       </c>
       <c r="AQ196" t="n">
-        <v>0.4855687606112054</v>
+        <v>0.3740336264758656</v>
       </c>
       <c r="AR196" t="n">
         <v>0.374</v>
       </c>
       <c r="AS196" t="n">
-        <v>0.4855687606112054</v>
+        <v>0.3740336264758656</v>
       </c>
       <c r="AT196" t="inlineStr">
         <is>
@@ -31782,11 +31780,11 @@
         <v>1141000000</v>
       </c>
       <c r="I197" t="n">
-        <v>1141098000</v>
+        <v>1436294000</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -31820,11 +31818,11 @@
         <v>159000000</v>
       </c>
       <c r="U197" t="n">
-        <v>159888000</v>
+        <v>171141000</v>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W197" t="n">
@@ -31858,11 +31856,11 @@
         <v>116000000</v>
       </c>
       <c r="AG197" t="n">
-        <v>116768000</v>
+        <v>121748000</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI197" t="n">
@@ -31890,13 +31888,13 @@
         </is>
       </c>
       <c r="AQ197" t="n">
-        <v>0.76471345854999</v>
+        <v>0.7625485156616533</v>
       </c>
       <c r="AR197" t="n">
         <v>0.763</v>
       </c>
       <c r="AS197" t="n">
-        <v>0.76471345854999</v>
+        <v>0.7625485156616533</v>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
@@ -33088,11 +33086,11 @@
         <v>2571000000</v>
       </c>
       <c r="I205" t="n">
-        <v>2571852000</v>
+        <v>3392422000</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K205" t="n">
@@ -33126,11 +33124,11 @@
         <v>1135000000</v>
       </c>
       <c r="U205" t="n">
-        <v>1135933000</v>
+        <v>1537470000</v>
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W205" t="n">
@@ -33164,11 +33162,11 @@
         <v>808000000</v>
       </c>
       <c r="AG205" t="n">
-        <v>808261000</v>
+        <v>1088240000</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI205" t="n">
@@ -33196,13 +33194,13 @@
         </is>
       </c>
       <c r="AQ205" t="n">
-        <v>0.7845737639089855</v>
+        <v>0.7879216516092161</v>
       </c>
       <c r="AR205" t="n">
         <v>0.788</v>
       </c>
       <c r="AS205" t="n">
-        <v>0.7845737639089855</v>
+        <v>0.7879216516092161</v>
       </c>
       <c r="AT205" t="inlineStr">
         <is>
@@ -33746,11 +33744,11 @@
         <v>1923000000</v>
       </c>
       <c r="I209" t="n">
-        <v>1923000000</v>
+        <v>2137000000</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K209" t="n">
@@ -33784,11 +33782,11 @@
         <v>391000000</v>
       </c>
       <c r="U209" t="n">
-        <v>392000000</v>
+        <v>359000000</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W209" t="n">
@@ -33822,11 +33820,11 @@
         <v>268000000</v>
       </c>
       <c r="AG209" t="n">
-        <v>268000000</v>
+        <v>129000000</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI209" t="n">
@@ -33854,13 +33852,13 @@
         </is>
       </c>
       <c r="AQ209" t="n">
-        <v>0.8082274652147611</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="AR209" t="n">
         <v>0.735</v>
       </c>
       <c r="AS209" t="n">
-        <v>0.8082274652147611</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
@@ -35228,11 +35226,11 @@
         <v>3542000000</v>
       </c>
       <c r="I218" t="n">
-        <v>3542027000</v>
+        <v>4653739000</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K218" t="n">
@@ -35266,11 +35264,11 @@
         <v>1026000000</v>
       </c>
       <c r="U218" t="n">
-        <v>1026173000</v>
+        <v>1199337000</v>
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W218" t="n">
@@ -35304,11 +35302,11 @@
         <v>757000000</v>
       </c>
       <c r="AG218" t="n">
-        <v>757427000</v>
+        <v>837093000</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI218" t="n">
@@ -35336,13 +35334,13 @@
         </is>
       </c>
       <c r="AQ218" t="n">
-        <v>0.8918752100112954</v>
+        <v>0.8171048552803526</v>
       </c>
       <c r="AR218" t="n">
         <v>0.8169999999999999</v>
       </c>
       <c r="AS218" t="n">
-        <v>0.8918752100112954</v>
+        <v>0.8171048552803526</v>
       </c>
       <c r="AT218" t="inlineStr">
         <is>
@@ -37528,11 +37526,11 @@
         <v>6461000000</v>
       </c>
       <c r="I232" t="n">
-        <v>6461829000</v>
+        <v>6716189000</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K232" t="n">
@@ -37566,11 +37564,11 @@
         <v>528000000</v>
       </c>
       <c r="U232" t="n">
-        <v>528186000</v>
+        <v>324762000</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W232" t="n">
@@ -37604,11 +37602,11 @@
         <v>394000000</v>
       </c>
       <c r="AG232" t="n">
-        <v>394676000</v>
+        <v>234059000</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI232" t="n">
@@ -37636,13 +37634,13 @@
         </is>
       </c>
       <c r="AQ232" t="n">
-        <v>0.5988463140648463</v>
+        <v>0.6242990512452803</v>
       </c>
       <c r="AR232" t="n">
         <v>0.624</v>
       </c>
       <c r="AS232" t="n">
-        <v>0.5988463140648463</v>
+        <v>0.6242990512452803</v>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
@@ -40836,11 +40834,11 @@
         <v>6287000000</v>
       </c>
       <c r="I252" t="n">
-        <v>6287105000</v>
+        <v>6462582000</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K252" t="n">
@@ -40874,11 +40872,11 @@
         <v>2493000000</v>
       </c>
       <c r="U252" t="n">
-        <v>2493848000</v>
+        <v>2384768000</v>
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W252" t="n">
@@ -40912,11 +40910,11 @@
         <v>1562000000</v>
       </c>
       <c r="AG252" t="n">
-        <v>1562679000</v>
+        <v>1498112000</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI252" t="n">
@@ -40944,13 +40942,13 @@
         </is>
       </c>
       <c r="AQ252" t="n">
-        <v>0.6598943451748985</v>
+        <v>0.6414642909054467</v>
       </c>
       <c r="AR252" t="n">
         <v>0.641</v>
       </c>
       <c r="AS252" t="n">
-        <v>0.6598943451748985</v>
+        <v>0.6414642909054467</v>
       </c>
       <c r="AT252" t="inlineStr">
         <is>
@@ -41002,11 +41000,11 @@
         <v>3902000000</v>
       </c>
       <c r="I253" t="n">
-        <v>3902046000</v>
+        <v>4788117000</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K253" t="n">
@@ -41040,11 +41038,11 @@
         <v>-84000000</v>
       </c>
       <c r="U253" t="n">
-        <v>-84306000</v>
+        <v>293083000</v>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W253" t="n">
@@ -41078,11 +41076,11 @@
         <v>-37000000</v>
       </c>
       <c r="AG253" t="n">
-        <v>-37617000</v>
+        <v>485016000</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI253" t="n">
@@ -41110,13 +41108,13 @@
         </is>
       </c>
       <c r="AQ253" t="n">
-        <v>0.1988514912686683</v>
+        <v>0.1990152784085578</v>
       </c>
       <c r="AR253" t="n">
         <v>0.199</v>
       </c>
       <c r="AS253" t="n">
-        <v>0.1988514912686683</v>
+        <v>0.1990152784085578</v>
       </c>
       <c r="AT253" t="inlineStr">
         <is>
@@ -44174,11 +44172,11 @@
         <v>7803000000</v>
       </c>
       <c r="I273" t="n">
-        <v>7803013000</v>
+        <v>9189733000</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K273" t="n">
@@ -44212,11 +44210,11 @@
         <v>426000000</v>
       </c>
       <c r="U273" t="n">
-        <v>426985000</v>
+        <v>525175000</v>
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W273" t="n">
@@ -44250,11 +44248,11 @@
         <v>278000000</v>
       </c>
       <c r="AG273" t="n">
-        <v>278018000</v>
+        <v>317729000</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI273" t="n">
@@ -44282,13 +44280,13 @@
         </is>
       </c>
       <c r="AQ273" t="n">
-        <v>0.6334792092297983</v>
+        <v>0.5923204553212793</v>
       </c>
       <c r="AR273" t="n">
         <v>0.592</v>
       </c>
       <c r="AS273" t="n">
-        <v>0.6334792092297983</v>
+        <v>0.5923204553212793</v>
       </c>
       <c r="AT273" t="inlineStr">
         <is>
@@ -44672,11 +44670,11 @@
         <v>22713000000</v>
       </c>
       <c r="I276" t="n">
-        <v>22713000000</v>
+        <v>25779000000</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K276" t="n">
@@ -44710,11 +44708,11 @@
         <v>455000000</v>
       </c>
       <c r="U276" t="n">
-        <v>456000000</v>
+        <v>86000000</v>
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W276" t="n">
@@ -44748,11 +44746,11 @@
         <v>254000000</v>
       </c>
       <c r="AG276" t="n">
-        <v>254000000</v>
+        <v>-36000000</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI276" t="n">
@@ -44780,13 +44778,13 @@
         </is>
       </c>
       <c r="AQ276" t="n">
-        <v>0.7428793371310202</v>
+        <v>0.7215109242626919</v>
       </c>
       <c r="AR276" t="n">
         <v>0.722</v>
       </c>
       <c r="AS276" t="n">
-        <v>0.7428793371310202</v>
+        <v>0.7215109242626919</v>
       </c>
       <c r="AT276" t="inlineStr">
         <is>
@@ -45496,11 +45494,11 @@
         <v>12272000000</v>
       </c>
       <c r="I281" t="n">
-        <v>12272583000</v>
+        <v>14721631000</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K281" t="n">
@@ -45534,11 +45532,11 @@
         <v>860000000</v>
       </c>
       <c r="U281" t="n">
-        <v>860266000</v>
+        <v>764871000</v>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W281" t="n">
@@ -45572,11 +45570,11 @@
         <v>535000000</v>
       </c>
       <c r="AG281" t="n">
-        <v>535590000</v>
+        <v>297445000</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI281" t="n">
@@ -45604,13 +45602,13 @@
         </is>
       </c>
       <c r="AQ281" t="n">
-        <v>0.6142180487117909</v>
+        <v>0.5332888766977967</v>
       </c>
       <c r="AR281" t="n">
         <v>0.533</v>
       </c>
       <c r="AS281" t="n">
-        <v>0.6142180487117909</v>
+        <v>0.5332888766977967</v>
       </c>
       <c r="AT281" t="inlineStr">
         <is>
@@ -46491,7 +46489,9 @@
       <c r="H287" t="n">
         <v>15924000000</v>
       </c>
-      <c r="I287" t="inlineStr"/>
+      <c r="I287" t="n">
+        <v>17454000000</v>
+      </c>
       <c r="J287" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -46527,7 +46527,9 @@
       <c r="T287" t="n">
         <v>3939000000</v>
       </c>
-      <c r="U287" t="inlineStr"/>
+      <c r="U287" t="n">
+        <v>4624000000</v>
+      </c>
       <c r="V287" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -46563,7 +46565,9 @@
       <c r="AF287" t="n">
         <v>3252000000</v>
       </c>
-      <c r="AG287" t="inlineStr"/>
+      <c r="AG287" t="n">
+        <v>2992000000</v>
+      </c>
       <c r="AH287" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -46594,13 +46598,13 @@
         </is>
       </c>
       <c r="AQ287" t="n">
-        <v>0.8167619578859294</v>
+        <v>0.8276775309862636</v>
       </c>
       <c r="AR287" t="n">
         <v>0.828</v>
       </c>
       <c r="AS287" t="n">
-        <v>0.8167619578859294</v>
+        <v>0.8276775309862636</v>
       </c>
       <c r="AT287" t="inlineStr">
         <is>
@@ -47814,11 +47818,11 @@
         <v>4863000000</v>
       </c>
       <c r="I295" t="n">
-        <v>4863766000</v>
+        <v>4863553000</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K295" t="n">
@@ -47852,11 +47856,11 @@
         <v>166000000</v>
       </c>
       <c r="U295" t="n">
-        <v>166053000</v>
+        <v>59325000</v>
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W295" t="n">
@@ -47890,11 +47894,11 @@
         <v>108000000</v>
       </c>
       <c r="AG295" t="n">
-        <v>108774000</v>
+        <v>34847000</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI295" t="n">
@@ -47922,13 +47926,13 @@
         </is>
       </c>
       <c r="AQ295" t="n">
-        <v>0.8311309442072088</v>
+        <v>0.8766014621307782</v>
       </c>
       <c r="AR295" t="n">
         <v>0.877</v>
       </c>
       <c r="AS295" t="n">
-        <v>0.8311309442072088</v>
+        <v>0.8766014621307782</v>
       </c>
       <c r="AT295" t="inlineStr">
         <is>
@@ -48146,11 +48150,11 @@
         <v>55952000000</v>
       </c>
       <c r="I297" t="n">
-        <v>55952804000</v>
+        <v>58922469000</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K297" t="n">
@@ -48184,11 +48188,11 @@
         <v>1242000000</v>
       </c>
       <c r="U297" t="n">
-        <v>1242400000</v>
+        <v>1468544000</v>
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W297" t="n">
@@ -48222,11 +48226,11 @@
         <v>865000000</v>
       </c>
       <c r="AG297" t="n">
-        <v>865914000</v>
+        <v>1031264000</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI297" t="n">
@@ -48254,13 +48258,13 @@
         </is>
       </c>
       <c r="AQ297" t="n">
-        <v>0.3303178148906977</v>
+        <v>0.3396123172545712</v>
       </c>
       <c r="AR297" t="n">
         <v>0.34</v>
       </c>
       <c r="AS297" t="n">
-        <v>0.3303178148906977</v>
+        <v>0.3396123172545712</v>
       </c>
       <c r="AT297" t="inlineStr">
         <is>
@@ -52720,7 +52724,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ノバレーゼ</t>
+          <t>オンザページ</t>
         </is>
       </c>
       <c r="C325" t="b">
@@ -52741,7 +52745,9 @@
       <c r="H325" t="n">
         <v>19299000000</v>
       </c>
-      <c r="I325" t="inlineStr"/>
+      <c r="I325" t="n">
+        <v>22039886000</v>
+      </c>
       <c r="J325" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -52777,7 +52783,9 @@
       <c r="T325" t="n">
         <v>1337000000</v>
       </c>
-      <c r="U325" t="inlineStr"/>
+      <c r="U325" t="n">
+        <v>2247951000</v>
+      </c>
       <c r="V325" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -52813,7 +52821,9 @@
       <c r="AF325" t="n">
         <v>663000000</v>
       </c>
-      <c r="AG325" t="inlineStr"/>
+      <c r="AG325" t="n">
+        <v>1256581000</v>
+      </c>
       <c r="AH325" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -58516,11 +58526,11 @@
         <v>3642000000</v>
       </c>
       <c r="I360" t="n">
-        <v>3642692000</v>
+        <v>3501884000</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K360" t="n">
@@ -58554,11 +58564,11 @@
         <v>155000000</v>
       </c>
       <c r="U360" t="n">
-        <v>155242000</v>
+        <v>211817000</v>
       </c>
       <c r="V360" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W360" t="n">
@@ -58592,11 +58602,11 @@
         <v>111000000</v>
       </c>
       <c r="AG360" t="n">
-        <v>111115000</v>
+        <v>98819000</v>
       </c>
       <c r="AH360" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI360" t="n">
@@ -58624,13 +58634,13 @@
         </is>
       </c>
       <c r="AQ360" t="n">
-        <v>0.7054981761415569</v>
+        <v>0.7113536589213938</v>
       </c>
       <c r="AR360" t="n">
         <v>0.711</v>
       </c>
       <c r="AS360" t="n">
-        <v>0.7054981761415569</v>
+        <v>0.7113536589213938</v>
       </c>
       <c r="AT360" t="inlineStr">
         <is>
@@ -59506,11 +59516,11 @@
         <v>3474000000</v>
       </c>
       <c r="I366" t="n">
-        <v>3474071000</v>
+        <v>3491179000</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K366" t="n">
@@ -59544,11 +59554,11 @@
         <v>378000000</v>
       </c>
       <c r="U366" t="n">
-        <v>378879000</v>
+        <v>283417000</v>
       </c>
       <c r="V366" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W366" t="n">
@@ -59582,11 +59592,11 @@
         <v>229000000</v>
       </c>
       <c r="AG366" t="n">
-        <v>229849000</v>
+        <v>197144000</v>
       </c>
       <c r="AH366" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI366" t="n">
@@ -59614,13 +59624,13 @@
         </is>
       </c>
       <c r="AQ366" t="n">
-        <v>0.6513381539391669</v>
+        <v>0.7133956805389573</v>
       </c>
       <c r="AR366" t="n">
         <v>0.713</v>
       </c>
       <c r="AS366" t="n">
-        <v>0.6513381539391669</v>
+        <v>0.7133956805389573</v>
       </c>
       <c r="AT366" t="inlineStr">
         <is>
@@ -61326,11 +61336,11 @@
         <v>1559000000</v>
       </c>
       <c r="I377" t="n">
-        <v>1559020000</v>
+        <v>1755413000</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K377" t="n">
@@ -61364,11 +61374,11 @@
         <v>-267000000</v>
       </c>
       <c r="U377" t="n">
-        <v>-267075000</v>
+        <v>-33684000</v>
       </c>
       <c r="V377" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W377" t="n">
@@ -61402,11 +61412,11 @@
         <v>-629000000</v>
       </c>
       <c r="AG377" t="n">
-        <v>-629039000</v>
+        <v>-31658000</v>
       </c>
       <c r="AH377" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI377" t="n">
@@ -61434,13 +61444,13 @@
         </is>
       </c>
       <c r="AQ377" t="n">
-        <v>0.291860469639155</v>
+        <v>0.330034226868805</v>
       </c>
       <c r="AR377" t="n">
         <v>0.33</v>
       </c>
       <c r="AS377" t="n">
-        <v>0.291860469639155</v>
+        <v>0.330034226868805</v>
       </c>
       <c r="AT377" t="inlineStr">
         <is>
@@ -61492,11 +61502,11 @@
         <v>2120000000</v>
       </c>
       <c r="I378" t="n">
-        <v>2120772000</v>
+        <v>2280860000</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K378" t="n">
@@ -61530,11 +61540,11 @@
         <v>-382000000</v>
       </c>
       <c r="U378" t="n">
-        <v>-382641000</v>
+        <v>9169000</v>
       </c>
       <c r="V378" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W378" t="n">
@@ -61568,11 +61578,11 @@
         <v>-852000000</v>
       </c>
       <c r="AG378" t="n">
-        <v>-852052000</v>
+        <v>22550000</v>
       </c>
       <c r="AH378" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI378" t="n">
@@ -61600,13 +61610,13 @@
         </is>
       </c>
       <c r="AQ378" t="n">
-        <v>0.8537787002057914</v>
+        <v>0.8630595477582084</v>
       </c>
       <c r="AR378" t="n">
         <v>0.863</v>
       </c>
       <c r="AS378" t="n">
-        <v>0.8537787002057914</v>
+        <v>0.8630595477582084</v>
       </c>
       <c r="AT378" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>77143000</v>
+        <v>47257000</v>
       </c>
       <c r="T9" t="n">
         <v>47000000</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>42941000</v>
+        <v>13054000</v>
       </c>
       <c r="AF9" t="n">
         <v>13000000</v>
@@ -2358,11 +2358,11 @@
         <v>2367000000</v>
       </c>
       <c r="I12" t="n">
-        <v>2367523000</v>
+        <v>2759255000</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2396,11 +2396,11 @@
         <v>183000000</v>
       </c>
       <c r="U12" t="n">
-        <v>183253000</v>
+        <v>262144000</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W12" t="n">
@@ -2434,11 +2434,11 @@
         <v>130000000</v>
       </c>
       <c r="AG12" t="n">
-        <v>130952000</v>
+        <v>246937000</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI12" t="n">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.3197329682066608</v>
+        <v>0.3562170418162481</v>
       </c>
       <c r="AR12" t="n">
         <v>0.356</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.3197329682066608</v>
+        <v>0.3562170418162481</v>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
@@ -2524,11 +2524,11 @@
         <v>1232000000</v>
       </c>
       <c r="I13" t="n">
-        <v>1232218000</v>
+        <v>1464358000</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2562,11 +2562,11 @@
         <v>78000000</v>
       </c>
       <c r="U13" t="n">
-        <v>78065000</v>
+        <v>60109000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W13" t="n">
@@ -2600,11 +2600,11 @@
         <v>16000000</v>
       </c>
       <c r="AG13" t="n">
-        <v>16073000</v>
+        <v>42955000</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI13" t="n">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>0.795806359218719</v>
+        <v>0.8185342486627568</v>
       </c>
       <c r="AR13" t="n">
         <v>0.819</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.795806359218719</v>
+        <v>0.8185342486627568</v>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
@@ -2855,9 +2855,7 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="n">
-        <v>13781848000</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2893,9 +2891,7 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="n">
-        <v>755967000</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2931,9 +2927,7 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="n">
-        <v>454620000</v>
-      </c>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2964,13 +2958,13 @@
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="AR15" t="n">
         <v>0.512</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
@@ -3519,9 +3513,7 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="n">
-        <v>2006859000</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3557,9 +3549,7 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="n">
-        <v>123675000</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3595,9 +3585,7 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="n">
-        <v>32652000</v>
-      </c>
+      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3628,17 +3616,15 @@
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>0.785581548809497</v>
+        <v>0.785</v>
       </c>
       <c r="AR19" t="n">
         <v>0.785</v>
       </c>
-      <c r="AS19" t="n">
-        <v>0.785581548809497</v>
-      </c>
+      <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AU19" t="n">
@@ -11970,11 +11956,11 @@
         <v>982000000</v>
       </c>
       <c r="I71" t="n">
-        <v>982352000</v>
+        <v>530019000</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -12008,11 +11994,11 @@
         <v>49000000</v>
       </c>
       <c r="U71" t="n">
-        <v>49517000</v>
+        <v>-628704000</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W71" t="n">
@@ -12046,11 +12032,11 @@
         <v>56000000</v>
       </c>
       <c r="AG71" t="n">
-        <v>56471000</v>
+        <v>-721633000</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI71" t="n">
@@ -12078,13 +12064,13 @@
         </is>
       </c>
       <c r="AQ71" t="n">
-        <v>0.6386841861153104</v>
+        <v>0.3553555818565322</v>
       </c>
       <c r="AR71" t="n">
         <v>0.353</v>
       </c>
       <c r="AS71" t="n">
-        <v>0.6386841861153104</v>
+        <v>0.3553555818565322</v>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
@@ -12284,11 +12270,11 @@
         <v>19833000000</v>
       </c>
       <c r="I73" t="n">
-        <v>19833896000</v>
+        <v>24734767000</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -12322,11 +12308,11 @@
         <v>2292000000</v>
       </c>
       <c r="U73" t="n">
-        <v>2292588000</v>
+        <v>2365011000</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W73" t="n">
@@ -12360,11 +12346,11 @@
         <v>2025000000</v>
       </c>
       <c r="AG73" t="n">
-        <v>2025848000</v>
+        <v>2776461000</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI73" t="n">
@@ -12392,13 +12378,13 @@
         </is>
       </c>
       <c r="AQ73" t="n">
-        <v>0.298593998450731</v>
+        <v>0.3150464298412788</v>
       </c>
       <c r="AR73" t="n">
         <v>0.315</v>
       </c>
       <c r="AS73" t="n">
-        <v>0.298593998450731</v>
+        <v>0.3150464298412788</v>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
@@ -16982,7 +16968,7 @@
       </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>1208065000</v>
+        <v>1374194000</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -17018,7 +17004,7 @@
       </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="n">
-        <v>183154000</v>
+        <v>260404000</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -17054,7 +17040,7 @@
       </c>
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="n">
-        <v>122319000</v>
+        <v>176706000</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17086,13 +17072,13 @@
         </is>
       </c>
       <c r="AQ102" t="n">
-        <v>0.7065623750183946</v>
+        <v>0.7525316296383453</v>
       </c>
       <c r="AR102" t="n">
         <v>0.753</v>
       </c>
       <c r="AS102" t="n">
-        <v>0.7065623750183946</v>
+        <v>0.7525316296383453</v>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
@@ -17454,7 +17440,7 @@
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>648942000</v>
+        <v>851943000</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -17490,7 +17476,7 @@
       </c>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="n">
-        <v>76528000</v>
+        <v>144139000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -17526,7 +17512,7 @@
       </c>
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="n">
-        <v>78513000</v>
+        <v>155917000</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17558,13 +17544,13 @@
         </is>
       </c>
       <c r="AQ105" t="n">
-        <v>0.3619898689169361</v>
+        <v>0.6332692724648876</v>
       </c>
       <c r="AR105" t="n">
         <v>0.629</v>
       </c>
       <c r="AS105" t="n">
-        <v>0.3619898689169361</v>
+        <v>0.6332692724648876</v>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
@@ -21602,13 +21588,13 @@
         </is>
       </c>
       <c r="AU131" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="AV131" t="n">
         <v>5529204</v>
       </c>
       <c r="AW131" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
@@ -25114,11 +25100,11 @@
         <v>19166000000</v>
       </c>
       <c r="I154" t="n">
-        <v>19166906000</v>
+        <v>20878460000</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K154" t="n">
@@ -25152,11 +25138,11 @@
         <v>2007000000</v>
       </c>
       <c r="U154" t="n">
-        <v>2007379000</v>
+        <v>2201676000</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W154" t="n">
@@ -25190,11 +25176,11 @@
         <v>1439000000</v>
       </c>
       <c r="AG154" t="n">
-        <v>1439468000</v>
+        <v>1501810000</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI154" t="n">
@@ -25222,13 +25208,13 @@
         </is>
       </c>
       <c r="AQ154" t="n">
-        <v>0.5237735417481867</v>
+        <v>0.5907661246570368</v>
       </c>
       <c r="AR154" t="n">
         <v>0.591</v>
       </c>
       <c r="AS154" t="n">
-        <v>0.5237735417481867</v>
+        <v>0.5907661246570368</v>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
@@ -25280,11 +25266,11 @@
         <v>2762000000</v>
       </c>
       <c r="I155" t="n">
-        <v>2762014000</v>
+        <v>3256436000</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -25318,11 +25304,11 @@
         <v>479000000</v>
       </c>
       <c r="U155" t="n">
-        <v>479696000</v>
+        <v>774393000</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W155" t="n">
@@ -25356,11 +25342,11 @@
         <v>320000000</v>
       </c>
       <c r="AG155" t="n">
-        <v>320759000</v>
+        <v>542126000</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI155" t="n">
@@ -25388,13 +25374,13 @@
         </is>
       </c>
       <c r="AQ155" t="n">
-        <v>0.1734600969463768</v>
+        <v>0.1519360702847296</v>
       </c>
       <c r="AR155" t="n">
         <v>0.15</v>
       </c>
       <c r="AS155" t="n">
-        <v>0.1734600969463768</v>
+        <v>0.1519360702847296</v>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
@@ -25446,11 +25432,11 @@
         <v>15049000000</v>
       </c>
       <c r="I156" t="n">
-        <v>15049858000</v>
+        <v>19029026000</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -25484,11 +25470,11 @@
         <v>-580000000</v>
       </c>
       <c r="U156" t="n">
-        <v>-580565000</v>
+        <v>-81587000</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W156" t="n">
@@ -25518,11 +25504,11 @@
         <v>-1552000000</v>
       </c>
       <c r="AG156" t="n">
-        <v>-1552485000</v>
+        <v>437887000</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI156" t="n">
@@ -25546,13 +25532,13 @@
         </is>
       </c>
       <c r="AQ156" t="n">
-        <v>0.7753032972254301</v>
+        <v>0.7531319473571764</v>
       </c>
       <c r="AR156" t="n">
         <v>0.75</v>
       </c>
       <c r="AS156" t="n">
-        <v>0.7753032972254301</v>
+        <v>0.7531319473571764</v>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
@@ -25766,11 +25752,11 @@
         <v>5401000000</v>
       </c>
       <c r="I158" t="n">
-        <v>5401367000</v>
+        <v>7576830000</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K158" t="n">
@@ -25804,11 +25790,11 @@
         <v>1296000000</v>
       </c>
       <c r="U158" t="n">
-        <v>1296146000</v>
+        <v>2128207000</v>
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W158" t="n">
@@ -25842,11 +25828,11 @@
         <v>923000000</v>
       </c>
       <c r="AG158" t="n">
-        <v>923371000</v>
+        <v>1500577000</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI158" t="n">
@@ -25874,13 +25860,13 @@
         </is>
       </c>
       <c r="AQ158" t="n">
-        <v>0.7053611762362547</v>
+        <v>0.6918072187900749</v>
       </c>
       <c r="AR158" t="n">
         <v>0.6909999999999999</v>
       </c>
       <c r="AS158" t="n">
-        <v>0.7053611762362547</v>
+        <v>0.6918072187900749</v>
       </c>
       <c r="AT158" t="inlineStr">
         <is>
@@ -28364,14 +28350,16 @@
         <v>1</v>
       </c>
       <c r="E175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
         <v>2</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
+      <c r="I175" t="n">
+        <v>7188192000</v>
+      </c>
       <c r="J175" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -28403,7 +28391,9 @@
       </c>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
-      <c r="U175" t="inlineStr"/>
+      <c r="U175" t="n">
+        <v>349230000</v>
+      </c>
       <c r="V175" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -28435,7 +28425,9 @@
       </c>
       <c r="AE175" t="inlineStr"/>
       <c r="AF175" t="inlineStr"/>
-      <c r="AG175" t="inlineStr"/>
+      <c r="AG175" t="n">
+        <v>739290000</v>
+      </c>
       <c r="AH175" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -28466,15 +28458,17 @@
         </is>
       </c>
       <c r="AQ175" t="n">
-        <v>0.677</v>
+        <v>0.6765962050891405</v>
       </c>
       <c r="AR175" t="n">
         <v>0.677</v>
       </c>
-      <c r="AS175" t="inlineStr"/>
+      <c r="AS175" t="n">
+        <v>0.6765962050891405</v>
+      </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="AU175" t="n">
@@ -28483,10 +28477,12 @@
       <c r="AV175" t="n">
         <v>16927750</v>
       </c>
-      <c r="AW175" t="inlineStr"/>
+      <c r="AW175" t="n">
+        <v>16927750</v>
+      </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>
@@ -29408,11 +29404,11 @@
         <v>5033000000</v>
       </c>
       <c r="I182" t="n">
-        <v>5033855000</v>
+        <v>5654084000</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -29446,11 +29442,11 @@
         <v>773000000</v>
       </c>
       <c r="U182" t="n">
-        <v>773510000</v>
+        <v>974658000</v>
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W182" t="n">
@@ -29484,11 +29480,11 @@
         <v>551000000</v>
       </c>
       <c r="AG182" t="n">
-        <v>551343000</v>
+        <v>757535000</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI182" t="n">
@@ -29516,13 +29512,13 @@
         </is>
       </c>
       <c r="AQ182" t="n">
-        <v>0.4880918098393903</v>
+        <v>0.5489935402691197</v>
       </c>
       <c r="AR182" t="n">
         <v>0.549</v>
       </c>
       <c r="AS182" t="n">
-        <v>0.4880918098393903</v>
+        <v>0.5489935402691197</v>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
@@ -30176,11 +30172,11 @@
         <v>54000000</v>
       </c>
       <c r="I187" t="n">
-        <v>54446000</v>
+        <v>230999000</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -30214,11 +30210,11 @@
         <v>-896000000</v>
       </c>
       <c r="U187" t="n">
-        <v>-896133000</v>
+        <v>-828179000</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W187" t="n">
@@ -30252,11 +30248,11 @@
         <v>-872000000</v>
       </c>
       <c r="AG187" t="n">
-        <v>-872238000</v>
+        <v>-763843000</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI187" t="n">
@@ -30284,13 +30280,13 @@
         </is>
       </c>
       <c r="AQ187" t="n">
-        <v>0.7226845586456627</v>
+        <v>0.6464156571010116</v>
       </c>
       <c r="AR187" t="n">
         <v>0.623</v>
       </c>
       <c r="AS187" t="n">
-        <v>0.7226845586456627</v>
+        <v>0.6464156571010116</v>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
@@ -35392,11 +35388,11 @@
         <v>1429000000</v>
       </c>
       <c r="I219" t="n">
-        <v>1429196000</v>
+        <v>980881000</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K219" t="n">
@@ -35430,11 +35426,11 @@
         <v>-281000000</v>
       </c>
       <c r="U219" t="n">
-        <v>-281826000</v>
+        <v>-390793000</v>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W219" t="n">
@@ -35468,11 +35464,11 @@
         <v>-585000000</v>
       </c>
       <c r="AG219" t="n">
-        <v>-585573000</v>
+        <v>-336159000</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI219" t="n">
@@ -35500,13 +35496,13 @@
         </is>
       </c>
       <c r="AQ219" t="n">
-        <v>0.8320886687528397</v>
+        <v>0.8649528203570179</v>
       </c>
       <c r="AR219" t="n">
         <v>0.865</v>
       </c>
       <c r="AS219" t="n">
-        <v>0.8320886687528397</v>
+        <v>0.8649528203570179</v>
       </c>
       <c r="AT219" t="inlineStr">
         <is>
@@ -35558,11 +35554,11 @@
         <v>1036000000</v>
       </c>
       <c r="I220" t="n">
-        <v>1036268000</v>
+        <v>965730000</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K220" t="n">
@@ -35596,11 +35592,11 @@
         <v>32000000</v>
       </c>
       <c r="U220" t="n">
-        <v>32315000</v>
+        <v>-51579000</v>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W220" t="n">
@@ -35634,11 +35630,11 @@
         <v>27000000</v>
       </c>
       <c r="AG220" t="n">
-        <v>27018000</v>
+        <v>-68010000</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI220" t="n">
@@ -35666,13 +35662,13 @@
         </is>
       </c>
       <c r="AQ220" t="n">
-        <v>0.697676935020785</v>
+        <v>0.5509097333437346</v>
       </c>
       <c r="AR220" t="n">
         <v>0.551</v>
       </c>
       <c r="AS220" t="n">
-        <v>0.697676935020785</v>
+        <v>0.5509097333437346</v>
       </c>
       <c r="AT220" t="inlineStr">
         <is>
@@ -38686,7 +38682,7 @@
       </c>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>5440231000</v>
+        <v>8191248000</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -38722,7 +38718,7 @@
       </c>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="n">
-        <v>552984000</v>
+        <v>1311447000</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -38758,7 +38754,7 @@
       </c>
       <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="n">
-        <v>378207000</v>
+        <v>981647000</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -38790,13 +38786,13 @@
         </is>
       </c>
       <c r="AQ239" t="n">
-        <v>0.3439893842518459</v>
+        <v>0.3832703749954613</v>
       </c>
       <c r="AR239" t="n">
         <v>0.383</v>
       </c>
       <c r="AS239" t="n">
-        <v>0.3439893842518459</v>
+        <v>0.3832703749954613</v>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
@@ -40668,11 +40664,11 @@
         <v>1707000000</v>
       </c>
       <c r="I251" t="n">
-        <v>1707072000</v>
+        <v>2369766000</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K251" t="n">
@@ -40706,11 +40702,11 @@
         <v>181000000</v>
       </c>
       <c r="U251" t="n">
-        <v>181754000</v>
+        <v>292176000</v>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W251" t="n">
@@ -40744,11 +40740,11 @@
         <v>465000000</v>
       </c>
       <c r="AG251" t="n">
-        <v>465191000</v>
+        <v>202143000</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI251" t="n">
@@ -40776,13 +40772,13 @@
         </is>
       </c>
       <c r="AQ251" t="n">
-        <v>0.5718403412853746</v>
+        <v>0.5913687594868079</v>
       </c>
       <c r="AR251" t="n">
         <v>0.573</v>
       </c>
       <c r="AS251" t="n">
-        <v>0.5718403412853746</v>
+        <v>0.5913687594868079</v>
       </c>
       <c r="AT251" t="inlineStr">
         <is>
@@ -41166,11 +41162,11 @@
         <v>1241000000</v>
       </c>
       <c r="I254" t="n">
-        <v>1241485000</v>
+        <v>1672557000</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K254" t="n">
@@ -41204,11 +41200,11 @@
         <v>189000000</v>
       </c>
       <c r="U254" t="n">
-        <v>189354000</v>
+        <v>274218000</v>
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W254" t="n">
@@ -41242,11 +41238,11 @@
         <v>116000000</v>
       </c>
       <c r="AG254" t="n">
-        <v>116012000</v>
+        <v>174313000</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI254" t="n">
@@ -41274,13 +41270,13 @@
         </is>
       </c>
       <c r="AQ254" t="n">
-        <v>0.4479885658509377</v>
+        <v>0.5263234868230524</v>
       </c>
       <c r="AR254" t="n">
         <v>0.526</v>
       </c>
       <c r="AS254" t="n">
-        <v>0.4479885658509377</v>
+        <v>0.5263234868230524</v>
       </c>
       <c r="AT254" t="inlineStr">
         <is>
@@ -41498,11 +41494,11 @@
         <v>1223000000</v>
       </c>
       <c r="I256" t="n">
-        <v>1223237000</v>
+        <v>1051466000</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K256" t="n">
@@ -41536,11 +41532,11 @@
         <v>-398000000</v>
       </c>
       <c r="U256" t="n">
-        <v>-398416000</v>
+        <v>-548051000</v>
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W256" t="n">
@@ -41574,11 +41570,11 @@
         <v>-394000000</v>
       </c>
       <c r="AG256" t="n">
-        <v>-394719000</v>
+        <v>-635461000</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI256" t="n">
@@ -41606,13 +41602,13 @@
         </is>
       </c>
       <c r="AQ256" t="n">
-        <v>0.4716543865214795</v>
+        <v>0.1463296744973883</v>
       </c>
       <c r="AR256" t="n">
         <v>0.144</v>
       </c>
       <c r="AS256" t="n">
-        <v>0.4716543865214795</v>
+        <v>0.1463296744973883</v>
       </c>
       <c r="AT256" t="inlineStr">
         <is>
@@ -41824,17 +41820,17 @@
         <v>9</v>
       </c>
       <c r="G258" t="n">
-        <v>1016159000</v>
+        <v>1021678000</v>
       </c>
       <c r="H258" t="n">
         <v>1016000000</v>
       </c>
       <c r="I258" t="n">
-        <v>1016159000</v>
+        <v>1027929000</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K258" t="n">
@@ -41862,17 +41858,17 @@
         </is>
       </c>
       <c r="S258" t="n">
-        <v>-161330000</v>
+        <v>-155811000</v>
       </c>
       <c r="T258" t="n">
         <v>-161000000</v>
       </c>
       <c r="U258" t="n">
-        <v>-161330000</v>
+        <v>-7222000</v>
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W258" t="n">
@@ -41906,11 +41902,11 @@
         <v>-163000000</v>
       </c>
       <c r="AG258" t="n">
-        <v>-163866000</v>
+        <v>-4146000</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI258" t="n">
@@ -41938,13 +41934,13 @@
         </is>
       </c>
       <c r="AQ258" t="n">
-        <v>0.3317141553106866</v>
+        <v>0.3434100882746375</v>
       </c>
       <c r="AR258" t="n">
         <v>0.343</v>
       </c>
       <c r="AS258" t="n">
-        <v>0.3317141553106866</v>
+        <v>0.3434100882746375</v>
       </c>
       <c r="AT258" t="inlineStr">
         <is>
@@ -41996,11 +41992,11 @@
         <v>5465000000</v>
       </c>
       <c r="I259" t="n">
-        <v>5465135000</v>
+        <v>6730288000</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K259" t="n">
@@ -42030,11 +42026,11 @@
         <v>-677000000</v>
       </c>
       <c r="U259" t="n">
-        <v>-677970000</v>
+        <v>-105746000</v>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W259" t="n">
@@ -42064,11 +42060,11 @@
         <v>-703000000</v>
       </c>
       <c r="AG259" t="n">
-        <v>-703266000</v>
+        <v>-152532000</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI259" t="n">
@@ -42092,13 +42088,13 @@
         </is>
       </c>
       <c r="AQ259" t="n">
-        <v>0.2029155730120664</v>
+        <v>0.1412890307255778</v>
       </c>
       <c r="AR259" t="n">
         <v>0.136</v>
       </c>
       <c r="AS259" t="n">
-        <v>0.2029155730120664</v>
+        <v>0.1412890307255778</v>
       </c>
       <c r="AT259" t="inlineStr">
         <is>
@@ -42150,11 +42146,11 @@
         <v>1333000000</v>
       </c>
       <c r="I260" t="n">
-        <v>1333059000</v>
+        <v>1078086000</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K260" t="n">
@@ -42188,11 +42184,11 @@
         <v>157000000</v>
       </c>
       <c r="U260" t="n">
-        <v>157518000</v>
+        <v>-33938000</v>
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W260" t="n">
@@ -42226,11 +42222,11 @@
         <v>101000000</v>
       </c>
       <c r="AG260" t="n">
-        <v>101004000</v>
+        <v>-23005000</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI260" t="n">
@@ -42258,13 +42254,13 @@
         </is>
       </c>
       <c r="AQ260" t="n">
-        <v>0.8961136328590951</v>
+        <v>0.9208588768642348</v>
       </c>
       <c r="AR260" t="n">
         <v>0.921</v>
       </c>
       <c r="AS260" t="n">
-        <v>0.8961136328590951</v>
+        <v>0.9208588768642348</v>
       </c>
       <c r="AT260" t="inlineStr">
         <is>
@@ -45436,13 +45432,13 @@
         </is>
       </c>
       <c r="AQ280" t="n">
-        <v>0.4712383111362992</v>
+        <v>0.4228619988154405</v>
       </c>
       <c r="AR280" t="n">
         <v>0.456</v>
       </c>
       <c r="AS280" t="n">
-        <v>0.4712383111362992</v>
+        <v>0.4228619988154405</v>
       </c>
       <c r="AT280" t="inlineStr">
         <is>
@@ -50129,9 +50125,7 @@
       <c r="H309" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I309" t="n">
-        <v>13007061000</v>
-      </c>
+      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -50167,9 +50161,7 @@
       <c r="T309" t="n">
         <v>147000000</v>
       </c>
-      <c r="U309" t="n">
-        <v>472174000</v>
-      </c>
+      <c r="U309" t="inlineStr"/>
       <c r="V309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -50205,9 +50197,7 @@
       <c r="AF309" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG309" t="n">
-        <v>168261000</v>
-      </c>
+      <c r="AG309" t="inlineStr"/>
       <c r="AH309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -50238,17 +50228,15 @@
         </is>
       </c>
       <c r="AQ309" t="n">
-        <v>0.3313848937891653</v>
+        <v>0.331</v>
       </c>
       <c r="AR309" t="n">
         <v>0.331</v>
       </c>
-      <c r="AS309" t="n">
-        <v>0.3313848937891653</v>
-      </c>
+      <c r="AS309" t="inlineStr"/>
       <c r="AT309" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AU309" t="n">
@@ -52579,9 +52567,7 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="n">
-        <v>3925672000</v>
-      </c>
+      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -52617,9 +52603,7 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="n">
-        <v>351613000</v>
-      </c>
+      <c r="U324" t="inlineStr"/>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -52655,9 +52639,7 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="n">
-        <v>173070000</v>
-      </c>
+      <c r="AG324" t="inlineStr"/>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -52688,17 +52670,15 @@
         </is>
       </c>
       <c r="AQ324" t="n">
-        <v>0.6076252752798235</v>
+        <v>0.608</v>
       </c>
       <c r="AR324" t="n">
         <v>0.608</v>
       </c>
-      <c r="AS324" t="n">
-        <v>0.6076252752798235</v>
-      </c>
+      <c r="AS324" t="inlineStr"/>
       <c r="AT324" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AU324" t="n">
@@ -53884,11 +53864,11 @@
         <v>5130000000</v>
       </c>
       <c r="I332" t="n">
-        <v>5130876000</v>
+        <v>11937987000</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K332" t="n">
@@ -53916,17 +53896,17 @@
         </is>
       </c>
       <c r="S332" t="n">
-        <v>1432421000</v>
+        <v>1328867000</v>
       </c>
       <c r="T332" t="n">
         <v>1432000000</v>
       </c>
       <c r="U332" t="n">
-        <v>1432421000</v>
+        <v>2309489000</v>
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W332" t="n">
@@ -53954,17 +53934,17 @@
         </is>
       </c>
       <c r="AE332" t="n">
-        <v>905735000</v>
+        <v>838000000</v>
       </c>
       <c r="AF332" t="n">
         <v>905000000</v>
       </c>
       <c r="AG332" t="n">
-        <v>905735000</v>
+        <v>1450235000</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI332" t="n">
@@ -53992,13 +53972,13 @@
         </is>
       </c>
       <c r="AQ332" t="n">
-        <v>0.3093437994917297</v>
+        <v>0.2851680938675751</v>
       </c>
       <c r="AR332" t="n">
         <v>0.282</v>
       </c>
       <c r="AS332" t="n">
-        <v>0.3093437994917297</v>
+        <v>0.2851680938675751</v>
       </c>
       <c r="AT332" t="inlineStr">
         <is>
@@ -54216,11 +54196,11 @@
         <v>2043000000</v>
       </c>
       <c r="I334" t="n">
-        <v>2043110000</v>
+        <v>2689620000</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K334" t="n">
@@ -54254,11 +54234,11 @@
         <v>180000000</v>
       </c>
       <c r="U334" t="n">
-        <v>180995000</v>
+        <v>203394000</v>
       </c>
       <c r="V334" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W334" t="n">
@@ -54292,11 +54272,11 @@
         <v>145000000</v>
       </c>
       <c r="AG334" t="n">
-        <v>145734000</v>
+        <v>127711000</v>
       </c>
       <c r="AH334" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI334" t="n">
@@ -54324,13 +54304,13 @@
         </is>
       </c>
       <c r="AQ334" t="n">
-        <v>0.6823108902761743</v>
+        <v>0.574489252377356</v>
       </c>
       <c r="AR334" t="n">
         <v>0.572</v>
       </c>
       <c r="AS334" t="n">
-        <v>0.6823108902761743</v>
+        <v>0.574489252377356</v>
       </c>
       <c r="AT334" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -729,12 +729,16 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>113000000</v>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -2855,7 +2859,9 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2891,7 +2897,9 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2927,7 +2935,9 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2958,13 +2968,13 @@
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="AR15" t="n">
         <v>0.512</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
@@ -3513,7 +3523,9 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2006859000</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3549,7 +3561,9 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>123675000</v>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3585,7 +3599,9 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>32652000</v>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3616,15 +3632,17 @@
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>0.785</v>
+        <v>0.785581548809497</v>
       </c>
       <c r="AR19" t="n">
         <v>0.785</v>
       </c>
-      <c r="AS19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>0.785581548809497</v>
+      </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="AU19" t="n">
@@ -10936,13 +10954,13 @@
         </is>
       </c>
       <c r="AU64" t="n">
-        <v>226264699</v>
+        <v>226070899</v>
       </c>
       <c r="AV64" t="n">
         <v>230375000</v>
       </c>
       <c r="AW64" t="n">
-        <v>226264699</v>
+        <v>226070899</v>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
@@ -15848,11 +15866,11 @@
         <v>11051000000</v>
       </c>
       <c r="I95" t="n">
-        <v>11051000000</v>
+        <v>14961000000</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -15886,11 +15904,11 @@
         <v>1517000000</v>
       </c>
       <c r="U95" t="n">
-        <v>1517000000</v>
+        <v>1432000000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W95" t="n">
@@ -15920,11 +15938,11 @@
         <v>901000000</v>
       </c>
       <c r="AG95" t="n">
-        <v>901000000</v>
+        <v>3091000000</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI95" t="n">
@@ -15948,13 +15966,13 @@
         </is>
       </c>
       <c r="AQ95" t="n">
-        <v>0.2531136481577582</v>
+        <v>0.2955297476156492</v>
       </c>
       <c r="AR95" t="n">
         <v>0.296</v>
       </c>
       <c r="AS95" t="n">
-        <v>0.2531136481577582</v>
+        <v>0.2955297476156492</v>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
@@ -21588,13 +21606,13 @@
         </is>
       </c>
       <c r="AU131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="AV131" t="n">
         <v>5529204</v>
       </c>
       <c r="AW131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
@@ -24015,7 +24033,9 @@
       <c r="H147" t="n">
         <v>6247000000</v>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="n">
+        <v>6840816000</v>
+      </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -24051,7 +24071,9 @@
       <c r="T147" t="n">
         <v>305000000</v>
       </c>
-      <c r="U147" t="inlineStr"/>
+      <c r="U147" t="n">
+        <v>326123000</v>
+      </c>
       <c r="V147" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -24087,7 +24109,9 @@
       <c r="AF147" t="n">
         <v>240000000</v>
       </c>
-      <c r="AG147" t="inlineStr"/>
+      <c r="AG147" t="n">
+        <v>187586000</v>
+      </c>
       <c r="AH147" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -24118,13 +24142,13 @@
         </is>
       </c>
       <c r="AQ147" t="n">
-        <v>0.3387992697287009</v>
+        <v>0.5566310824112335</v>
       </c>
       <c r="AR147" t="n">
         <v>0.5570000000000001</v>
       </c>
       <c r="AS147" t="n">
-        <v>0.3387992697287009</v>
+        <v>0.5566310824112335</v>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
@@ -33925,12 +33949,16 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
+      <c r="O210" t="n">
+        <v>3990000000</v>
+      </c>
+      <c r="P210" t="n">
+        <v>3990000000</v>
+      </c>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S210" t="n">
@@ -45988,11 +46016,11 @@
         <v>32069000000</v>
       </c>
       <c r="I284" t="n">
-        <v>32069000000</v>
+        <v>34322000000</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K284" t="n">
@@ -46026,11 +46054,11 @@
         <v>4030000000</v>
       </c>
       <c r="U284" t="n">
-        <v>4031000000</v>
+        <v>4531000000</v>
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W284" t="n">
@@ -46064,11 +46092,11 @@
         <v>3336000000</v>
       </c>
       <c r="AG284" t="n">
-        <v>3336000000</v>
+        <v>3455000000</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI284" t="n">
@@ -46096,13 +46124,13 @@
         </is>
       </c>
       <c r="AQ284" t="n">
-        <v>0.6989601588970674</v>
+        <v>0.6658505716123411</v>
       </c>
       <c r="AR284" t="n">
         <v>0.666</v>
       </c>
       <c r="AS284" t="n">
-        <v>0.6989601588970674</v>
+        <v>0.6658505716123411</v>
       </c>
       <c r="AT284" t="inlineStr">
         <is>
@@ -46110,13 +46138,13 @@
         </is>
       </c>
       <c r="AU284" t="n">
-        <v>20418300</v>
+        <v>19536000</v>
       </c>
       <c r="AV284" t="n">
         <v>20500000</v>
       </c>
       <c r="AW284" t="n">
-        <v>20418300</v>
+        <v>19536000</v>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
@@ -50125,7 +50153,9 @@
       <c r="H309" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I309" t="inlineStr"/>
+      <c r="I309" t="n">
+        <v>13007061000</v>
+      </c>
       <c r="J309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -50161,7 +50191,9 @@
       <c r="T309" t="n">
         <v>147000000</v>
       </c>
-      <c r="U309" t="inlineStr"/>
+      <c r="U309" t="n">
+        <v>472174000</v>
+      </c>
       <c r="V309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -50197,7 +50229,9 @@
       <c r="AF309" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG309" t="inlineStr"/>
+      <c r="AG309" t="n">
+        <v>168261000</v>
+      </c>
       <c r="AH309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -50228,15 +50262,17 @@
         </is>
       </c>
       <c r="AQ309" t="n">
-        <v>0.331</v>
+        <v>0.3313848937891653</v>
       </c>
       <c r="AR309" t="n">
         <v>0.331</v>
       </c>
-      <c r="AS309" t="inlineStr"/>
+      <c r="AS309" t="n">
+        <v>0.3313848937891653</v>
+      </c>
       <c r="AT309" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="AU309" t="n">
@@ -52567,7 +52603,9 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="n">
+        <v>3925672000</v>
+      </c>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -52603,7 +52641,9 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="inlineStr"/>
+      <c r="U324" t="n">
+        <v>351613000</v>
+      </c>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -52639,7 +52679,9 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="inlineStr"/>
+      <c r="AG324" t="n">
+        <v>173070000</v>
+      </c>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -52670,15 +52712,17 @@
         </is>
       </c>
       <c r="AQ324" t="n">
-        <v>0.608</v>
+        <v>0.6076252752798235</v>
       </c>
       <c r="AR324" t="n">
         <v>0.608</v>
       </c>
-      <c r="AS324" t="inlineStr"/>
+      <c r="AS324" t="n">
+        <v>0.6076252752798235</v>
+      </c>
       <c r="AT324" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="AU324" t="n">
@@ -52909,12 +52953,16 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="O326" t="inlineStr"/>
-      <c r="P326" t="inlineStr"/>
+      <c r="O326" t="n">
+        <v>17370000000</v>
+      </c>
+      <c r="P326" t="n">
+        <v>17370000000</v>
+      </c>
       <c r="Q326" t="inlineStr"/>
       <c r="R326" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="S326" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -4038,11 +4038,11 @@
         <v>1225000000</v>
       </c>
       <c r="I16" t="n">
-        <v>1225271000</v>
+        <v>1400716000</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -4076,11 +4076,11 @@
         <v>412000000</v>
       </c>
       <c r="U16" t="n">
-        <v>412666000</v>
+        <v>408098000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -4114,11 +4114,11 @@
         <v>276000000</v>
       </c>
       <c r="AG16" t="n">
-        <v>276298000</v>
+        <v>276442000</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI16" t="n">
@@ -4146,11 +4146,11 @@
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>769468000</v>
+        <v>994995000</v>
       </c>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
-        <v>769468000</v>
+        <v>994995000</v>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
@@ -4158,11 +4158,11 @@
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>217831000</v>
+        <v>295861000</v>
       </c>
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="n">
-        <v>217831000</v>
+        <v>295861000</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
@@ -4170,11 +4170,11 @@
         </is>
       </c>
       <c r="AY16" t="n">
-        <v>249960000</v>
+        <v>260372000</v>
       </c>
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="n">
-        <v>249960000</v>
+        <v>260372000</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>1487000000</v>
       </c>
       <c r="BE16" t="n">
-        <v>1733104000</v>
+        <v>1487072000</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>1656000000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1315535000</v>
+        <v>1656542000</v>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>0.6499495814594154</v>
+        <v>0.7591096577471443</v>
       </c>
       <c r="BL16" t="n">
         <v>0.759</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.6499495814594154</v>
+        <v>0.7591096577471443</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
@@ -45838,11 +45838,11 @@
         <v>4918000000</v>
       </c>
       <c r="I203" t="n">
-        <v>4918699000</v>
+        <v>4779287000</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K203" t="n">
@@ -45876,11 +45876,11 @@
         <v>78000000</v>
       </c>
       <c r="U203" t="n">
-        <v>78659000</v>
+        <v>36553000</v>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W203" t="n">
@@ -45914,11 +45914,11 @@
         <v>125000000</v>
       </c>
       <c r="AG203" t="n">
-        <v>125997000</v>
+        <v>-195091000</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI203" t="n">
@@ -45952,7 +45952,7 @@
         <v>4639000000</v>
       </c>
       <c r="AS203" t="n">
-        <v>4253916000</v>
+        <v>4639586000</v>
       </c>
       <c r="AT203" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>155000000</v>
       </c>
       <c r="AW203" t="n">
-        <v>184804000</v>
+        <v>155784000</v>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>147000000</v>
       </c>
       <c r="BA203" t="n">
-        <v>134705000</v>
+        <v>147031000</v>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>1419000000</v>
       </c>
       <c r="BE203" t="n">
-        <v>840288000</v>
+        <v>1419927000</v>
       </c>
       <c r="BF203" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>3079000000</v>
       </c>
       <c r="BI203" t="n">
-        <v>3286724000</v>
+        <v>3062173000</v>
       </c>
       <c r="BJ203" t="inlineStr">
         <is>
@@ -46016,13 +46016,13 @@
         </is>
       </c>
       <c r="BK203" t="n">
-        <v>0.6400743148370662</v>
+        <v>0.6398167076750266</v>
       </c>
       <c r="BL203" t="n">
         <v>0.64</v>
       </c>
       <c r="BM203" t="n">
-        <v>0.6400743148370662</v>
+        <v>0.6398167076750266</v>
       </c>
       <c r="BN203" t="inlineStr">
         <is>
@@ -74191,7 +74191,7 @@
         <v>1</v>
       </c>
       <c r="F325" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G325" t="n">
         <v>19299719000</v>
@@ -74220,10 +74220,10 @@
         </is>
       </c>
       <c r="O325" t="n">
-        <v>20505000000</v>
+        <v>42789000000</v>
       </c>
       <c r="P325" t="n">
-        <v>20505000000</v>
+        <v>42789000000</v>
       </c>
       <c r="Q325" t="inlineStr"/>
       <c r="R325" t="inlineStr">
@@ -74258,10 +74258,10 @@
         </is>
       </c>
       <c r="AA325" t="n">
-        <v>1878000000</v>
+        <v>3000000000</v>
       </c>
       <c r="AB325" t="n">
-        <v>1878000000</v>
+        <v>3000000000</v>
       </c>
       <c r="AC325" t="inlineStr"/>
       <c r="AD325" t="inlineStr">
@@ -74296,10 +74296,10 @@
         </is>
       </c>
       <c r="AM325" t="n">
-        <v>1008000000</v>
+        <v>1640000000</v>
       </c>
       <c r="AN325" t="n">
-        <v>1008000000</v>
+        <v>1640000000</v>
       </c>
       <c r="AO325" t="inlineStr"/>
       <c r="AP325" t="inlineStr">
@@ -85915,7 +85915,7 @@
         <v>1</v>
       </c>
       <c r="F375" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G375" t="n">
         <v>11211465000</v>
@@ -86119,7 +86119,7 @@
         <v>3964099</v>
       </c>
       <c r="BP375" t="n">
-        <v>4012600</v>
+        <v>4013400</v>
       </c>
       <c r="BQ375" t="n">
         <v>3964099</v>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -54983,12 +54983,10 @@
       <c r="H242" t="n">
         <v>1071000000</v>
       </c>
-      <c r="I242" t="n">
-        <v>1071954000</v>
-      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K242" t="n">
@@ -55021,12 +55019,10 @@
       <c r="T242" t="n">
         <v>152000000</v>
       </c>
-      <c r="U242" t="n">
-        <v>152739000</v>
-      </c>
+      <c r="U242" t="inlineStr"/>
       <c r="V242" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W242" t="n">
@@ -55059,12 +55055,10 @@
       <c r="AF242" t="n">
         <v>121000000</v>
       </c>
-      <c r="AG242" t="n">
-        <v>121697000</v>
-      </c>
+      <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI242" t="n">
@@ -55098,7 +55092,7 @@
         <v>790000000</v>
       </c>
       <c r="AS242" t="n">
-        <v>968521000</v>
+        <v>790384000</v>
       </c>
       <c r="AT242" t="inlineStr">
         <is>
@@ -55112,7 +55106,7 @@
         <v>70000000</v>
       </c>
       <c r="AW242" t="n">
-        <v>56404000</v>
+        <v>70347000</v>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
@@ -55126,7 +55120,7 @@
         <v>44000000</v>
       </c>
       <c r="BA242" t="n">
-        <v>150061000</v>
+        <v>44564000</v>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
@@ -66725,12 +66719,10 @@
       <c r="H293" t="n">
         <v>7012000000</v>
       </c>
-      <c r="I293" t="n">
-        <v>7012802000</v>
-      </c>
+      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K293" t="n">
@@ -66763,12 +66755,10 @@
       <c r="T293" t="n">
         <v>1083000000</v>
       </c>
-      <c r="U293" t="n">
-        <v>1083700000</v>
-      </c>
+      <c r="U293" t="inlineStr"/>
       <c r="V293" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W293" t="n">
@@ -66801,12 +66791,10 @@
       <c r="AF293" t="n">
         <v>785000000</v>
       </c>
-      <c r="AG293" t="n">
-        <v>785757000</v>
-      </c>
+      <c r="AG293" t="inlineStr"/>
       <c r="AH293" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI293" t="n">
@@ -66840,7 +66828,7 @@
         <v>6060000000</v>
       </c>
       <c r="AS293" t="n">
-        <v>5163136000</v>
+        <v>6060836000</v>
       </c>
       <c r="AT293" t="inlineStr">
         <is>
@@ -66854,7 +66842,7 @@
         <v>965000000</v>
       </c>
       <c r="AW293" t="n">
-        <v>841855000</v>
+        <v>965680000</v>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
@@ -66868,7 +66856,7 @@
         <v>695000000</v>
       </c>
       <c r="BA293" t="n">
-        <v>561349000</v>
+        <v>695339000</v>
       </c>
       <c r="BB293" t="inlineStr">
         <is>
@@ -68377,12 +68365,10 @@
       <c r="H300" t="n">
         <v>11167000000</v>
       </c>
-      <c r="I300" t="n">
-        <v>11167786000</v>
-      </c>
+      <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K300" t="n">
@@ -68415,12 +68401,10 @@
       <c r="T300" t="n">
         <v>629000000</v>
       </c>
-      <c r="U300" t="n">
-        <v>629967000</v>
-      </c>
+      <c r="U300" t="inlineStr"/>
       <c r="V300" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W300" t="n">
@@ -68453,12 +68437,10 @@
       <c r="AF300" t="n">
         <v>443000000</v>
       </c>
-      <c r="AG300" t="n">
-        <v>443764000</v>
-      </c>
+      <c r="AG300" t="inlineStr"/>
       <c r="AH300" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI300" t="n">
@@ -68492,7 +68474,7 @@
         <v>10407000000</v>
       </c>
       <c r="AS300" t="n">
-        <v>9093584000</v>
+        <v>10407282000</v>
       </c>
       <c r="AT300" t="inlineStr">
         <is>
@@ -68506,7 +68488,7 @@
         <v>659000000</v>
       </c>
       <c r="AW300" t="n">
-        <v>548967000</v>
+        <v>659809000</v>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
@@ -68520,7 +68502,7 @@
         <v>473000000</v>
       </c>
       <c r="BA300" t="n">
-        <v>343054000</v>
+        <v>473239000</v>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
@@ -78401,12 +78383,10 @@
       <c r="H343" t="n">
         <v>756000000</v>
       </c>
-      <c r="I343" t="n">
-        <v>756715000</v>
-      </c>
+      <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K343" t="n">
@@ -78439,12 +78419,10 @@
       <c r="T343" t="n">
         <v>-308000000</v>
       </c>
-      <c r="U343" t="n">
-        <v>-308416000</v>
-      </c>
+      <c r="U343" t="inlineStr"/>
       <c r="V343" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W343" t="n">
@@ -78477,12 +78455,10 @@
       <c r="AF343" t="n">
         <v>-326000000</v>
       </c>
-      <c r="AG343" t="n">
-        <v>-326733000</v>
-      </c>
+      <c r="AG343" t="inlineStr"/>
       <c r="AH343" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI343" t="n">
@@ -78510,11 +78486,11 @@
         </is>
       </c>
       <c r="AQ343" t="n">
-        <v>843801000</v>
+        <v>959399000</v>
       </c>
       <c r="AR343" t="inlineStr"/>
       <c r="AS343" t="n">
-        <v>843801000</v>
+        <v>959399000</v>
       </c>
       <c r="AT343" t="inlineStr">
         <is>
@@ -78522,11 +78498,11 @@
         </is>
       </c>
       <c r="AU343" t="n">
-        <v>-77912000</v>
+        <v>151239000</v>
       </c>
       <c r="AV343" t="inlineStr"/>
       <c r="AW343" t="n">
-        <v>-77912000</v>
+        <v>151239000</v>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
@@ -78534,11 +78510,11 @@
         </is>
       </c>
       <c r="AY343" t="n">
-        <v>-52911000</v>
+        <v>113307000</v>
       </c>
       <c r="AZ343" t="inlineStr"/>
       <c r="BA343" t="n">
-        <v>-52911000</v>
+        <v>113307000</v>
       </c>
       <c r="BB343" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -9703,12 +9703,10 @@
       <c r="H41" t="n">
         <v>6475000000</v>
       </c>
-      <c r="I41" t="n">
-        <v>6475088000</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -9741,12 +9739,10 @@
       <c r="T41" t="n">
         <v>637000000</v>
       </c>
-      <c r="U41" t="n">
-        <v>637497000</v>
-      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W41" t="n">
@@ -9779,12 +9775,10 @@
       <c r="AF41" t="n">
         <v>405000000</v>
       </c>
-      <c r="AG41" t="n">
-        <v>405173000</v>
-      </c>
+      <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI41" t="n">
@@ -9812,11 +9806,11 @@
         </is>
       </c>
       <c r="AQ41" t="n">
-        <v>4522655000</v>
+        <v>5659947000</v>
       </c>
       <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="n">
-        <v>4522655000</v>
+        <v>5659947000</v>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
@@ -9824,11 +9818,11 @@
         </is>
       </c>
       <c r="AU41" t="n">
-        <v>484620000</v>
+        <v>521344000</v>
       </c>
       <c r="AV41" t="inlineStr"/>
       <c r="AW41" t="n">
-        <v>484620000</v>
+        <v>521344000</v>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
@@ -9836,11 +9830,11 @@
         </is>
       </c>
       <c r="AY41" t="n">
-        <v>312915000</v>
+        <v>365879000</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
-        <v>312915000</v>
+        <v>365879000</v>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
@@ -10387,12 +10381,10 @@
       <c r="H44" t="n">
         <v>815000000</v>
       </c>
-      <c r="I44" t="n">
-        <v>815308000</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -10425,12 +10417,10 @@
       <c r="T44" t="n">
         <v>-440000000</v>
       </c>
-      <c r="U44" t="n">
-        <v>-440786000</v>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -10463,12 +10453,10 @@
       <c r="AF44" t="n">
         <v>-437000000</v>
       </c>
-      <c r="AG44" t="n">
-        <v>-437972000</v>
-      </c>
+      <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI44" t="n">
@@ -10496,11 +10484,11 @@
         </is>
       </c>
       <c r="AQ44" t="n">
-        <v>260461000</v>
+        <v>379604000</v>
       </c>
       <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="n">
-        <v>260461000</v>
+        <v>379604000</v>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
@@ -10508,11 +10496,11 @@
         </is>
       </c>
       <c r="AU44" t="n">
-        <v>-462888000</v>
+        <v>-630907000</v>
       </c>
       <c r="AV44" t="inlineStr"/>
       <c r="AW44" t="n">
-        <v>-462888000</v>
+        <v>-630907000</v>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
@@ -10520,11 +10508,11 @@
         </is>
       </c>
       <c r="AY44" t="n">
-        <v>-456073000</v>
+        <v>-641105000</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
-        <v>-456073000</v>
+        <v>-641105000</v>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
@@ -29279,12 +29267,10 @@
       <c r="H128" t="n">
         <v>1004000000</v>
       </c>
-      <c r="I128" t="n">
-        <v>1004611000</v>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -29317,12 +29303,10 @@
       <c r="T128" t="n">
         <v>73000000</v>
       </c>
-      <c r="U128" t="n">
-        <v>73262000</v>
-      </c>
+      <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W128" t="n">
@@ -29355,12 +29339,10 @@
       <c r="AF128" t="n">
         <v>48000000</v>
       </c>
-      <c r="AG128" t="n">
-        <v>48643000</v>
-      </c>
+      <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI128" t="n">
@@ -29394,7 +29376,7 @@
         <v>1053000000</v>
       </c>
       <c r="AS128" t="n">
-        <v>934255000</v>
+        <v>1053861000</v>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
@@ -29408,7 +29390,7 @@
         <v>163000000</v>
       </c>
       <c r="AW128" t="n">
-        <v>174042000</v>
+        <v>163246000</v>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
@@ -29422,7 +29404,7 @@
         <v>122000000</v>
       </c>
       <c r="BA128" t="n">
-        <v>141315000</v>
+        <v>122646000</v>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
@@ -47711,12 +47693,10 @@
       <c r="H211" t="n">
         <v>1464000000</v>
       </c>
-      <c r="I211" t="n">
-        <v>1464541000</v>
-      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K211" t="n">
@@ -47749,12 +47729,10 @@
       <c r="T211" t="n">
         <v>-223000000</v>
       </c>
-      <c r="U211" t="n">
-        <v>-223432000</v>
-      </c>
+      <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W211" t="n">
@@ -47787,12 +47765,10 @@
       <c r="AF211" t="n">
         <v>-200000000</v>
       </c>
-      <c r="AG211" t="n">
-        <v>-200744000</v>
-      </c>
+      <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI211" t="n">
@@ -47826,7 +47802,7 @@
         <v>1607000000</v>
       </c>
       <c r="AS211" t="n">
-        <v>1412575000</v>
+        <v>1607768000</v>
       </c>
       <c r="AT211" t="inlineStr">
         <is>
@@ -47840,7 +47816,7 @@
         <v>85000000</v>
       </c>
       <c r="AW211" t="n">
-        <v>65489000</v>
+        <v>85751000</v>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
@@ -47854,7 +47830,7 @@
         <v>102000000</v>
       </c>
       <c r="BA211" t="n">
-        <v>49010000</v>
+        <v>102170000</v>
       </c>
       <c r="BB211" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="BO7" t="n">
-        <v>2902600</v>
+        <v>2905200</v>
       </c>
       <c r="BP7" t="n">
         <v>2905200</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2902600</v>
+        <v>2905200</v>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
@@ -3807,9 +3807,7 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="n">
-        <v>13781848000</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3845,9 +3843,7 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="n">
-        <v>755967000</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3883,9 +3879,7 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="n">
-        <v>454620000</v>
-      </c>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3958,7 +3952,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2065504000</v>
+        <v>2038006000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3972,7 +3966,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2272296000</v>
+        <v>1895989000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3980,13 +3974,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4454,13 +4448,13 @@
         </is>
       </c>
       <c r="BO17" t="n">
-        <v>10237253</v>
+        <v>10269836</v>
       </c>
       <c r="BP17" t="n">
         <v>10637253</v>
       </c>
       <c r="BQ17" t="n">
-        <v>10237253</v>
+        <v>10269836</v>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
@@ -4727,9 +4721,7 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="n">
-        <v>2006859000</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4765,9 +4757,7 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="n">
-        <v>123675000</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4803,9 +4793,7 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="n">
-        <v>32652000</v>
-      </c>
+      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4883,9 +4871,7 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="n">
-        <v>1185144000</v>
-      </c>
+      <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4897,26 +4883,22 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="n">
-        <v>1430969000</v>
-      </c>
+      <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785581548809497</v>
+        <v>0.785</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="n">
-        <v>0.785581548809497</v>
-      </c>
+      <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -14194,13 +14176,13 @@
         </is>
       </c>
       <c r="BO60" t="n">
-        <v>11866000</v>
+        <v>11699800</v>
       </c>
       <c r="BP60" t="n">
         <v>11866000</v>
       </c>
       <c r="BQ60" t="n">
-        <v>11866000</v>
+        <v>11699800</v>
       </c>
       <c r="BR60" t="inlineStr">
         <is>
@@ -30066,13 +30048,13 @@
         </is>
       </c>
       <c r="BO131" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="BP131" t="n">
         <v>5529204</v>
       </c>
       <c r="BQ131" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="BR131" t="inlineStr">
         <is>
@@ -34808,13 +34790,13 @@
         </is>
       </c>
       <c r="BO152" t="n">
-        <v>7868000</v>
+        <v>8215200</v>
       </c>
       <c r="BP152" t="n">
         <v>8687000</v>
       </c>
       <c r="BQ152" t="n">
-        <v>7868000</v>
+        <v>8215200</v>
       </c>
       <c r="BR152" t="inlineStr">
         <is>
@@ -40572,13 +40554,13 @@
         </is>
       </c>
       <c r="BO179" t="n">
-        <v>10040000</v>
+        <v>10095000</v>
       </c>
       <c r="BP179" t="n">
         <v>10040000</v>
       </c>
       <c r="BQ179" t="n">
-        <v>10040000</v>
+        <v>10095000</v>
       </c>
       <c r="BR179" t="inlineStr">
         <is>
@@ -40796,13 +40778,13 @@
         </is>
       </c>
       <c r="BO180" t="n">
-        <v>4382560</v>
+        <v>4401200</v>
       </c>
       <c r="BP180" t="n">
         <v>4382560</v>
       </c>
       <c r="BQ180" t="n">
-        <v>4382560</v>
+        <v>4401200</v>
       </c>
       <c r="BR180" t="inlineStr">
         <is>
@@ -41020,13 +41002,13 @@
         </is>
       </c>
       <c r="BO181" t="n">
-        <v>6400000</v>
+        <v>6647500</v>
       </c>
       <c r="BP181" t="n">
         <v>6400000</v>
       </c>
       <c r="BQ181" t="n">
-        <v>6400000</v>
+        <v>6647500</v>
       </c>
       <c r="BR181" t="inlineStr">
         <is>
@@ -57730,13 +57712,13 @@
         </is>
       </c>
       <c r="BO253" t="n">
-        <v>16772743</v>
+        <v>16890743</v>
       </c>
       <c r="BP253" t="n">
         <v>16828800</v>
       </c>
       <c r="BQ253" t="n">
-        <v>16772743</v>
+        <v>16890743</v>
       </c>
       <c r="BR253" t="inlineStr">
         <is>
@@ -62906,13 +62888,13 @@
         </is>
       </c>
       <c r="BO276" t="n">
-        <v>5298400</v>
+        <v>5358673</v>
       </c>
       <c r="BP276" t="n">
         <v>6000000</v>
       </c>
       <c r="BQ276" t="n">
-        <v>5298400</v>
+        <v>5358673</v>
       </c>
       <c r="BR276" t="inlineStr">
         <is>
@@ -70447,9 +70429,7 @@
       <c r="H309" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I309" t="n">
-        <v>13007061000</v>
-      </c>
+      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70485,9 +70465,7 @@
       <c r="T309" t="n">
         <v>147000000</v>
       </c>
-      <c r="U309" t="n">
-        <v>472174000</v>
-      </c>
+      <c r="U309" t="inlineStr"/>
       <c r="V309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70523,9 +70501,7 @@
       <c r="AF309" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG309" t="n">
-        <v>168261000</v>
-      </c>
+      <c r="AG309" t="inlineStr"/>
       <c r="AH309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70603,9 +70579,7 @@
       <c r="BD309" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE309" t="n">
-        <v>754210000</v>
-      </c>
+      <c r="BE309" t="inlineStr"/>
       <c r="BF309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70617,26 +70591,22 @@
       <c r="BH309" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI309" t="n">
-        <v>2187588000</v>
-      </c>
+      <c r="BI309" t="inlineStr"/>
       <c r="BJ309" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK309" t="n">
-        <v>0.3313848937891653</v>
+        <v>0.331</v>
       </c>
       <c r="BL309" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM309" t="n">
-        <v>0.3313848937891653</v>
-      </c>
+      <c r="BM309" t="inlineStr"/>
       <c r="BN309" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO309" t="n">
@@ -73921,9 +73891,7 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="n">
-        <v>3925672000</v>
-      </c>
+      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73959,9 +73927,7 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="n">
-        <v>351613000</v>
-      </c>
+      <c r="U324" t="inlineStr"/>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73997,9 +73963,7 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="n">
-        <v>173070000</v>
-      </c>
+      <c r="AG324" t="inlineStr"/>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74077,9 +74041,7 @@
       <c r="BD324" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE324" t="n">
-        <v>1844498000</v>
-      </c>
+      <c r="BE324" t="inlineStr"/>
       <c r="BF324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74091,26 +74053,22 @@
       <c r="BH324" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI324" t="n">
-        <v>1571322000</v>
-      </c>
+      <c r="BI324" t="inlineStr"/>
       <c r="BJ324" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK324" t="n">
-        <v>0.6076252752798235</v>
+        <v>0.608</v>
       </c>
       <c r="BL324" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM324" t="n">
-        <v>0.6076252752798235</v>
-      </c>
+      <c r="BM324" t="inlineStr"/>
       <c r="BN324" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO324" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3298,13 +3298,13 @@
         </is>
       </c>
       <c r="BO12" t="n">
-        <v>1913600</v>
+        <v>1918600</v>
       </c>
       <c r="BP12" t="n">
         <v>1918600</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1913600</v>
+        <v>1918600</v>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="BO13" t="n">
-        <v>3196320</v>
+        <v>3214320</v>
       </c>
       <c r="BP13" t="n">
         <v>3206320</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3196320</v>
+        <v>3214320</v>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
@@ -10320,13 +10320,13 @@
         </is>
       </c>
       <c r="BO43" t="n">
-        <v>100662000</v>
+        <v>100629897</v>
       </c>
       <c r="BP43" t="n">
         <v>100725000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>100662000</v>
+        <v>100629897</v>
       </c>
       <c r="BR43" t="inlineStr">
         <is>
@@ -10780,13 +10780,13 @@
         </is>
       </c>
       <c r="BO45" t="n">
-        <v>22811000</v>
+        <v>22858200</v>
       </c>
       <c r="BP45" t="n">
         <v>22858200</v>
       </c>
       <c r="BQ45" t="n">
-        <v>22811000</v>
+        <v>22858200</v>
       </c>
       <c r="BR45" t="inlineStr">
         <is>
@@ -17104,13 +17104,13 @@
         </is>
       </c>
       <c r="BO73" t="n">
-        <v>35639300</v>
+        <v>35728900</v>
       </c>
       <c r="BP73" t="n">
         <v>37982900</v>
       </c>
       <c r="BQ73" t="n">
-        <v>35639300</v>
+        <v>35728900</v>
       </c>
       <c r="BR73" t="inlineStr">
         <is>
@@ -35210,13 +35210,13 @@
         </is>
       </c>
       <c r="BO154" t="n">
-        <v>15963412</v>
+        <v>16232712</v>
       </c>
       <c r="BP154" t="n">
         <v>17602800</v>
       </c>
       <c r="BQ154" t="n">
-        <v>15963412</v>
+        <v>16232712</v>
       </c>
       <c r="BR154" t="inlineStr">
         <is>
@@ -35446,13 +35446,13 @@
         </is>
       </c>
       <c r="BO155" t="n">
-        <v>3693982</v>
+        <v>3693932</v>
       </c>
       <c r="BP155" t="n">
         <v>3815994</v>
       </c>
       <c r="BQ155" t="n">
-        <v>3693982</v>
+        <v>3693932</v>
       </c>
       <c r="BR155" t="inlineStr">
         <is>
@@ -36142,13 +36142,13 @@
         </is>
       </c>
       <c r="BO158" t="n">
-        <v>18003414</v>
+        <v>18362529</v>
       </c>
       <c r="BP158" t="n">
         <v>18351510</v>
       </c>
       <c r="BQ158" t="n">
-        <v>18003414</v>
+        <v>18362529</v>
       </c>
       <c r="BR158" t="inlineStr">
         <is>
@@ -41238,13 +41238,13 @@
         </is>
       </c>
       <c r="BO182" t="n">
-        <v>11614050</v>
+        <v>11980550</v>
       </c>
       <c r="BP182" t="n">
         <v>12163800</v>
       </c>
       <c r="BQ182" t="n">
-        <v>11614050</v>
+        <v>11980550</v>
       </c>
       <c r="BR182" t="inlineStr">
         <is>
@@ -42328,13 +42328,13 @@
         </is>
       </c>
       <c r="BO187" t="n">
-        <v>9956900</v>
+        <v>9970400</v>
       </c>
       <c r="BP187" t="n">
         <v>9611800</v>
       </c>
       <c r="BQ187" t="n">
-        <v>9956900</v>
+        <v>9970400</v>
       </c>
       <c r="BR187" t="inlineStr">
         <is>
@@ -54426,13 +54426,13 @@
         </is>
       </c>
       <c r="BO239" t="n">
-        <v>8133200</v>
+        <v>8183600</v>
       </c>
       <c r="BP239" t="n">
         <v>8183200</v>
       </c>
       <c r="BQ239" t="n">
-        <v>8133200</v>
+        <v>8183600</v>
       </c>
       <c r="BR239" t="inlineStr">
         <is>
@@ -57948,13 +57948,13 @@
         </is>
       </c>
       <c r="BO254" t="n">
-        <v>6107493</v>
+        <v>6107654</v>
       </c>
       <c r="BP254" t="n">
         <v>6107654</v>
       </c>
       <c r="BQ254" t="n">
-        <v>6107493</v>
+        <v>6107654</v>
       </c>
       <c r="BR254" t="inlineStr">
         <is>
@@ -75031,7 +75031,7 @@
         <v>1</v>
       </c>
       <c r="F329" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G329" t="n">
         <v>111786000000</v>
@@ -75086,10 +75086,10 @@
         </is>
       </c>
       <c r="W329" t="n">
-        <v>7425000000</v>
+        <v>7695000000</v>
       </c>
       <c r="X329" t="n">
-        <v>7425000000</v>
+        <v>7695000000</v>
       </c>
       <c r="Y329" t="inlineStr"/>
       <c r="Z329" t="inlineStr">
@@ -75124,10 +75124,10 @@
         </is>
       </c>
       <c r="AI329" t="n">
-        <v>3655000000</v>
+        <v>3826000000</v>
       </c>
       <c r="AJ329" t="n">
-        <v>3655000000</v>
+        <v>3826000000</v>
       </c>
       <c r="AK329" t="inlineStr"/>
       <c r="AL329" t="inlineStr">
@@ -75190,10 +75190,10 @@
         </is>
       </c>
       <c r="BC329" t="n">
-        <v>32209000000</v>
+        <v>31901000000</v>
       </c>
       <c r="BD329" t="n">
-        <v>32209000000</v>
+        <v>31901000000</v>
       </c>
       <c r="BE329" t="n">
         <v>25649000000</v>
@@ -75204,10 +75204,10 @@
         </is>
       </c>
       <c r="BG329" t="n">
-        <v>65181000000</v>
+        <v>65357000000</v>
       </c>
       <c r="BH329" t="n">
-        <v>65181000000</v>
+        <v>65357000000</v>
       </c>
       <c r="BI329" t="n">
         <v>35482000000</v>
@@ -75232,13 +75232,13 @@
         </is>
       </c>
       <c r="BO329" t="n">
-        <v>183599706</v>
+        <v>183348206</v>
       </c>
       <c r="BP329" t="n">
         <v>187756582</v>
       </c>
       <c r="BQ329" t="n">
-        <v>183599706</v>
+        <v>183348206</v>
       </c>
       <c r="BR329" t="inlineStr">
         <is>
@@ -86498,13 +86498,13 @@
         </is>
       </c>
       <c r="BO377" t="n">
-        <v>8432908</v>
+        <v>8433508</v>
       </c>
       <c r="BP377" t="n">
         <v>8433540</v>
       </c>
       <c r="BQ377" t="n">
-        <v>8432908</v>
+        <v>8433508</v>
       </c>
       <c r="BR377" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3807,7 +3807,9 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3843,7 +3845,9 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3879,7 +3883,9 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3952,7 +3958,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2038006000</v>
+        <v>2065504000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3966,7 +3972,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1895989000</v>
+        <v>2272296000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3974,13 +3980,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4721,7 +4727,9 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2006859000</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4757,7 +4765,9 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>123675000</v>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4793,7 +4803,9 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>32652000</v>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4871,7 +4883,9 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>1185144000</v>
+      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4883,22 +4897,26 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>1430969000</v>
+      </c>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785</v>
+        <v>0.785581548809497</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.785581548809497</v>
+      </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -17104,13 +17122,13 @@
         </is>
       </c>
       <c r="BO73" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BP73" t="n">
         <v>37982900</v>
       </c>
       <c r="BQ73" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BR73" t="inlineStr">
         <is>
@@ -30048,13 +30066,13 @@
         </is>
       </c>
       <c r="BO131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BP131" t="n">
         <v>5529204</v>
       </c>
       <c r="BQ131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BR131" t="inlineStr">
         <is>
@@ -35446,13 +35464,13 @@
         </is>
       </c>
       <c r="BO155" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BP155" t="n">
         <v>3815994</v>
       </c>
       <c r="BQ155" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BR155" t="inlineStr">
         <is>
@@ -41238,13 +41256,13 @@
         </is>
       </c>
       <c r="BO182" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BP182" t="n">
         <v>12163800</v>
       </c>
       <c r="BQ182" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BR182" t="inlineStr">
         <is>
@@ -42328,13 +42346,13 @@
         </is>
       </c>
       <c r="BO187" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BP187" t="n">
         <v>9611800</v>
       </c>
       <c r="BQ187" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BR187" t="inlineStr">
         <is>
@@ -54426,13 +54444,13 @@
         </is>
       </c>
       <c r="BO239" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BP239" t="n">
         <v>8183200</v>
       </c>
       <c r="BQ239" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BR239" t="inlineStr">
         <is>
@@ -70429,7 +70447,9 @@
       <c r="H309" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I309" t="inlineStr"/>
+      <c r="I309" t="n">
+        <v>13007061000</v>
+      </c>
       <c r="J309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70465,7 +70485,9 @@
       <c r="T309" t="n">
         <v>147000000</v>
       </c>
-      <c r="U309" t="inlineStr"/>
+      <c r="U309" t="n">
+        <v>472174000</v>
+      </c>
       <c r="V309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70501,7 +70523,9 @@
       <c r="AF309" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG309" t="inlineStr"/>
+      <c r="AG309" t="n">
+        <v>168261000</v>
+      </c>
       <c r="AH309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70579,7 +70603,9 @@
       <c r="BD309" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE309" t="inlineStr"/>
+      <c r="BE309" t="n">
+        <v>754210000</v>
+      </c>
       <c r="BF309" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70591,22 +70617,26 @@
       <c r="BH309" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI309" t="inlineStr"/>
+      <c r="BI309" t="n">
+        <v>2187588000</v>
+      </c>
       <c r="BJ309" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK309" t="n">
-        <v>0.331</v>
+        <v>0.3313848937891653</v>
       </c>
       <c r="BL309" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM309" t="inlineStr"/>
+      <c r="BM309" t="n">
+        <v>0.3313848937891653</v>
+      </c>
       <c r="BN309" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO309" t="n">
@@ -73891,7 +73921,9 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="n">
+        <v>3925672000</v>
+      </c>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73927,7 +73959,9 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="inlineStr"/>
+      <c r="U324" t="n">
+        <v>351613000</v>
+      </c>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73963,7 +73997,9 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="inlineStr"/>
+      <c r="AG324" t="n">
+        <v>173070000</v>
+      </c>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74041,7 +74077,9 @@
       <c r="BD324" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE324" t="inlineStr"/>
+      <c r="BE324" t="n">
+        <v>1844498000</v>
+      </c>
       <c r="BF324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74053,22 +74091,26 @@
       <c r="BH324" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI324" t="inlineStr"/>
+      <c r="BI324" t="n">
+        <v>1571322000</v>
+      </c>
       <c r="BJ324" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK324" t="n">
-        <v>0.608</v>
+        <v>0.6076252752798235</v>
       </c>
       <c r="BL324" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM324" t="inlineStr"/>
+      <c r="BM324" t="n">
+        <v>0.6076252752798235</v>
+      </c>
       <c r="BN324" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO324" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3807,7 +3807,9 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3843,7 +3845,9 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3879,7 +3883,9 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3952,7 +3958,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2038006000</v>
+        <v>2065504000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3966,7 +3972,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1895989000</v>
+        <v>2272296000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3974,13 +3980,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4721,7 +4727,9 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2006859000</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4757,7 +4765,9 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>123675000</v>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4793,7 +4803,9 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>32652000</v>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4871,7 +4883,9 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>1185144000</v>
+      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4883,22 +4897,26 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>1430969000</v>
+      </c>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785</v>
+        <v>0.785581548809497</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.785581548809497</v>
+      </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -17104,13 +17122,13 @@
         </is>
       </c>
       <c r="BO73" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BP73" t="n">
         <v>37982900</v>
       </c>
       <c r="BQ73" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BR73" t="inlineStr">
         <is>
@@ -30048,13 +30066,13 @@
         </is>
       </c>
       <c r="BO131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BP131" t="n">
         <v>5529204</v>
       </c>
       <c r="BQ131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BR131" t="inlineStr">
         <is>
@@ -35446,13 +35464,13 @@
         </is>
       </c>
       <c r="BO155" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BP155" t="n">
         <v>3815994</v>
       </c>
       <c r="BQ155" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BR155" t="inlineStr">
         <is>
@@ -41002,13 +41020,13 @@
         </is>
       </c>
       <c r="BO181" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BP181" t="n">
         <v>12163800</v>
       </c>
       <c r="BQ181" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BR181" t="inlineStr">
         <is>
@@ -42092,13 +42110,13 @@
         </is>
       </c>
       <c r="BO186" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BP186" t="n">
         <v>9611800</v>
       </c>
       <c r="BQ186" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BR186" t="inlineStr">
         <is>
@@ -54190,13 +54208,13 @@
         </is>
       </c>
       <c r="BO238" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BP238" t="n">
         <v>8183200</v>
       </c>
       <c r="BQ238" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BR238" t="inlineStr">
         <is>
@@ -70193,7 +70211,9 @@
       <c r="H308" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I308" t="inlineStr"/>
+      <c r="I308" t="n">
+        <v>13007061000</v>
+      </c>
       <c r="J308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70229,7 +70249,9 @@
       <c r="T308" t="n">
         <v>147000000</v>
       </c>
-      <c r="U308" t="inlineStr"/>
+      <c r="U308" t="n">
+        <v>472174000</v>
+      </c>
       <c r="V308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70265,7 +70287,9 @@
       <c r="AF308" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG308" t="inlineStr"/>
+      <c r="AG308" t="n">
+        <v>168261000</v>
+      </c>
       <c r="AH308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70343,7 +70367,9 @@
       <c r="BD308" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE308" t="inlineStr"/>
+      <c r="BE308" t="n">
+        <v>754210000</v>
+      </c>
       <c r="BF308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70355,22 +70381,26 @@
       <c r="BH308" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI308" t="inlineStr"/>
+      <c r="BI308" t="n">
+        <v>2187588000</v>
+      </c>
       <c r="BJ308" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK308" t="n">
-        <v>0.331</v>
+        <v>0.3313848937891653</v>
       </c>
       <c r="BL308" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM308" t="inlineStr"/>
+      <c r="BM308" t="n">
+        <v>0.3313848937891653</v>
+      </c>
       <c r="BN308" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO308" t="n">
@@ -73655,7 +73685,9 @@
       <c r="H323" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I323" t="inlineStr"/>
+      <c r="I323" t="n">
+        <v>3925672000</v>
+      </c>
       <c r="J323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73691,7 +73723,9 @@
       <c r="T323" t="n">
         <v>508000000</v>
       </c>
-      <c r="U323" t="inlineStr"/>
+      <c r="U323" t="n">
+        <v>351613000</v>
+      </c>
       <c r="V323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73727,7 +73761,9 @@
       <c r="AF323" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG323" t="inlineStr"/>
+      <c r="AG323" t="n">
+        <v>173070000</v>
+      </c>
       <c r="AH323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73805,7 +73841,9 @@
       <c r="BD323" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE323" t="inlineStr"/>
+      <c r="BE323" t="n">
+        <v>1844498000</v>
+      </c>
       <c r="BF323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73817,22 +73855,26 @@
       <c r="BH323" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI323" t="inlineStr"/>
+      <c r="BI323" t="n">
+        <v>1571322000</v>
+      </c>
       <c r="BJ323" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK323" t="n">
-        <v>0.608</v>
+        <v>0.6076252752798235</v>
       </c>
       <c r="BL323" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM323" t="inlineStr"/>
+      <c r="BM323" t="n">
+        <v>0.6076252752798235</v>
+      </c>
       <c r="BN323" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO323" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -1259,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
         <v>1027747000</v>
@@ -1455,7 +1455,7 @@
         <v>3022440</v>
       </c>
       <c r="BP4" t="n">
-        <v>3022440</v>
+        <v>3043840</v>
       </c>
       <c r="BQ4" t="n">
         <v>3022440</v>
@@ -20595,7 +20595,7 @@
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G89" t="n">
         <v>19730322000</v>
@@ -20799,7 +20799,7 @@
         <v>9360198</v>
       </c>
       <c r="BP89" t="n">
-        <v>9360198</v>
+        <v>9395400</v>
       </c>
       <c r="BQ89" t="n">
         <v>9360198</v>
@@ -33246,13 +33246,13 @@
         </is>
       </c>
       <c r="BO145" t="n">
-        <v>1473493</v>
+        <v>1477493</v>
       </c>
       <c r="BP145" t="n">
         <v>1477600</v>
       </c>
       <c r="BQ145" t="n">
-        <v>1473493</v>
+        <v>1477493</v>
       </c>
       <c r="BR145" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G150" t="n">
         <v>10256796000</v>
@@ -47221,7 +47221,7 @@
         <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G209" t="n">
         <v>6468000000</v>
@@ -47250,10 +47250,10 @@
         </is>
       </c>
       <c r="O209" t="n">
-        <v>3990000000</v>
+        <v>4348000000</v>
       </c>
       <c r="P209" t="n">
-        <v>3990000000</v>
+        <v>4348000000</v>
       </c>
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr">
@@ -47287,12 +47287,16 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AA209" t="inlineStr"/>
-      <c r="AB209" t="inlineStr"/>
+      <c r="AA209" t="n">
+        <v>-1546000000</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>-1546000000</v>
+      </c>
       <c r="AC209" t="inlineStr"/>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AE209" t="n">
@@ -47321,12 +47325,16 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AM209" t="inlineStr"/>
-      <c r="AN209" t="inlineStr"/>
+      <c r="AM209" t="n">
+        <v>-1566000000</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>-1566000000</v>
+      </c>
       <c r="AO209" t="inlineStr"/>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AQ209" t="n">
@@ -47417,7 +47425,7 @@
         <v>14812720</v>
       </c>
       <c r="BP209" t="n">
-        <v>14813400</v>
+        <v>14814600</v>
       </c>
       <c r="BQ209" t="n">
         <v>14812720</v>
@@ -50240,13 +50248,13 @@
         </is>
       </c>
       <c r="BO221" t="n">
-        <v>41668400</v>
+        <v>41208200</v>
       </c>
       <c r="BP221" t="n">
         <v>42568400</v>
       </c>
       <c r="BQ221" t="n">
-        <v>41668400</v>
+        <v>41208200</v>
       </c>
       <c r="BR221" t="inlineStr">
         <is>
@@ -70439,7 +70447,7 @@
         <v>1</v>
       </c>
       <c r="F309" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G309" t="n">
         <v>10618472000</v>
@@ -76483,7 +76491,7 @@
         <v>1</v>
       </c>
       <c r="F335" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G335" t="n">
         <v>38253042000</v>
@@ -76687,7 +76695,7 @@
         <v>14146348</v>
       </c>
       <c r="BP335" t="n">
-        <v>14134400</v>
+        <v>14183200</v>
       </c>
       <c r="BQ335" t="n">
         <v>14146348</v>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3807,9 +3807,7 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="n">
-        <v>13781848000</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3845,9 +3843,7 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="n">
-        <v>755967000</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3883,9 +3879,7 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="n">
-        <v>454620000</v>
-      </c>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3958,7 +3952,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2065504000</v>
+        <v>2038006000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3972,7 +3966,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2272296000</v>
+        <v>1895989000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3980,13 +3974,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4300,13 +4294,13 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>413119000</v>
+        <v>414109000</v>
       </c>
       <c r="T17" t="n">
         <v>413000000</v>
       </c>
       <c r="U17" t="n">
-        <v>553165000</v>
+        <v>554869000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4388,11 +4382,11 @@
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>388135000</v>
+        <v>389740000</v>
       </c>
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="n">
-        <v>388135000</v>
+        <v>389740000</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
@@ -4727,9 +4721,7 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="n">
-        <v>2006859000</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4765,9 +4757,7 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="n">
-        <v>123675000</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4803,9 +4793,7 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="n">
-        <v>32652000</v>
-      </c>
+      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4883,9 +4871,7 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="n">
-        <v>1185144000</v>
-      </c>
+      <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4897,26 +4883,22 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="n">
-        <v>1430969000</v>
-      </c>
+      <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785581548809497</v>
+        <v>0.785</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="n">
-        <v>0.785581548809497</v>
-      </c>
+      <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -17122,13 +17104,13 @@
         </is>
       </c>
       <c r="BO73" t="n">
-        <v>35639300</v>
+        <v>35728900</v>
       </c>
       <c r="BP73" t="n">
         <v>37982900</v>
       </c>
       <c r="BQ73" t="n">
-        <v>35639300</v>
+        <v>35728900</v>
       </c>
       <c r="BR73" t="inlineStr">
         <is>
@@ -30066,13 +30048,13 @@
         </is>
       </c>
       <c r="BO131" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="BP131" t="n">
         <v>5529204</v>
       </c>
       <c r="BQ131" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="BR131" t="inlineStr">
         <is>
@@ -33054,11 +33036,11 @@
         <v>4061000000</v>
       </c>
       <c r="I145" t="n">
-        <v>4061428000</v>
+        <v>4920288000</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -33092,11 +33074,11 @@
         <v>458000000</v>
       </c>
       <c r="U145" t="n">
-        <v>458783000</v>
+        <v>439412000</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W145" t="n">
@@ -33130,11 +33112,11 @@
         <v>295000000</v>
       </c>
       <c r="AG145" t="n">
-        <v>295397000</v>
+        <v>290954000</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI145" t="n">
@@ -33168,7 +33150,7 @@
         <v>3139000000</v>
       </c>
       <c r="AS145" t="n">
-        <v>2612888000</v>
+        <v>3139811000</v>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
@@ -33182,7 +33164,7 @@
         <v>310000000</v>
       </c>
       <c r="AW145" t="n">
-        <v>367072000</v>
+        <v>310480000</v>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
@@ -33196,7 +33178,7 @@
         <v>198000000</v>
       </c>
       <c r="BA145" t="n">
-        <v>232447000</v>
+        <v>198962000</v>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
@@ -33210,7 +33192,7 @@
         <v>1462000000</v>
       </c>
       <c r="BE145" t="n">
-        <v>1520790000</v>
+        <v>1462028000</v>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
@@ -33224,7 +33206,7 @@
         <v>1967000000</v>
       </c>
       <c r="BI145" t="n">
-        <v>1688851000</v>
+        <v>1967913000</v>
       </c>
       <c r="BJ145" t="inlineStr">
         <is>
@@ -33232,13 +33214,13 @@
         </is>
       </c>
       <c r="BK145" t="n">
-        <v>0.6109014104784081</v>
+        <v>0.6722185216687333</v>
       </c>
       <c r="BL145" t="n">
         <v>0.672</v>
       </c>
       <c r="BM145" t="n">
-        <v>0.6109014104784081</v>
+        <v>0.6722185216687333</v>
       </c>
       <c r="BN145" t="inlineStr">
         <is>
@@ -35464,13 +35446,13 @@
         </is>
       </c>
       <c r="BO155" t="n">
-        <v>3693982</v>
+        <v>3693932</v>
       </c>
       <c r="BP155" t="n">
         <v>3815994</v>
       </c>
       <c r="BQ155" t="n">
-        <v>3693982</v>
+        <v>3693932</v>
       </c>
       <c r="BR155" t="inlineStr">
         <is>
@@ -41020,13 +41002,13 @@
         </is>
       </c>
       <c r="BO181" t="n">
-        <v>11614050</v>
+        <v>11980550</v>
       </c>
       <c r="BP181" t="n">
         <v>12163800</v>
       </c>
       <c r="BQ181" t="n">
-        <v>11614050</v>
+        <v>11980550</v>
       </c>
       <c r="BR181" t="inlineStr">
         <is>
@@ -42110,13 +42092,13 @@
         </is>
       </c>
       <c r="BO186" t="n">
-        <v>9956900</v>
+        <v>9970400</v>
       </c>
       <c r="BP186" t="n">
         <v>9611800</v>
       </c>
       <c r="BQ186" t="n">
-        <v>9956900</v>
+        <v>9970400</v>
       </c>
       <c r="BR186" t="inlineStr">
         <is>
@@ -51926,11 +51908,11 @@
         <v>10003000000</v>
       </c>
       <c r="I229" t="n">
-        <v>10003292000</v>
+        <v>7795270000</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K229" t="n">
@@ -51964,11 +51946,11 @@
         <v>-10269000000</v>
       </c>
       <c r="U229" t="n">
-        <v>-10269868000</v>
+        <v>-187540000</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W229" t="n">
@@ -52002,11 +51984,11 @@
         <v>-9947000000</v>
       </c>
       <c r="AG229" t="n">
-        <v>-9947586000</v>
+        <v>-337203000</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI229" t="n">
@@ -52040,7 +52022,7 @@
         <v>13346000000</v>
       </c>
       <c r="AS229" t="n">
-        <v>14270932000</v>
+        <v>13346962000</v>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
@@ -52054,7 +52036,7 @@
         <v>-2056000000</v>
       </c>
       <c r="AW229" t="n">
-        <v>-389677000</v>
+        <v>-2056730000</v>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
@@ -52068,7 +52050,7 @@
         <v>-2355000000</v>
       </c>
       <c r="BA229" t="n">
-        <v>-674767000</v>
+        <v>-2355328000</v>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
@@ -52082,7 +52064,7 @@
         <v>3957000000</v>
       </c>
       <c r="BE229" t="n">
-        <v>1550889000</v>
+        <v>3957482000</v>
       </c>
       <c r="BF229" t="inlineStr">
         <is>
@@ -52096,7 +52078,7 @@
         <v>657000000</v>
       </c>
       <c r="BI229" t="n">
-        <v>-4738544000</v>
+        <v>701360000</v>
       </c>
       <c r="BJ229" t="inlineStr">
         <is>
@@ -52104,13 +52086,13 @@
         </is>
       </c>
       <c r="BK229" t="n">
-        <v>-0.6243865724071529</v>
+        <v>0.0761478168357073</v>
       </c>
       <c r="BL229" t="n">
         <v>0.076</v>
       </c>
       <c r="BM229" t="n">
-        <v>-0.6243865724071529</v>
+        <v>0.0761478168357073</v>
       </c>
       <c r="BN229" t="inlineStr">
         <is>
@@ -54216,13 +54198,13 @@
         </is>
       </c>
       <c r="BO238" t="n">
-        <v>8133200</v>
+        <v>8183600</v>
       </c>
       <c r="BP238" t="n">
         <v>8183200</v>
       </c>
       <c r="BQ238" t="n">
-        <v>8133200</v>
+        <v>8183600</v>
       </c>
       <c r="BR238" t="inlineStr">
         <is>
@@ -70219,9 +70201,7 @@
       <c r="H308" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I308" t="n">
-        <v>13007061000</v>
-      </c>
+      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70257,9 +70237,7 @@
       <c r="T308" t="n">
         <v>147000000</v>
       </c>
-      <c r="U308" t="n">
-        <v>472174000</v>
-      </c>
+      <c r="U308" t="inlineStr"/>
       <c r="V308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70295,9 +70273,7 @@
       <c r="AF308" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG308" t="n">
-        <v>168261000</v>
-      </c>
+      <c r="AG308" t="inlineStr"/>
       <c r="AH308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70375,9 +70351,7 @@
       <c r="BD308" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE308" t="n">
-        <v>754210000</v>
-      </c>
+      <c r="BE308" t="inlineStr"/>
       <c r="BF308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70389,26 +70363,22 @@
       <c r="BH308" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI308" t="n">
-        <v>2187588000</v>
-      </c>
+      <c r="BI308" t="inlineStr"/>
       <c r="BJ308" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK308" t="n">
-        <v>0.3313848937891653</v>
+        <v>0.331</v>
       </c>
       <c r="BL308" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM308" t="n">
-        <v>0.3313848937891653</v>
-      </c>
+      <c r="BM308" t="inlineStr"/>
       <c r="BN308" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO308" t="n">
@@ -73693,9 +73663,7 @@
       <c r="H323" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I323" t="n">
-        <v>3925672000</v>
-      </c>
+      <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73731,9 +73699,7 @@
       <c r="T323" t="n">
         <v>508000000</v>
       </c>
-      <c r="U323" t="n">
-        <v>351613000</v>
-      </c>
+      <c r="U323" t="inlineStr"/>
       <c r="V323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73769,9 +73735,7 @@
       <c r="AF323" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG323" t="n">
-        <v>173070000</v>
-      </c>
+      <c r="AG323" t="inlineStr"/>
       <c r="AH323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73849,9 +73813,7 @@
       <c r="BD323" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE323" t="n">
-        <v>1844498000</v>
-      </c>
+      <c r="BE323" t="inlineStr"/>
       <c r="BF323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73863,26 +73825,22 @@
       <c r="BH323" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI323" t="n">
-        <v>1571322000</v>
-      </c>
+      <c r="BI323" t="inlineStr"/>
       <c r="BJ323" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK323" t="n">
-        <v>0.6076252752798235</v>
+        <v>0.608</v>
       </c>
       <c r="BL323" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM323" t="n">
-        <v>0.6076252752798235</v>
-      </c>
+      <c r="BM323" t="inlineStr"/>
       <c r="BN323" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO323" t="n">
@@ -75792,11 +75750,11 @@
         <v>2130000000</v>
       </c>
       <c r="I332" t="n">
-        <v>2130602000</v>
+        <v>1928222000</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K332" t="n">
@@ -75830,11 +75788,11 @@
         <v>21000000</v>
       </c>
       <c r="U332" t="n">
-        <v>21661000</v>
+        <v>-113178000</v>
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W332" t="n">
@@ -75868,11 +75826,11 @@
         <v>20000000</v>
       </c>
       <c r="AG332" t="n">
-        <v>20851000</v>
+        <v>-180527000</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI332" t="n">
@@ -75906,7 +75864,7 @@
         <v>2166000000</v>
       </c>
       <c r="AS332" t="n">
-        <v>2241984000</v>
+        <v>2166905000</v>
       </c>
       <c r="AT332" t="inlineStr">
         <is>
@@ -75920,7 +75878,7 @@
         <v>174000000</v>
       </c>
       <c r="AW332" t="n">
-        <v>234828000</v>
+        <v>174537000</v>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
@@ -75934,7 +75892,7 @@
         <v>123000000</v>
       </c>
       <c r="BA332" t="n">
-        <v>149614000</v>
+        <v>123189000</v>
       </c>
       <c r="BB332" t="inlineStr">
         <is>
@@ -75948,7 +75906,7 @@
         <v>853000000</v>
       </c>
       <c r="BE332" t="n">
-        <v>1073318000</v>
+        <v>963625000</v>
       </c>
       <c r="BF332" t="inlineStr">
         <is>
@@ -75962,7 +75920,7 @@
         <v>852000000</v>
       </c>
       <c r="BI332" t="n">
-        <v>1082169000</v>
+        <v>852380000</v>
       </c>
       <c r="BJ332" t="inlineStr">
         <is>
@@ -75970,13 +75928,13 @@
         </is>
       </c>
       <c r="BK332" t="n">
-        <v>0.6200482668289312</v>
+        <v>0.5783784260599386</v>
       </c>
       <c r="BL332" t="n">
         <v>0.578</v>
       </c>
       <c r="BM332" t="n">
-        <v>0.6200482668289312</v>
+        <v>0.5783784260599386</v>
       </c>
       <c r="BN332" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3807,7 +3807,9 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3843,7 +3845,9 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3879,7 +3883,9 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3952,7 +3958,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2038006000</v>
+        <v>2065504000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3966,7 +3972,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1895989000</v>
+        <v>2272296000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3974,13 +3980,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4721,7 +4727,9 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2006859000</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4757,7 +4765,9 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>123675000</v>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4793,7 +4803,9 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>32652000</v>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4871,7 +4883,9 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>1185144000</v>
+      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4883,22 +4897,26 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>1430969000</v>
+      </c>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785</v>
+        <v>0.785581548809497</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.785581548809497</v>
+      </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -17104,13 +17122,13 @@
         </is>
       </c>
       <c r="BO73" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BP73" t="n">
         <v>37982900</v>
       </c>
       <c r="BQ73" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BR73" t="inlineStr">
         <is>
@@ -17994,13 +18012,13 @@
         </is>
       </c>
       <c r="BO77" t="n">
-        <v>2037300</v>
+        <v>2035600</v>
       </c>
       <c r="BP77" t="n">
         <v>2065900</v>
       </c>
       <c r="BQ77" t="n">
-        <v>2037300</v>
+        <v>2035600</v>
       </c>
       <c r="BR77" t="inlineStr">
         <is>
@@ -30048,13 +30066,13 @@
         </is>
       </c>
       <c r="BO131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BP131" t="n">
         <v>5529204</v>
       </c>
       <c r="BQ131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BR131" t="inlineStr">
         <is>
@@ -35210,13 +35228,13 @@
         </is>
       </c>
       <c r="BO154" t="n">
-        <v>16232712</v>
+        <v>15963412</v>
       </c>
       <c r="BP154" t="n">
         <v>17602800</v>
       </c>
       <c r="BQ154" t="n">
-        <v>16232712</v>
+        <v>15963412</v>
       </c>
       <c r="BR154" t="inlineStr">
         <is>
@@ -35446,13 +35464,13 @@
         </is>
       </c>
       <c r="BO155" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BP155" t="n">
         <v>3815994</v>
       </c>
       <c r="BQ155" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BR155" t="inlineStr">
         <is>
@@ -41002,13 +41020,13 @@
         </is>
       </c>
       <c r="BO181" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BP181" t="n">
         <v>12163800</v>
       </c>
       <c r="BQ181" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BR181" t="inlineStr">
         <is>
@@ -42092,13 +42110,13 @@
         </is>
       </c>
       <c r="BO186" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BP186" t="n">
         <v>9611800</v>
       </c>
       <c r="BQ186" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BR186" t="inlineStr">
         <is>
@@ -45758,13 +45776,13 @@
         </is>
       </c>
       <c r="BO202" t="n">
-        <v>6720090</v>
+        <v>6689096</v>
       </c>
       <c r="BP202" t="n">
         <v>7094200</v>
       </c>
       <c r="BQ202" t="n">
-        <v>6720090</v>
+        <v>6689096</v>
       </c>
       <c r="BR202" t="inlineStr">
         <is>
@@ -49994,13 +50012,13 @@
         </is>
       </c>
       <c r="BO220" t="n">
-        <v>18253377</v>
+        <v>19317677</v>
       </c>
       <c r="BP220" t="n">
         <v>16748700</v>
       </c>
       <c r="BQ220" t="n">
-        <v>18253377</v>
+        <v>19317677</v>
       </c>
       <c r="BR220" t="inlineStr">
         <is>
@@ -54198,13 +54216,13 @@
         </is>
       </c>
       <c r="BO238" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BP238" t="n">
         <v>8183200</v>
       </c>
       <c r="BQ238" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BR238" t="inlineStr">
         <is>
@@ -55372,13 +55390,13 @@
         </is>
       </c>
       <c r="BO243" t="n">
-        <v>5070069</v>
+        <v>5051669</v>
       </c>
       <c r="BP243" t="n">
         <v>5090202</v>
       </c>
       <c r="BQ243" t="n">
-        <v>5070069</v>
+        <v>5051669</v>
       </c>
       <c r="BR243" t="inlineStr">
         <is>
@@ -59342,13 +59360,13 @@
         </is>
       </c>
       <c r="BO260" t="n">
-        <v>9593200</v>
+        <v>9593157</v>
       </c>
       <c r="BP260" t="n">
         <v>9593200</v>
       </c>
       <c r="BQ260" t="n">
-        <v>9593200</v>
+        <v>9593157</v>
       </c>
       <c r="BR260" t="inlineStr">
         <is>
@@ -70201,7 +70219,9 @@
       <c r="H308" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I308" t="inlineStr"/>
+      <c r="I308" t="n">
+        <v>13007061000</v>
+      </c>
       <c r="J308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70237,7 +70257,9 @@
       <c r="T308" t="n">
         <v>147000000</v>
       </c>
-      <c r="U308" t="inlineStr"/>
+      <c r="U308" t="n">
+        <v>472174000</v>
+      </c>
       <c r="V308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70273,7 +70295,9 @@
       <c r="AF308" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG308" t="inlineStr"/>
+      <c r="AG308" t="n">
+        <v>168261000</v>
+      </c>
       <c r="AH308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70351,7 +70375,9 @@
       <c r="BD308" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE308" t="inlineStr"/>
+      <c r="BE308" t="n">
+        <v>754210000</v>
+      </c>
       <c r="BF308" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70363,22 +70389,26 @@
       <c r="BH308" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI308" t="inlineStr"/>
+      <c r="BI308" t="n">
+        <v>2187588000</v>
+      </c>
       <c r="BJ308" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK308" t="n">
-        <v>0.331</v>
+        <v>0.3313848937891653</v>
       </c>
       <c r="BL308" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM308" t="inlineStr"/>
+      <c r="BM308" t="n">
+        <v>0.3313848937891653</v>
+      </c>
       <c r="BN308" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO308" t="n">
@@ -73663,7 +73693,9 @@
       <c r="H323" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I323" t="inlineStr"/>
+      <c r="I323" t="n">
+        <v>3925672000</v>
+      </c>
       <c r="J323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73699,7 +73731,9 @@
       <c r="T323" t="n">
         <v>508000000</v>
       </c>
-      <c r="U323" t="inlineStr"/>
+      <c r="U323" t="n">
+        <v>351613000</v>
+      </c>
       <c r="V323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73735,7 +73769,9 @@
       <c r="AF323" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG323" t="inlineStr"/>
+      <c r="AG323" t="n">
+        <v>173070000</v>
+      </c>
       <c r="AH323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73813,7 +73849,9 @@
       <c r="BD323" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE323" t="inlineStr"/>
+      <c r="BE323" t="n">
+        <v>1844498000</v>
+      </c>
       <c r="BF323" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73825,22 +73863,26 @@
       <c r="BH323" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI323" t="inlineStr"/>
+      <c r="BI323" t="n">
+        <v>1571322000</v>
+      </c>
       <c r="BJ323" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK323" t="n">
-        <v>0.608</v>
+        <v>0.6076252752798235</v>
       </c>
       <c r="BL323" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM323" t="inlineStr"/>
+      <c r="BM323" t="n">
+        <v>0.6076252752798235</v>
+      </c>
       <c r="BN323" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO323" t="n">
@@ -76178,13 +76220,13 @@
         </is>
       </c>
       <c r="BO333" t="n">
-        <v>1319998</v>
+        <v>1307998</v>
       </c>
       <c r="BP333" t="n">
         <v>1414000</v>
       </c>
       <c r="BQ333" t="n">
-        <v>1319998</v>
+        <v>1307998</v>
       </c>
       <c r="BR333" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3807,7 +3807,9 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3843,7 +3845,9 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3879,7 +3883,9 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3952,7 +3958,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2038006000</v>
+        <v>2065504000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3966,7 +3972,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1895989000</v>
+        <v>2272296000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3974,13 +3980,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4721,7 +4727,9 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2006859000</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4757,7 +4765,9 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>123675000</v>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4793,7 +4803,9 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>32652000</v>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4871,7 +4883,9 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>1185144000</v>
+      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4883,22 +4897,26 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>1430969000</v>
+      </c>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785</v>
+        <v>0.785581548809497</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.785581548809497</v>
+      </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -17104,13 +17122,13 @@
         </is>
       </c>
       <c r="BO73" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BP73" t="n">
         <v>37982900</v>
       </c>
       <c r="BQ73" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BR73" t="inlineStr">
         <is>
@@ -30056,13 +30074,13 @@
         </is>
       </c>
       <c r="BO131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BP131" t="n">
         <v>5529204</v>
       </c>
       <c r="BQ131" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BR131" t="inlineStr">
         <is>
@@ -35454,13 +35472,13 @@
         </is>
       </c>
       <c r="BO155" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BP155" t="n">
         <v>3815994</v>
       </c>
       <c r="BQ155" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BR155" t="inlineStr">
         <is>
@@ -41214,13 +41232,13 @@
         </is>
       </c>
       <c r="BO182" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BP182" t="n">
         <v>12163800</v>
       </c>
       <c r="BQ182" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BR182" t="inlineStr">
         <is>
@@ -42304,13 +42322,13 @@
         </is>
       </c>
       <c r="BO187" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BP187" t="n">
         <v>9611800</v>
       </c>
       <c r="BQ187" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BR187" t="inlineStr">
         <is>
@@ -54808,13 +54826,13 @@
         </is>
       </c>
       <c r="BO241" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BP241" t="n">
         <v>8183200</v>
       </c>
       <c r="BQ241" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BR241" t="inlineStr">
         <is>
@@ -70811,7 +70829,9 @@
       <c r="H311" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I311" t="inlineStr"/>
+      <c r="I311" t="n">
+        <v>13007061000</v>
+      </c>
       <c r="J311" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70847,7 +70867,9 @@
       <c r="T311" t="n">
         <v>147000000</v>
       </c>
-      <c r="U311" t="inlineStr"/>
+      <c r="U311" t="n">
+        <v>472174000</v>
+      </c>
       <c r="V311" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70883,7 +70905,9 @@
       <c r="AF311" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG311" t="inlineStr"/>
+      <c r="AG311" t="n">
+        <v>168261000</v>
+      </c>
       <c r="AH311" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70961,7 +70985,9 @@
       <c r="BD311" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE311" t="inlineStr"/>
+      <c r="BE311" t="n">
+        <v>754210000</v>
+      </c>
       <c r="BF311" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70973,22 +70999,26 @@
       <c r="BH311" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI311" t="inlineStr"/>
+      <c r="BI311" t="n">
+        <v>2187588000</v>
+      </c>
       <c r="BJ311" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK311" t="n">
-        <v>0.331</v>
+        <v>0.3313848937891653</v>
       </c>
       <c r="BL311" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM311" t="inlineStr"/>
+      <c r="BM311" t="n">
+        <v>0.3313848937891653</v>
+      </c>
       <c r="BN311" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO311" t="n">
@@ -74273,7 +74303,9 @@
       <c r="H326" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I326" t="inlineStr"/>
+      <c r="I326" t="n">
+        <v>3925672000</v>
+      </c>
       <c r="J326" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74309,7 +74341,9 @@
       <c r="T326" t="n">
         <v>508000000</v>
       </c>
-      <c r="U326" t="inlineStr"/>
+      <c r="U326" t="n">
+        <v>351613000</v>
+      </c>
       <c r="V326" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74345,7 +74379,9 @@
       <c r="AF326" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG326" t="inlineStr"/>
+      <c r="AG326" t="n">
+        <v>173070000</v>
+      </c>
       <c r="AH326" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74423,7 +74459,9 @@
       <c r="BD326" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE326" t="inlineStr"/>
+      <c r="BE326" t="n">
+        <v>1844498000</v>
+      </c>
       <c r="BF326" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74435,22 +74473,26 @@
       <c r="BH326" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI326" t="inlineStr"/>
+      <c r="BI326" t="n">
+        <v>1571322000</v>
+      </c>
       <c r="BJ326" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK326" t="n">
-        <v>0.608</v>
+        <v>0.6076252752798235</v>
       </c>
       <c r="BL326" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM326" t="inlineStr"/>
+      <c r="BM326" t="n">
+        <v>0.6076252752798235</v>
+      </c>
       <c r="BN326" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO326" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3821,7 +3821,9 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3857,7 +3859,9 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3893,7 +3897,9 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3966,7 +3972,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2038006000</v>
+        <v>2065504000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3980,7 +3986,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1895989000</v>
+        <v>2272296000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3988,13 +3994,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4735,7 +4741,9 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2006859000</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4771,7 +4779,9 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>123675000</v>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4807,7 +4817,9 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>32652000</v>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4885,7 +4897,9 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>1185144000</v>
+      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4897,22 +4911,26 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>1430969000</v>
+      </c>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785</v>
+        <v>0.785581548809497</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.785581548809497</v>
+      </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -16916,13 +16934,13 @@
         </is>
       </c>
       <c r="BO72" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BP72" t="n">
         <v>37982900</v>
       </c>
       <c r="BQ72" t="n">
-        <v>35728900</v>
+        <v>35639300</v>
       </c>
       <c r="BR72" t="inlineStr">
         <is>
@@ -29900,13 +29918,13 @@
         </is>
       </c>
       <c r="BO130" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BP130" t="n">
         <v>5529204</v>
       </c>
       <c r="BQ130" t="n">
-        <v>5530536</v>
+        <v>5164800</v>
       </c>
       <c r="BR130" t="inlineStr">
         <is>
@@ -35298,13 +35316,13 @@
         </is>
       </c>
       <c r="BO154" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BP154" t="n">
         <v>3815994</v>
       </c>
       <c r="BQ154" t="n">
-        <v>3693932</v>
+        <v>3693982</v>
       </c>
       <c r="BR154" t="inlineStr">
         <is>
@@ -40822,13 +40840,13 @@
         </is>
       </c>
       <c r="BO180" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BP180" t="n">
         <v>12163800</v>
       </c>
       <c r="BQ180" t="n">
-        <v>11980550</v>
+        <v>11614050</v>
       </c>
       <c r="BR180" t="inlineStr">
         <is>
@@ -41912,13 +41930,13 @@
         </is>
       </c>
       <c r="BO185" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BP185" t="n">
         <v>9611800</v>
       </c>
       <c r="BQ185" t="n">
-        <v>9970400</v>
+        <v>9956900</v>
       </c>
       <c r="BR185" t="inlineStr">
         <is>
@@ -54604,13 +54622,13 @@
         </is>
       </c>
       <c r="BO240" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BP240" t="n">
         <v>8183200</v>
       </c>
       <c r="BQ240" t="n">
-        <v>8183600</v>
+        <v>8133200</v>
       </c>
       <c r="BR240" t="inlineStr">
         <is>
@@ -70607,7 +70625,9 @@
       <c r="H310" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I310" t="inlineStr"/>
+      <c r="I310" t="n">
+        <v>13007061000</v>
+      </c>
       <c r="J310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70643,7 +70663,9 @@
       <c r="T310" t="n">
         <v>147000000</v>
       </c>
-      <c r="U310" t="inlineStr"/>
+      <c r="U310" t="n">
+        <v>472174000</v>
+      </c>
       <c r="V310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70679,7 +70701,9 @@
       <c r="AF310" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG310" t="inlineStr"/>
+      <c r="AG310" t="n">
+        <v>168261000</v>
+      </c>
       <c r="AH310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70757,7 +70781,9 @@
       <c r="BD310" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE310" t="inlineStr"/>
+      <c r="BE310" t="n">
+        <v>754210000</v>
+      </c>
       <c r="BF310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70769,22 +70795,26 @@
       <c r="BH310" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI310" t="inlineStr"/>
+      <c r="BI310" t="n">
+        <v>2187588000</v>
+      </c>
       <c r="BJ310" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK310" t="n">
-        <v>0.331</v>
+        <v>0.3313848937891653</v>
       </c>
       <c r="BL310" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM310" t="inlineStr"/>
+      <c r="BM310" t="n">
+        <v>0.3313848937891653</v>
+      </c>
       <c r="BN310" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO310" t="n">
@@ -73833,7 +73863,9 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="n">
+        <v>3925672000</v>
+      </c>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73869,7 +73901,9 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="inlineStr"/>
+      <c r="U324" t="n">
+        <v>351613000</v>
+      </c>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73905,7 +73939,9 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="inlineStr"/>
+      <c r="AG324" t="n">
+        <v>173070000</v>
+      </c>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73983,7 +74019,9 @@
       <c r="BD324" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE324" t="inlineStr"/>
+      <c r="BE324" t="n">
+        <v>1844498000</v>
+      </c>
       <c r="BF324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73995,22 +74033,26 @@
       <c r="BH324" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI324" t="inlineStr"/>
+      <c r="BI324" t="n">
+        <v>1571322000</v>
+      </c>
       <c r="BJ324" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK324" t="n">
-        <v>0.608</v>
+        <v>0.6076252752798235</v>
       </c>
       <c r="BL324" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM324" t="inlineStr"/>
+      <c r="BM324" t="n">
+        <v>0.6076252752798235</v>
+      </c>
       <c r="BN324" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO324" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -38733,7 +38733,7 @@
         <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G171" t="n">
         <v>2454420000</v>
@@ -38760,10 +38760,10 @@
         </is>
       </c>
       <c r="O171" t="n">
-        <v>3570000000</v>
+        <v>3574000000</v>
       </c>
       <c r="P171" t="n">
-        <v>3570000000</v>
+        <v>3574000000</v>
       </c>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr">
@@ -38796,10 +38796,10 @@
         </is>
       </c>
       <c r="AA171" t="n">
-        <v>344000000</v>
+        <v>172000000</v>
       </c>
       <c r="AB171" t="n">
-        <v>344000000</v>
+        <v>172000000</v>
       </c>
       <c r="AC171" t="inlineStr"/>
       <c r="AD171" t="inlineStr">
@@ -38832,10 +38832,10 @@
         </is>
       </c>
       <c r="AM171" t="n">
-        <v>261000000</v>
+        <v>147000000</v>
       </c>
       <c r="AN171" t="n">
-        <v>261000000</v>
+        <v>147000000</v>
       </c>
       <c r="AO171" t="inlineStr"/>
       <c r="AP171" t="inlineStr">
@@ -38925,7 +38925,7 @@
         <v>1055487</v>
       </c>
       <c r="BP171" t="n">
-        <v>965487</v>
+        <v>1075487</v>
       </c>
       <c r="BQ171" t="n">
         <v>1055487</v>
@@ -43293,27 +43293,27 @@
         <v>1</v>
       </c>
       <c r="F192" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G192" t="n">
-        <v>1437040000</v>
+        <v>1763285000</v>
       </c>
       <c r="H192" t="n">
-        <v>1437000000</v>
+        <v>1763000000</v>
       </c>
       <c r="I192" t="n">
         <v>1763285000</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="K192" t="n">
-        <v>1763000000</v>
+        <v>1601000000</v>
       </c>
       <c r="L192" t="n">
-        <v>1763000000</v>
+        <v>1601000000</v>
       </c>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr">
@@ -43322,10 +43322,10 @@
         </is>
       </c>
       <c r="O192" t="n">
-        <v>1601000000</v>
+        <v>1703000000</v>
       </c>
       <c r="P192" t="n">
-        <v>1601000000</v>
+        <v>1703000000</v>
       </c>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr">
@@ -43334,24 +43334,24 @@
         </is>
       </c>
       <c r="S192" t="n">
-        <v>56819000</v>
+        <v>170149000</v>
       </c>
       <c r="T192" t="n">
-        <v>56000000</v>
+        <v>170000000</v>
       </c>
       <c r="U192" t="n">
         <v>170149000</v>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="W192" t="n">
-        <v>170000000</v>
+        <v>74000000</v>
       </c>
       <c r="X192" t="n">
-        <v>170000000</v>
+        <v>74000000</v>
       </c>
       <c r="Y192" t="inlineStr"/>
       <c r="Z192" t="inlineStr">
@@ -43360,10 +43360,10 @@
         </is>
       </c>
       <c r="AA192" t="n">
-        <v>74000000</v>
+        <v>117000000</v>
       </c>
       <c r="AB192" t="n">
-        <v>74000000</v>
+        <v>117000000</v>
       </c>
       <c r="AC192" t="inlineStr"/>
       <c r="AD192" t="inlineStr">
@@ -43372,24 +43372,24 @@
         </is>
       </c>
       <c r="AE192" t="n">
-        <v>48380000</v>
+        <v>126540000</v>
       </c>
       <c r="AF192" t="n">
-        <v>48000000</v>
+        <v>126000000</v>
       </c>
       <c r="AG192" t="n">
         <v>126540000</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="AI192" t="n">
-        <v>126000000</v>
+        <v>162000000</v>
       </c>
       <c r="AJ192" t="n">
-        <v>126000000</v>
+        <v>162000000</v>
       </c>
       <c r="AK192" t="inlineStr"/>
       <c r="AL192" t="inlineStr">
@@ -43398,10 +43398,10 @@
         </is>
       </c>
       <c r="AM192" t="n">
-        <v>162000000</v>
+        <v>79000000</v>
       </c>
       <c r="AN192" t="n">
-        <v>162000000</v>
+        <v>79000000</v>
       </c>
       <c r="AO192" t="inlineStr"/>
       <c r="AP192" t="inlineStr">
@@ -43410,10 +43410,10 @@
         </is>
       </c>
       <c r="AQ192" t="n">
-        <v>1414000000</v>
+        <v>1437000000</v>
       </c>
       <c r="AR192" t="n">
-        <v>1414000000</v>
+        <v>1437000000</v>
       </c>
       <c r="AS192" t="n">
         <v>1414567000</v>
@@ -43424,10 +43424,10 @@
         </is>
       </c>
       <c r="AU192" t="n">
-        <v>138000000</v>
+        <v>56000000</v>
       </c>
       <c r="AV192" t="n">
-        <v>138000000</v>
+        <v>56000000</v>
       </c>
       <c r="AW192" t="n">
         <v>138970000</v>
@@ -43438,10 +43438,10 @@
         </is>
       </c>
       <c r="AY192" t="n">
-        <v>92000000</v>
+        <v>48000000</v>
       </c>
       <c r="AZ192" t="n">
-        <v>92000000</v>
+        <v>48000000</v>
       </c>
       <c r="BA192" t="n">
         <v>92368000</v>
@@ -43452,10 +43452,10 @@
         </is>
       </c>
       <c r="BC192" t="n">
-        <v>683000000</v>
+        <v>855000000</v>
       </c>
       <c r="BD192" t="n">
-        <v>683000000</v>
+        <v>855000000</v>
       </c>
       <c r="BE192" t="n">
         <v>683053000</v>
@@ -43466,10 +43466,10 @@
         </is>
       </c>
       <c r="BG192" t="n">
-        <v>889000000</v>
+        <v>1112000000</v>
       </c>
       <c r="BH192" t="n">
-        <v>889000000</v>
+        <v>1112000000</v>
       </c>
       <c r="BI192" t="n">
         <v>889059000</v>
@@ -43483,7 +43483,7 @@
         <v>0.7488073780847301</v>
       </c>
       <c r="BL192" t="n">
-        <v>0.708</v>
+        <v>0.783</v>
       </c>
       <c r="BM192" t="n">
         <v>0.7488073780847301</v>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -1958,20 +1958,18 @@
         <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>2082994000</v>
+        <v>2082000000</v>
       </c>
       <c r="H7" t="n">
         <v>2082000000</v>
       </c>
-      <c r="I7" t="n">
-        <v>2400260000</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2002,14 +2000,12 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>272411000</v>
+        <v>272000000</v>
       </c>
       <c r="T7" t="n">
         <v>272000000</v>
       </c>
-      <c r="U7" t="n">
-        <v>62546000</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2040,14 +2036,12 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>141803000</v>
+        <v>141000000</v>
       </c>
       <c r="AF7" t="n">
         <v>141000000</v>
       </c>
-      <c r="AG7" t="n">
-        <v>-184425000</v>
-      </c>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2077,40 +2071,28 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AQ7" t="n">
-        <v>1517574000</v>
-      </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="n">
-        <v>1517574000</v>
-      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>YF</t>
-        </is>
-      </c>
-      <c r="AU7" t="n">
-        <v>73773000</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="n">
-        <v>73773000</v>
-      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>YF</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>41495000</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="n">
-        <v>41495000</v>
-      </c>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="BC7" t="n">
@@ -2119,9 +2101,7 @@
       <c r="BD7" t="n">
         <v>1593000000</v>
       </c>
-      <c r="BE7" t="n">
-        <v>1593893000</v>
-      </c>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2133,26 +2113,22 @@
       <c r="BH7" t="n">
         <v>389000000</v>
       </c>
-      <c r="BI7" t="n">
-        <v>389870000</v>
-      </c>
+      <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>0.1864782130386952</v>
+        <v>0.186</v>
       </c>
       <c r="BL7" t="n">
         <v>0.186</v>
       </c>
-      <c r="BM7" t="n">
-        <v>0.1864782130386952</v>
-      </c>
+      <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO7" t="n">
@@ -2161,12 +2137,10 @@
       <c r="BP7" t="n">
         <v>2905200</v>
       </c>
-      <c r="BQ7" t="n">
-        <v>2905200</v>
-      </c>
+      <c r="BQ7" t="inlineStr"/>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
     </row>
@@ -2809,9 +2783,7 @@
       <c r="BD10" t="n">
         <v>7855000000</v>
       </c>
-      <c r="BE10" t="n">
-        <v>7892000000</v>
-      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2823,26 +2795,22 @@
       <c r="BH10" t="n">
         <v>17439000000</v>
       </c>
-      <c r="BI10" t="n">
-        <v>17422000000</v>
-      </c>
+      <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>0.2605080969541098</v>
+        <v>0.261</v>
       </c>
       <c r="BL10" t="n">
         <v>0.261</v>
       </c>
-      <c r="BM10" t="n">
-        <v>0.2605080969541098</v>
-      </c>
+      <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO10" t="n">
@@ -2851,12 +2819,10 @@
       <c r="BP10" t="n">
         <v>7716600</v>
       </c>
-      <c r="BQ10" t="n">
-        <v>7716600</v>
-      </c>
+      <c r="BQ10" t="inlineStr"/>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
     </row>
@@ -2878,20 +2844,18 @@
         <v>1</v>
       </c>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>7928778000</v>
+        <v>7928000000</v>
       </c>
       <c r="H11" t="n">
         <v>7928000000</v>
       </c>
-      <c r="I11" t="n">
-        <v>8993031000</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2922,14 +2886,12 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>727337000</v>
+        <v>727000000</v>
       </c>
       <c r="T11" t="n">
         <v>727000000</v>
       </c>
-      <c r="U11" t="n">
-        <v>656540000</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2960,14 +2922,12 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>485565000</v>
+        <v>485000000</v>
       </c>
       <c r="AF11" t="n">
         <v>485000000</v>
       </c>
-      <c r="AG11" t="n">
-        <v>352716000</v>
-      </c>
+      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3003,9 +2963,7 @@
       <c r="AR11" t="n">
         <v>7928000000</v>
       </c>
-      <c r="AS11" t="n">
-        <v>6299403000</v>
-      </c>
+      <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3017,9 +2975,7 @@
       <c r="AV11" t="n">
         <v>727000000</v>
       </c>
-      <c r="AW11" t="n">
-        <v>101377000</v>
-      </c>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3031,9 +2987,7 @@
       <c r="AZ11" t="n">
         <v>485000000</v>
       </c>
-      <c r="BA11" t="n">
-        <v>70874000</v>
-      </c>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3045,9 +2999,7 @@
       <c r="BD11" t="n">
         <v>8917000000</v>
       </c>
-      <c r="BE11" t="n">
-        <v>8917773000</v>
-      </c>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3059,40 +3011,34 @@
       <c r="BH11" t="n">
         <v>10355000000</v>
       </c>
-      <c r="BI11" t="n">
-        <v>10316268000</v>
-      </c>
+      <c r="BI11" t="inlineStr"/>
       <c r="BJ11" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>0.7696783841113143</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
         <v>0.75</v>
       </c>
-      <c r="BM11" t="n">
-        <v>0.7696783841113143</v>
-      </c>
+      <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO11" t="n">
-        <v>45325211</v>
+        <v>45325241</v>
       </c>
       <c r="BP11" t="n">
         <v>45325241</v>
       </c>
-      <c r="BQ11" t="n">
-        <v>45325211</v>
-      </c>
+      <c r="BQ11" t="inlineStr"/>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3263,10 @@
       <c r="BP12" t="n">
         <v>1918600</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>1918600</v>
-      </c>
+      <c r="BQ12" t="inlineStr"/>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3727,10 @@
       <c r="BP14" t="n">
         <v>5666100</v>
       </c>
-      <c r="BQ14" t="n">
-        <v>5666100</v>
-      </c>
+      <c r="BQ14" t="inlineStr"/>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
     </row>
@@ -3810,20 +3752,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>12363389000</v>
+        <v>12363000000</v>
       </c>
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="n">
-        <v>13781848000</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3854,14 +3794,12 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>542316000</v>
+        <v>542000000</v>
       </c>
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="n">
-        <v>755967000</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3892,14 +3830,12 @@
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>320998000</v>
+        <v>320000000</v>
       </c>
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="n">
-        <v>454620000</v>
-      </c>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3929,40 +3865,28 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AQ15" t="n">
-        <v>8265919000</v>
-      </c>
+      <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="n">
-        <v>8265919000</v>
-      </c>
+      <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>YF</t>
-        </is>
-      </c>
-      <c r="AU15" t="n">
-        <v>120007000</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="n">
-        <v>120007000</v>
-      </c>
+      <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>YF</t>
-        </is>
-      </c>
-      <c r="AY15" t="n">
-        <v>168348000</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="n">
-        <v>168348000</v>
-      </c>
+      <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="BC15" t="n">
@@ -3971,9 +3895,7 @@
       <c r="BD15" t="n">
         <v>2065000000</v>
       </c>
-      <c r="BE15" t="n">
-        <v>2065504000</v>
-      </c>
+      <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3985,40 +3907,34 @@
       <c r="BH15" t="n">
         <v>2272000000</v>
       </c>
-      <c r="BI15" t="n">
-        <v>2272296000</v>
-      </c>
+      <c r="BI15" t="inlineStr"/>
       <c r="BJ15" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.512</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
-      <c r="BM15" t="n">
-        <v>0.5118512364823101</v>
-      </c>
+      <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO15" t="n">
-        <v>8398975</v>
+        <v>8569275</v>
       </c>
       <c r="BP15" t="n">
         <v>8569275</v>
       </c>
-      <c r="BQ15" t="n">
-        <v>8398975</v>
-      </c>
+      <c r="BQ15" t="inlineStr"/>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
     </row>
@@ -4270,20 +4186,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>5847966000</v>
+        <v>5847000000</v>
       </c>
       <c r="H17" t="n">
         <v>5847000000</v>
       </c>
-      <c r="I17" t="n">
-        <v>8019568000</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4314,14 +4228,12 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>414109000</v>
+        <v>413000000</v>
       </c>
       <c r="T17" t="n">
         <v>413000000</v>
       </c>
-      <c r="U17" t="n">
-        <v>554869000</v>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4352,14 +4264,12 @@
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>273173000</v>
+        <v>273000000</v>
       </c>
       <c r="AF17" t="n">
         <v>273000000</v>
       </c>
-      <c r="AG17" t="n">
-        <v>304310000</v>
-      </c>
+      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4389,40 +4299,28 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AQ17" t="n">
-        <v>5298404000</v>
-      </c>
+      <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="n">
-        <v>5298404000</v>
-      </c>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>YF</t>
-        </is>
-      </c>
-      <c r="AU17" t="n">
-        <v>389740000</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="n">
-        <v>389740000</v>
-      </c>
+      <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>YF</t>
-        </is>
-      </c>
-      <c r="AY17" t="n">
-        <v>275454000</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="n">
-        <v>275454000</v>
-      </c>
+      <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="BC17" t="n">
@@ -4431,9 +4329,7 @@
       <c r="BD17" t="n">
         <v>1667000000</v>
       </c>
-      <c r="BE17" t="n">
-        <v>1987756000</v>
-      </c>
+      <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4445,40 +4341,34 @@
       <c r="BH17" t="n">
         <v>1739000000</v>
       </c>
-      <c r="BI17" t="n">
-        <v>1739547000</v>
-      </c>
+      <c r="BI17" t="inlineStr"/>
       <c r="BJ17" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>0.4271421292686969</v>
+        <v>0.427</v>
       </c>
       <c r="BL17" t="n">
         <v>0.427</v>
       </c>
-      <c r="BM17" t="n">
-        <v>0.4271421292686969</v>
-      </c>
+      <c r="BM17" t="inlineStr"/>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO17" t="n">
-        <v>10269836</v>
+        <v>10637253</v>
       </c>
       <c r="BP17" t="n">
         <v>10637253</v>
       </c>
-      <c r="BQ17" t="n">
-        <v>10269836</v>
-      </c>
+      <c r="BQ17" t="inlineStr"/>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
     </row>
@@ -5345,9 +5235,7 @@
       <c r="BD21" t="n">
         <v>26201000000</v>
       </c>
-      <c r="BE21" t="n">
-        <v>26203066000</v>
-      </c>
+      <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -5359,40 +5247,34 @@
       <c r="BH21" t="n">
         <v>33005000000</v>
       </c>
-      <c r="BI21" t="n">
-        <v>31925761000</v>
-      </c>
+      <c r="BI21" t="inlineStr"/>
       <c r="BJ21" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>0.3834985579116227</v>
+        <v>0.383</v>
       </c>
       <c r="BL21" t="n">
         <v>0.383</v>
       </c>
-      <c r="BM21" t="n">
-        <v>0.3834985579116227</v>
-      </c>
+      <c r="BM21" t="inlineStr"/>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO21" t="n">
-        <v>61621872</v>
+        <v>61636723</v>
       </c>
       <c r="BP21" t="n">
         <v>61636723</v>
       </c>
-      <c r="BQ21" t="n">
-        <v>61621872</v>
-      </c>
+      <c r="BQ21" t="inlineStr"/>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
     </row>
@@ -13308,13 +13190,13 @@
         </is>
       </c>
       <c r="BO56" t="n">
-        <v>13065140</v>
+        <v>13025870</v>
       </c>
       <c r="BP56" t="n">
         <v>13681230</v>
       </c>
       <c r="BQ56" t="n">
-        <v>13065140</v>
+        <v>13025870</v>
       </c>
       <c r="BR56" t="inlineStr">
         <is>
@@ -14458,13 +14340,13 @@
         </is>
       </c>
       <c r="BO61" t="n">
-        <v>12420380</v>
+        <v>12355780</v>
       </c>
       <c r="BP61" t="n">
         <v>12700350</v>
       </c>
       <c r="BQ61" t="n">
-        <v>12420380</v>
+        <v>12355780</v>
       </c>
       <c r="BR61" t="inlineStr">
         <is>
@@ -16934,13 +16816,13 @@
         </is>
       </c>
       <c r="BO72" t="n">
-        <v>35639300</v>
+        <v>35728900</v>
       </c>
       <c r="BP72" t="n">
         <v>37982900</v>
       </c>
       <c r="BQ72" t="n">
-        <v>35639300</v>
+        <v>35728900</v>
       </c>
       <c r="BR72" t="inlineStr">
         <is>
@@ -24428,13 +24310,13 @@
         </is>
       </c>
       <c r="BO105" t="n">
-        <v>7752950</v>
+        <v>7618050</v>
       </c>
       <c r="BP105" t="n">
         <v>7823150</v>
       </c>
       <c r="BQ105" t="n">
-        <v>7752950</v>
+        <v>7618050</v>
       </c>
       <c r="BR105" t="inlineStr">
         <is>
@@ -27944,13 +27826,13 @@
         </is>
       </c>
       <c r="BO121" t="n">
-        <v>5481114</v>
+        <v>5467314</v>
       </c>
       <c r="BP121" t="n">
         <v>6185000</v>
       </c>
       <c r="BQ121" t="n">
-        <v>5481114</v>
+        <v>5467314</v>
       </c>
       <c r="BR121" t="inlineStr">
         <is>
@@ -28380,13 +28262,13 @@
         </is>
       </c>
       <c r="BO123" t="n">
-        <v>2004225</v>
+        <v>1993925</v>
       </c>
       <c r="BP123" t="n">
         <v>2330330</v>
       </c>
       <c r="BQ123" t="n">
-        <v>2004225</v>
+        <v>1993925</v>
       </c>
       <c r="BR123" t="inlineStr">
         <is>
@@ -29918,13 +29800,13 @@
         </is>
       </c>
       <c r="BO130" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="BP130" t="n">
         <v>5529204</v>
       </c>
       <c r="BQ130" t="n">
-        <v>5164800</v>
+        <v>5530536</v>
       </c>
       <c r="BR130" t="inlineStr">
         <is>
@@ -32862,13 +32744,13 @@
         </is>
       </c>
       <c r="BO143" t="n">
-        <v>11443868</v>
+        <v>11393168</v>
       </c>
       <c r="BP143" t="n">
         <v>11493548</v>
       </c>
       <c r="BQ143" t="n">
-        <v>11443868</v>
+        <v>11393168</v>
       </c>
       <c r="BR143" t="inlineStr">
         <is>
@@ -35316,13 +35198,13 @@
         </is>
       </c>
       <c r="BO154" t="n">
-        <v>3693982</v>
+        <v>3693932</v>
       </c>
       <c r="BP154" t="n">
         <v>3815994</v>
       </c>
       <c r="BQ154" t="n">
-        <v>3693982</v>
+        <v>3693932</v>
       </c>
       <c r="BR154" t="inlineStr">
         <is>
@@ -38698,13 +38580,13 @@
         </is>
       </c>
       <c r="BO170" t="n">
-        <v>55711000</v>
+        <v>55710432</v>
       </c>
       <c r="BP170" t="n">
         <v>48411000</v>
       </c>
       <c r="BQ170" t="n">
-        <v>55711000</v>
+        <v>55710432</v>
       </c>
       <c r="BR170" t="inlineStr">
         <is>
@@ -40840,13 +40722,13 @@
         </is>
       </c>
       <c r="BO180" t="n">
-        <v>11614050</v>
+        <v>11980550</v>
       </c>
       <c r="BP180" t="n">
         <v>12163800</v>
       </c>
       <c r="BQ180" t="n">
-        <v>11614050</v>
+        <v>11980550</v>
       </c>
       <c r="BR180" t="inlineStr">
         <is>
@@ -41930,13 +41812,13 @@
         </is>
       </c>
       <c r="BO185" t="n">
-        <v>9956900</v>
+        <v>9970400</v>
       </c>
       <c r="BP185" t="n">
         <v>9611800</v>
       </c>
       <c r="BQ185" t="n">
-        <v>9956900</v>
+        <v>9970400</v>
       </c>
       <c r="BR185" t="inlineStr">
         <is>
@@ -47894,13 +47776,13 @@
         </is>
       </c>
       <c r="BO211" t="n">
-        <v>7850055</v>
+        <v>7811155</v>
       </c>
       <c r="BP211" t="n">
         <v>7850358</v>
       </c>
       <c r="BQ211" t="n">
-        <v>7850055</v>
+        <v>7811155</v>
       </c>
       <c r="BR211" t="inlineStr">
         <is>
@@ -54622,13 +54504,13 @@
         </is>
       </c>
       <c r="BO240" t="n">
-        <v>8133200</v>
+        <v>8183600</v>
       </c>
       <c r="BP240" t="n">
         <v>8183200</v>
       </c>
       <c r="BQ240" t="n">
-        <v>8133200</v>
+        <v>8183600</v>
       </c>
       <c r="BR240" t="inlineStr">
         <is>
@@ -58840,13 +58722,13 @@
         </is>
       </c>
       <c r="BO258" t="n">
-        <v>5528937</v>
+        <v>5571204</v>
       </c>
       <c r="BP258" t="n">
         <v>5627200</v>
       </c>
       <c r="BQ258" t="n">
-        <v>5528937</v>
+        <v>5571204</v>
       </c>
       <c r="BR258" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -1958,18 +1958,20 @@
         <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>2082000000</v>
+        <v>2082994000</v>
       </c>
       <c r="H7" t="n">
         <v>2082000000</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>2400260000</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2000,12 +2002,14 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>272000000</v>
+        <v>272411000</v>
       </c>
       <c r="T7" t="n">
         <v>272000000</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>62546000</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2036,12 +2040,14 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>141000000</v>
+        <v>141803000</v>
       </c>
       <c r="AF7" t="n">
         <v>141000000</v>
       </c>
-      <c r="AG7" t="inlineStr"/>
+      <c r="AG7" t="n">
+        <v>-184425000</v>
+      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2071,28 +2077,40 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>1517574000</v>
+      </c>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>1517574000</v>
+      </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr"/>
+          <t>YF</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>73773000</v>
+      </c>
       <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>73773000</v>
+      </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>YF</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>41495000</v>
+      </c>
       <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>41495000</v>
+      </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BC7" t="n">
@@ -2101,7 +2119,9 @@
       <c r="BD7" t="n">
         <v>1593000000</v>
       </c>
-      <c r="BE7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>1593893000</v>
+      </c>
       <c r="BF7" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2113,22 +2133,26 @@
       <c r="BH7" t="n">
         <v>389000000</v>
       </c>
-      <c r="BI7" t="inlineStr"/>
+      <c r="BI7" t="n">
+        <v>389870000</v>
+      </c>
       <c r="BJ7" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>0.186</v>
+        <v>0.1864782130386952</v>
       </c>
       <c r="BL7" t="n">
         <v>0.186</v>
       </c>
-      <c r="BM7" t="inlineStr"/>
+      <c r="BM7" t="n">
+        <v>0.1864782130386952</v>
+      </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO7" t="n">
@@ -2137,10 +2161,12 @@
       <c r="BP7" t="n">
         <v>2905200</v>
       </c>
-      <c r="BQ7" t="inlineStr"/>
+      <c r="BQ7" t="n">
+        <v>2905200</v>
+      </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2809,9 @@
       <c r="BD10" t="n">
         <v>7855000000</v>
       </c>
-      <c r="BE10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>7892000000</v>
+      </c>
       <c r="BF10" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2795,22 +2823,26 @@
       <c r="BH10" t="n">
         <v>17439000000</v>
       </c>
-      <c r="BI10" t="inlineStr"/>
+      <c r="BI10" t="n">
+        <v>17422000000</v>
+      </c>
       <c r="BJ10" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>0.261</v>
+        <v>0.2605080969541098</v>
       </c>
       <c r="BL10" t="n">
         <v>0.261</v>
       </c>
-      <c r="BM10" t="inlineStr"/>
+      <c r="BM10" t="n">
+        <v>0.2605080969541098</v>
+      </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO10" t="n">
@@ -2819,10 +2851,12 @@
       <c r="BP10" t="n">
         <v>7716600</v>
       </c>
-      <c r="BQ10" t="inlineStr"/>
+      <c r="BQ10" t="n">
+        <v>7716600</v>
+      </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>
@@ -2844,18 +2878,20 @@
         <v>1</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>7928000000</v>
+        <v>7928778000</v>
       </c>
       <c r="H11" t="n">
         <v>7928000000</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>8993031000</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2886,12 +2922,14 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>727000000</v>
+        <v>727337000</v>
       </c>
       <c r="T11" t="n">
         <v>727000000</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>656540000</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2922,12 +2960,14 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>485000000</v>
+        <v>485565000</v>
       </c>
       <c r="AF11" t="n">
         <v>485000000</v>
       </c>
-      <c r="AG11" t="inlineStr"/>
+      <c r="AG11" t="n">
+        <v>352716000</v>
+      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2963,7 +3003,9 @@
       <c r="AR11" t="n">
         <v>7928000000</v>
       </c>
-      <c r="AS11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>6299403000</v>
+      </c>
       <c r="AT11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2975,7 +3017,9 @@
       <c r="AV11" t="n">
         <v>727000000</v>
       </c>
-      <c r="AW11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>101377000</v>
+      </c>
       <c r="AX11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2987,7 +3031,9 @@
       <c r="AZ11" t="n">
         <v>485000000</v>
       </c>
-      <c r="BA11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>70874000</v>
+      </c>
       <c r="BB11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -2999,7 +3045,9 @@
       <c r="BD11" t="n">
         <v>8917000000</v>
       </c>
-      <c r="BE11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>8917773000</v>
+      </c>
       <c r="BF11" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3011,34 +3059,40 @@
       <c r="BH11" t="n">
         <v>10355000000</v>
       </c>
-      <c r="BI11" t="inlineStr"/>
+      <c r="BI11" t="n">
+        <v>10316268000</v>
+      </c>
       <c r="BJ11" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.7696783841113143</v>
       </c>
       <c r="BL11" t="n">
         <v>0.75</v>
       </c>
-      <c r="BM11" t="inlineStr"/>
+      <c r="BM11" t="n">
+        <v>0.7696783841113143</v>
+      </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO11" t="n">
-        <v>45325241</v>
+        <v>45325211</v>
       </c>
       <c r="BP11" t="n">
         <v>45325241</v>
       </c>
-      <c r="BQ11" t="inlineStr"/>
+      <c r="BQ11" t="n">
+        <v>45325211</v>
+      </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>
@@ -3263,10 +3317,12 @@
       <c r="BP12" t="n">
         <v>1918600</v>
       </c>
-      <c r="BQ12" t="inlineStr"/>
+      <c r="BQ12" t="n">
+        <v>1918600</v>
+      </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>
@@ -3727,10 +3783,12 @@
       <c r="BP14" t="n">
         <v>5666100</v>
       </c>
-      <c r="BQ14" t="inlineStr"/>
+      <c r="BQ14" t="n">
+        <v>5666100</v>
+      </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>
@@ -3752,18 +3810,20 @@
         <v>1</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>12363000000</v>
+        <v>12363389000</v>
       </c>
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3794,12 +3854,14 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>542000000</v>
+        <v>542316000</v>
       </c>
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3830,12 +3892,14 @@
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>320000000</v>
+        <v>320998000</v>
       </c>
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3865,28 +3929,40 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>8265919000</v>
+      </c>
       <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>8265919000</v>
+      </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr"/>
+          <t>YF</t>
+        </is>
+      </c>
+      <c r="AU15" t="n">
+        <v>120007000</v>
+      </c>
       <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>120007000</v>
+      </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>YF</t>
+        </is>
+      </c>
+      <c r="AY15" t="n">
+        <v>168348000</v>
+      </c>
       <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
+      <c r="BA15" t="n">
+        <v>168348000</v>
+      </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BC15" t="n">
@@ -3895,7 +3971,9 @@
       <c r="BD15" t="n">
         <v>2065000000</v>
       </c>
-      <c r="BE15" t="inlineStr"/>
+      <c r="BE15" t="n">
+        <v>2065504000</v>
+      </c>
       <c r="BF15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3907,34 +3985,40 @@
       <c r="BH15" t="n">
         <v>2272000000</v>
       </c>
-      <c r="BI15" t="inlineStr"/>
+      <c r="BI15" t="n">
+        <v>2272296000</v>
+      </c>
       <c r="BJ15" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.512</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
-      <c r="BM15" t="inlineStr"/>
+      <c r="BM15" t="n">
+        <v>0.5118512364823101</v>
+      </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO15" t="n">
-        <v>8569275</v>
+        <v>8398975</v>
       </c>
       <c r="BP15" t="n">
         <v>8569275</v>
       </c>
-      <c r="BQ15" t="inlineStr"/>
+      <c r="BQ15" t="n">
+        <v>8398975</v>
+      </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>
@@ -4186,18 +4270,20 @@
         <v>1</v>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>5847000000</v>
+        <v>5847966000</v>
       </c>
       <c r="H17" t="n">
         <v>5847000000</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>8019568000</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4228,12 +4314,14 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>413000000</v>
+        <v>414109000</v>
       </c>
       <c r="T17" t="n">
         <v>413000000</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>554869000</v>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4264,12 +4352,14 @@
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>273000000</v>
+        <v>273173000</v>
       </c>
       <c r="AF17" t="n">
         <v>273000000</v>
       </c>
-      <c r="AG17" t="inlineStr"/>
+      <c r="AG17" t="n">
+        <v>304310000</v>
+      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4299,28 +4389,40 @@
           <t>JQ</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>5298404000</v>
+      </c>
       <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>5298404000</v>
+      </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr"/>
+          <t>YF</t>
+        </is>
+      </c>
+      <c r="AU17" t="n">
+        <v>389740000</v>
+      </c>
       <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
+      <c r="AW17" t="n">
+        <v>389740000</v>
+      </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>YF</t>
+        </is>
+      </c>
+      <c r="AY17" t="n">
+        <v>275454000</v>
+      </c>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
+      <c r="BA17" t="n">
+        <v>275454000</v>
+      </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BC17" t="n">
@@ -4329,7 +4431,9 @@
       <c r="BD17" t="n">
         <v>1667000000</v>
       </c>
-      <c r="BE17" t="inlineStr"/>
+      <c r="BE17" t="n">
+        <v>1987756000</v>
+      </c>
       <c r="BF17" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4341,34 +4445,40 @@
       <c r="BH17" t="n">
         <v>1739000000</v>
       </c>
-      <c r="BI17" t="inlineStr"/>
+      <c r="BI17" t="n">
+        <v>1739547000</v>
+      </c>
       <c r="BJ17" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>0.427</v>
+        <v>0.4271421292686969</v>
       </c>
       <c r="BL17" t="n">
         <v>0.427</v>
       </c>
-      <c r="BM17" t="inlineStr"/>
+      <c r="BM17" t="n">
+        <v>0.4271421292686969</v>
+      </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO17" t="n">
-        <v>10637253</v>
+        <v>10269836</v>
       </c>
       <c r="BP17" t="n">
         <v>10637253</v>
       </c>
-      <c r="BQ17" t="inlineStr"/>
+      <c r="BQ17" t="n">
+        <v>10269836</v>
+      </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5345,9 @@
       <c r="BD21" t="n">
         <v>26201000000</v>
       </c>
-      <c r="BE21" t="inlineStr"/>
+      <c r="BE21" t="n">
+        <v>26203066000</v>
+      </c>
       <c r="BF21" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -5247,34 +5359,40 @@
       <c r="BH21" t="n">
         <v>33005000000</v>
       </c>
-      <c r="BI21" t="inlineStr"/>
+      <c r="BI21" t="n">
+        <v>31925761000</v>
+      </c>
       <c r="BJ21" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>0.383</v>
+        <v>0.3834985579116227</v>
       </c>
       <c r="BL21" t="n">
         <v>0.383</v>
       </c>
-      <c r="BM21" t="inlineStr"/>
+      <c r="BM21" t="n">
+        <v>0.3834985579116227</v>
+      </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO21" t="n">
-        <v>61636723</v>
+        <v>61621872</v>
       </c>
       <c r="BP21" t="n">
         <v>61636723</v>
       </c>
-      <c r="BQ21" t="inlineStr"/>
+      <c r="BQ21" t="n">
+        <v>61621872</v>
+      </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
     </row>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="BO4" t="n">
-        <v>3022440</v>
+        <v>3043840</v>
       </c>
       <c r="BP4" t="n">
         <v>3043840</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3022440</v>
+        <v>3043840</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
@@ -15191,12 +15191,10 @@
       <c r="H65" t="n">
         <v>17159000000</v>
       </c>
-      <c r="I65" t="n">
-        <v>17159077000</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -15229,12 +15227,10 @@
       <c r="T65" t="n">
         <v>1849000000</v>
       </c>
-      <c r="U65" t="n">
-        <v>1849976000</v>
-      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W65" t="n">
@@ -15267,12 +15263,10 @@
       <c r="AF65" t="n">
         <v>1207000000</v>
       </c>
-      <c r="AG65" t="n">
-        <v>1207252000</v>
-      </c>
+      <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI65" t="n">
@@ -15300,11 +15294,11 @@
         </is>
       </c>
       <c r="AQ65" t="n">
-        <v>11841779000</v>
+        <v>15311567000</v>
       </c>
       <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="n">
-        <v>11841779000</v>
+        <v>15311567000</v>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
@@ -15312,11 +15306,11 @@
         </is>
       </c>
       <c r="AU65" t="n">
-        <v>364511000</v>
+        <v>1516404000</v>
       </c>
       <c r="AV65" t="inlineStr"/>
       <c r="AW65" t="n">
-        <v>364511000</v>
+        <v>1516404000</v>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
@@ -15324,11 +15318,11 @@
         </is>
       </c>
       <c r="AY65" t="n">
-        <v>252530000</v>
+        <v>1065693000</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
-        <v>252530000</v>
+        <v>1065693000</v>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
@@ -15814,13 +15808,13 @@
         </is>
       </c>
       <c r="BO67" t="n">
-        <v>28441200</v>
+        <v>28432500</v>
       </c>
       <c r="BP67" t="n">
         <v>28728000</v>
       </c>
       <c r="BQ67" t="n">
-        <v>28441200</v>
+        <v>28432500</v>
       </c>
       <c r="BR67" t="inlineStr">
         <is>
@@ -16274,13 +16268,13 @@
         </is>
       </c>
       <c r="BO69" t="n">
-        <v>3660300</v>
+        <v>3677300</v>
       </c>
       <c r="BP69" t="n">
         <v>3698100</v>
       </c>
       <c r="BQ69" t="n">
-        <v>3660300</v>
+        <v>3677300</v>
       </c>
       <c r="BR69" t="inlineStr">
         <is>
@@ -21545,12 +21539,10 @@
       <c r="H93" t="n">
         <v>2310000000</v>
       </c>
-      <c r="I93" t="n">
-        <v>2310220000</v>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -21583,12 +21575,10 @@
       <c r="T93" t="n">
         <v>215000000</v>
       </c>
-      <c r="U93" t="n">
-        <v>215336000</v>
-      </c>
+      <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="W93" t="n">
@@ -21621,12 +21611,10 @@
       <c r="AF93" t="n">
         <v>131000000</v>
       </c>
-      <c r="AG93" t="n">
-        <v>131697000</v>
-      </c>
+      <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="AI93" t="n">
@@ -21654,11 +21642,11 @@
         </is>
       </c>
       <c r="AQ93" t="n">
-        <v>2146176000</v>
+        <v>1946946000</v>
       </c>
       <c r="AR93" t="inlineStr"/>
       <c r="AS93" t="n">
-        <v>2146176000</v>
+        <v>1946946000</v>
       </c>
       <c r="AT93" t="inlineStr">
         <is>
@@ -21666,11 +21654,11 @@
         </is>
       </c>
       <c r="AU93" t="n">
-        <v>102329000</v>
+        <v>139156000</v>
       </c>
       <c r="AV93" t="inlineStr"/>
       <c r="AW93" t="n">
-        <v>102329000</v>
+        <v>139156000</v>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
@@ -21678,11 +21666,11 @@
         </is>
       </c>
       <c r="AY93" t="n">
-        <v>130053000</v>
+        <v>99086000</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
-        <v>130053000</v>
+        <v>99086000</v>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
@@ -47428,13 +47416,13 @@
         </is>
       </c>
       <c r="BO209" t="n">
-        <v>14812720</v>
+        <v>14814520</v>
       </c>
       <c r="BP209" t="n">
         <v>14814600</v>
       </c>
       <c r="BQ209" t="n">
-        <v>14812720</v>
+        <v>14814520</v>
       </c>
       <c r="BR209" t="inlineStr">
         <is>
@@ -64948,13 +64936,13 @@
         </is>
       </c>
       <c r="BO285" t="n">
-        <v>19536000</v>
+        <v>19433900</v>
       </c>
       <c r="BP285" t="n">
         <v>20500000</v>
       </c>
       <c r="BQ285" t="n">
-        <v>19536000</v>
+        <v>19433900</v>
       </c>
       <c r="BR285" t="inlineStr">
         <is>
@@ -71054,13 +71042,13 @@
         </is>
       </c>
       <c r="BO311" t="n">
-        <v>14862978</v>
+        <v>14862940</v>
       </c>
       <c r="BP311" t="n">
         <v>15313240</v>
       </c>
       <c r="BQ311" t="n">
-        <v>14862978</v>
+        <v>14862940</v>
       </c>
       <c r="BR311" t="inlineStr">
         <is>
@@ -76632,13 +76620,13 @@
         </is>
       </c>
       <c r="BO335" t="n">
-        <v>14146348</v>
+        <v>14183148</v>
       </c>
       <c r="BP335" t="n">
         <v>14183200</v>
       </c>
       <c r="BQ335" t="n">
-        <v>14146348</v>
+        <v>14183148</v>
       </c>
       <c r="BR335" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3821,9 +3821,7 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="n">
-        <v>13781848000</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3859,9 +3857,7 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="n">
-        <v>755967000</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3897,9 +3893,7 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="n">
-        <v>454620000</v>
-      </c>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3972,7 +3966,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2065504000</v>
+        <v>2038006000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3986,7 +3980,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2272296000</v>
+        <v>1895989000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3994,13 +3988,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4741,9 +4735,7 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="n">
-        <v>2006859000</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4779,9 +4771,7 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="n">
-        <v>123675000</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4817,9 +4807,7 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="n">
-        <v>32652000</v>
-      </c>
+      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4897,9 +4885,7 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="n">
-        <v>1185144000</v>
-      </c>
+      <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4911,26 +4897,22 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="n">
-        <v>1430969000</v>
-      </c>
+      <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785581548809497</v>
+        <v>0.785</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="n">
-        <v>0.785581548809497</v>
-      </c>
+      <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -70613,9 +70595,7 @@
       <c r="H310" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I310" t="n">
-        <v>13007061000</v>
-      </c>
+      <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70651,9 +70631,7 @@
       <c r="T310" t="n">
         <v>147000000</v>
       </c>
-      <c r="U310" t="n">
-        <v>472174000</v>
-      </c>
+      <c r="U310" t="inlineStr"/>
       <c r="V310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70689,9 +70667,7 @@
       <c r="AF310" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG310" t="n">
-        <v>168261000</v>
-      </c>
+      <c r="AG310" t="inlineStr"/>
       <c r="AH310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70769,9 +70745,7 @@
       <c r="BD310" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE310" t="n">
-        <v>754210000</v>
-      </c>
+      <c r="BE310" t="inlineStr"/>
       <c r="BF310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70783,26 +70757,22 @@
       <c r="BH310" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI310" t="n">
-        <v>2187588000</v>
-      </c>
+      <c r="BI310" t="inlineStr"/>
       <c r="BJ310" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK310" t="n">
-        <v>0.3313848937891653</v>
+        <v>0.331</v>
       </c>
       <c r="BL310" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM310" t="n">
-        <v>0.3313848937891653</v>
-      </c>
+      <c r="BM310" t="inlineStr"/>
       <c r="BN310" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO310" t="n">
@@ -73851,9 +73821,7 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="n">
-        <v>3925672000</v>
-      </c>
+      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73889,9 +73857,7 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="n">
-        <v>351613000</v>
-      </c>
+      <c r="U324" t="inlineStr"/>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73927,9 +73893,7 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="n">
-        <v>173070000</v>
-      </c>
+      <c r="AG324" t="inlineStr"/>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74007,9 +73971,7 @@
       <c r="BD324" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE324" t="n">
-        <v>1844498000</v>
-      </c>
+      <c r="BE324" t="inlineStr"/>
       <c r="BF324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74021,26 +73983,22 @@
       <c r="BH324" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI324" t="n">
-        <v>1571322000</v>
-      </c>
+      <c r="BI324" t="inlineStr"/>
       <c r="BJ324" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK324" t="n">
-        <v>0.6076252752798235</v>
+        <v>0.608</v>
       </c>
       <c r="BL324" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM324" t="n">
-        <v>0.6076252752798235</v>
-      </c>
+      <c r="BM324" t="inlineStr"/>
       <c r="BN324" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO324" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>10233000</v>
+        <v>10256000</v>
       </c>
       <c r="BP3" t="n">
         <v>10256000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10233000</v>
+        <v>10256000</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -3821,7 +3821,9 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3857,7 +3859,9 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3893,7 +3897,9 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3966,7 +3972,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2038006000</v>
+        <v>2065504000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3980,7 +3986,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1895989000</v>
+        <v>2272296000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3988,13 +3994,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4735,7 +4741,9 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2006859000</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4771,7 +4779,9 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>123675000</v>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4807,7 +4817,9 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>32652000</v>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4885,7 +4897,9 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>1185144000</v>
+      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4897,22 +4911,26 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>1430969000</v>
+      </c>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785</v>
+        <v>0.785581548809497</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.785581548809497</v>
+      </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -7194,13 +7212,13 @@
         </is>
       </c>
       <c r="BO29" t="n">
-        <v>2268000</v>
+        <v>2286000</v>
       </c>
       <c r="BP29" t="n">
         <v>2286000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>2268000</v>
+        <v>2286000</v>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
@@ -7414,13 +7432,13 @@
         </is>
       </c>
       <c r="BO30" t="n">
-        <v>73595900</v>
+        <v>75216400</v>
       </c>
       <c r="BP30" t="n">
         <v>73730900</v>
       </c>
       <c r="BQ30" t="n">
-        <v>73595900</v>
+        <v>75216400</v>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
@@ -11044,13 +11062,13 @@
         </is>
       </c>
       <c r="BO46" t="n">
-        <v>2331900</v>
+        <v>2338150</v>
       </c>
       <c r="BP46" t="n">
         <v>2331900</v>
       </c>
       <c r="BQ46" t="n">
-        <v>2331900</v>
+        <v>2338150</v>
       </c>
       <c r="BR46" t="inlineStr">
         <is>
@@ -11504,13 +11522,13 @@
         </is>
       </c>
       <c r="BO48" t="n">
-        <v>3354780</v>
+        <v>3355580</v>
       </c>
       <c r="BP48" t="n">
         <v>3378380</v>
       </c>
       <c r="BQ48" t="n">
-        <v>3354780</v>
+        <v>3355580</v>
       </c>
       <c r="BR48" t="inlineStr">
         <is>
@@ -11734,13 +11752,13 @@
         </is>
       </c>
       <c r="BO49" t="n">
-        <v>2517900</v>
+        <v>2524660</v>
       </c>
       <c r="BP49" t="n">
         <v>2521360</v>
       </c>
       <c r="BQ49" t="n">
-        <v>2517900</v>
+        <v>2524660</v>
       </c>
       <c r="BR49" t="inlineStr">
         <is>
@@ -15354,13 +15372,13 @@
         </is>
       </c>
       <c r="BO65" t="n">
-        <v>6958445</v>
+        <v>7148730</v>
       </c>
       <c r="BP65" t="n">
         <v>7148730</v>
       </c>
       <c r="BQ65" t="n">
-        <v>6958445</v>
+        <v>7148730</v>
       </c>
       <c r="BR65" t="inlineStr">
         <is>
@@ -15578,13 +15596,13 @@
         </is>
       </c>
       <c r="BO66" t="n">
-        <v>4991746</v>
+        <v>5058023</v>
       </c>
       <c r="BP66" t="n">
         <v>5098660</v>
       </c>
       <c r="BQ66" t="n">
-        <v>4991746</v>
+        <v>5058023</v>
       </c>
       <c r="BR66" t="inlineStr">
         <is>
@@ -18504,13 +18522,13 @@
         </is>
       </c>
       <c r="BO79" t="n">
-        <v>53394070</v>
+        <v>53394065</v>
       </c>
       <c r="BP79" t="n">
         <v>54752100</v>
       </c>
       <c r="BQ79" t="n">
-        <v>53394070</v>
+        <v>53394065</v>
       </c>
       <c r="BR79" t="inlineStr">
         <is>
@@ -22154,13 +22172,13 @@
         </is>
       </c>
       <c r="BO95" t="n">
-        <v>3417260</v>
+        <v>3419400</v>
       </c>
       <c r="BP95" t="n">
         <v>3419400</v>
       </c>
       <c r="BQ95" t="n">
-        <v>3417260</v>
+        <v>3419400</v>
       </c>
       <c r="BR95" t="inlineStr">
         <is>
@@ -22378,13 +22396,13 @@
         </is>
       </c>
       <c r="BO96" t="n">
-        <v>5914800</v>
+        <v>5414800</v>
       </c>
       <c r="BP96" t="n">
         <v>5914800</v>
       </c>
       <c r="BQ96" t="n">
-        <v>5914800</v>
+        <v>5414800</v>
       </c>
       <c r="BR96" t="inlineStr">
         <is>
@@ -22608,13 +22626,13 @@
         </is>
       </c>
       <c r="BO97" t="n">
-        <v>7500441</v>
+        <v>7506441</v>
       </c>
       <c r="BP97" t="n">
         <v>7656441</v>
       </c>
       <c r="BQ97" t="n">
-        <v>7500441</v>
+        <v>7506441</v>
       </c>
       <c r="BR97" t="inlineStr">
         <is>
@@ -24622,13 +24640,13 @@
         </is>
       </c>
       <c r="BO106" t="n">
-        <v>7732980</v>
+        <v>7753815</v>
       </c>
       <c r="BP106" t="n">
         <v>7753815</v>
       </c>
       <c r="BQ106" t="n">
-        <v>7732980</v>
+        <v>7753815</v>
       </c>
       <c r="BR106" t="inlineStr">
         <is>
@@ -25730,13 +25748,13 @@
         </is>
       </c>
       <c r="BO111" t="n">
-        <v>9885600</v>
+        <v>9700000</v>
       </c>
       <c r="BP111" t="n">
         <v>10000000</v>
       </c>
       <c r="BQ111" t="n">
-        <v>9885600</v>
+        <v>9700000</v>
       </c>
       <c r="BR111" t="inlineStr">
         <is>
@@ -26582,13 +26600,13 @@
         </is>
       </c>
       <c r="BO115" t="n">
-        <v>4232100</v>
+        <v>4242900</v>
       </c>
       <c r="BP115" t="n">
         <v>4241300</v>
       </c>
       <c r="BQ115" t="n">
-        <v>4232100</v>
+        <v>4242900</v>
       </c>
       <c r="BR115" t="inlineStr">
         <is>
@@ -26806,13 +26824,13 @@
         </is>
       </c>
       <c r="BO116" t="n">
-        <v>3856471</v>
+        <v>3857137</v>
       </c>
       <c r="BP116" t="n">
         <v>3886000</v>
       </c>
       <c r="BQ116" t="n">
-        <v>3856471</v>
+        <v>3857137</v>
       </c>
       <c r="BR116" t="inlineStr">
         <is>
@@ -27030,13 +27048,13 @@
         </is>
       </c>
       <c r="BO117" t="n">
-        <v>2550000</v>
+        <v>2587500</v>
       </c>
       <c r="BP117" t="n">
         <v>2587500</v>
       </c>
       <c r="BQ117" t="n">
-        <v>2550000</v>
+        <v>2587500</v>
       </c>
       <c r="BR117" t="inlineStr">
         <is>
@@ -30348,13 +30366,13 @@
         </is>
       </c>
       <c r="BO132" t="n">
-        <v>20000000</v>
+        <v>20008000</v>
       </c>
       <c r="BP132" t="n">
         <v>20000000</v>
       </c>
       <c r="BQ132" t="n">
-        <v>20000000</v>
+        <v>20008000</v>
       </c>
       <c r="BR132" t="inlineStr">
         <is>
@@ -31912,13 +31930,13 @@
         </is>
       </c>
       <c r="BO139" t="n">
-        <v>1156937</v>
+        <v>1157537</v>
       </c>
       <c r="BP139" t="n">
         <v>1157600</v>
       </c>
       <c r="BQ139" t="n">
-        <v>1156937</v>
+        <v>1157537</v>
       </c>
       <c r="BR139" t="inlineStr">
         <is>
@@ -33990,13 +34008,13 @@
         </is>
       </c>
       <c r="BO148" t="n">
-        <v>2232700</v>
+        <v>2248300</v>
       </c>
       <c r="BP148" t="n">
         <v>2251300</v>
       </c>
       <c r="BQ148" t="n">
-        <v>2232700</v>
+        <v>2248300</v>
       </c>
       <c r="BR148" t="inlineStr">
         <is>
@@ -43464,13 +43482,13 @@
         </is>
       </c>
       <c r="BO192" t="n">
-        <v>2588099</v>
+        <v>2669399</v>
       </c>
       <c r="BP192" t="n">
         <v>2744000</v>
       </c>
       <c r="BQ192" t="n">
-        <v>2588099</v>
+        <v>2669399</v>
       </c>
       <c r="BR192" t="inlineStr">
         <is>
@@ -46460,13 +46478,13 @@
         </is>
       </c>
       <c r="BO205" t="n">
-        <v>3387572</v>
+        <v>3388018</v>
       </c>
       <c r="BP205" t="n">
         <v>3491900</v>
       </c>
       <c r="BQ205" t="n">
-        <v>3387572</v>
+        <v>3388018</v>
       </c>
       <c r="BR205" t="inlineStr">
         <is>
@@ -53660,13 +53678,13 @@
         </is>
       </c>
       <c r="BO236" t="n">
-        <v>12454353</v>
+        <v>12455253</v>
       </c>
       <c r="BP236" t="n">
         <v>12455253</v>
       </c>
       <c r="BQ236" t="n">
-        <v>12454353</v>
+        <v>12455253</v>
       </c>
       <c r="BR236" t="inlineStr">
         <is>
@@ -55530,13 +55548,13 @@
         </is>
       </c>
       <c r="BO244" t="n">
-        <v>9909185</v>
+        <v>9936142</v>
       </c>
       <c r="BP244" t="n">
         <v>9936257</v>
       </c>
       <c r="BQ244" t="n">
-        <v>9909185</v>
+        <v>9936142</v>
       </c>
       <c r="BR244" t="inlineStr">
         <is>
@@ -56232,13 +56250,13 @@
         </is>
       </c>
       <c r="BO247" t="n">
-        <v>9773220</v>
+        <v>9806799</v>
       </c>
       <c r="BP247" t="n">
         <v>10407180</v>
       </c>
       <c r="BQ247" t="n">
-        <v>9773220</v>
+        <v>9806799</v>
       </c>
       <c r="BR247" t="inlineStr">
         <is>
@@ -64464,13 +64482,13 @@
         </is>
       </c>
       <c r="BO283" t="n">
-        <v>5139378</v>
+        <v>5363578</v>
       </c>
       <c r="BP283" t="n">
         <v>4697100</v>
       </c>
       <c r="BQ283" t="n">
-        <v>5139378</v>
+        <v>5363578</v>
       </c>
       <c r="BR283" t="inlineStr">
         <is>
@@ -65154,13 +65172,13 @@
         </is>
       </c>
       <c r="BO286" t="n">
-        <v>12875797</v>
+        <v>12919737</v>
       </c>
       <c r="BP286" t="n">
         <v>13117620</v>
       </c>
       <c r="BQ286" t="n">
-        <v>12875797</v>
+        <v>12919737</v>
       </c>
       <c r="BR286" t="inlineStr">
         <is>
@@ -70595,7 +70613,9 @@
       <c r="H310" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I310" t="inlineStr"/>
+      <c r="I310" t="n">
+        <v>13007061000</v>
+      </c>
       <c r="J310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70631,7 +70651,9 @@
       <c r="T310" t="n">
         <v>147000000</v>
       </c>
-      <c r="U310" t="inlineStr"/>
+      <c r="U310" t="n">
+        <v>472174000</v>
+      </c>
       <c r="V310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70667,7 +70689,9 @@
       <c r="AF310" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG310" t="inlineStr"/>
+      <c r="AG310" t="n">
+        <v>168261000</v>
+      </c>
       <c r="AH310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70745,7 +70769,9 @@
       <c r="BD310" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE310" t="inlineStr"/>
+      <c r="BE310" t="n">
+        <v>754210000</v>
+      </c>
       <c r="BF310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70757,22 +70783,26 @@
       <c r="BH310" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI310" t="inlineStr"/>
+      <c r="BI310" t="n">
+        <v>2187588000</v>
+      </c>
       <c r="BJ310" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK310" t="n">
-        <v>0.331</v>
+        <v>0.3313848937891653</v>
       </c>
       <c r="BL310" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM310" t="inlineStr"/>
+      <c r="BM310" t="n">
+        <v>0.3313848937891653</v>
+      </c>
       <c r="BN310" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO310" t="n">
@@ -71928,13 +71958,13 @@
         </is>
       </c>
       <c r="BO315" t="n">
-        <v>22935495</v>
+        <v>22933853</v>
       </c>
       <c r="BP315" t="n">
         <v>23270000</v>
       </c>
       <c r="BQ315" t="n">
-        <v>22935495</v>
+        <v>22933853</v>
       </c>
       <c r="BR315" t="inlineStr">
         <is>
@@ -73821,7 +73851,9 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="n">
+        <v>3925672000</v>
+      </c>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73857,7 +73889,9 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="inlineStr"/>
+      <c r="U324" t="n">
+        <v>351613000</v>
+      </c>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73893,7 +73927,9 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="inlineStr"/>
+      <c r="AG324" t="n">
+        <v>173070000</v>
+      </c>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73971,7 +74007,9 @@
       <c r="BD324" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE324" t="inlineStr"/>
+      <c r="BE324" t="n">
+        <v>1844498000</v>
+      </c>
       <c r="BF324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73983,22 +74021,26 @@
       <c r="BH324" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI324" t="inlineStr"/>
+      <c r="BI324" t="n">
+        <v>1571322000</v>
+      </c>
       <c r="BJ324" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK324" t="n">
-        <v>0.608</v>
+        <v>0.6076252752798235</v>
       </c>
       <c r="BL324" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM324" t="inlineStr"/>
+      <c r="BM324" t="n">
+        <v>0.6076252752798235</v>
+      </c>
       <c r="BN324" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO324" t="n">
@@ -78670,13 +78712,13 @@
         </is>
       </c>
       <c r="BO344" t="n">
-        <v>4064510</v>
+        <v>4045510</v>
       </c>
       <c r="BP344" t="n">
         <v>4064780</v>
       </c>
       <c r="BQ344" t="n">
-        <v>4064510</v>
+        <v>4045510</v>
       </c>
       <c r="BR344" t="inlineStr">
         <is>
@@ -80535,26 +80577,22 @@
       <c r="BH352" t="n">
         <v>3241000000</v>
       </c>
-      <c r="BI352" t="n">
-        <v>3236552000</v>
-      </c>
+      <c r="BI352" t="inlineStr"/>
       <c r="BJ352" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK352" t="n">
-        <v>0.5339396374976821</v>
+        <v>0.536</v>
       </c>
       <c r="BL352" t="n">
         <v>0.536</v>
       </c>
-      <c r="BM352" t="n">
-        <v>0.5339396374976821</v>
-      </c>
+      <c r="BM352" t="inlineStr"/>
       <c r="BN352" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO352" t="n">
@@ -85962,13 +86000,13 @@
         </is>
       </c>
       <c r="BO375" t="n">
-        <v>12497321</v>
+        <v>12503621</v>
       </c>
       <c r="BP375" t="n">
         <v>12739837</v>
       </c>
       <c r="BQ375" t="n">
-        <v>12497321</v>
+        <v>12503621</v>
       </c>
       <c r="BR375" t="inlineStr">
         <is>

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3821,9 +3821,7 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="n">
-        <v>13781848000</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3859,9 +3857,7 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="n">
-        <v>755967000</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3897,9 +3893,7 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="n">
-        <v>454620000</v>
-      </c>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3972,7 +3966,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2065504000</v>
+        <v>2038006000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3986,7 +3980,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2272296000</v>
+        <v>1895989000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3994,13 +3988,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5118512364823101</v>
+        <v>0.43940040037581</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4741,9 +4735,7 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="n">
-        <v>2006859000</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4779,9 +4771,7 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="n">
-        <v>123675000</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4817,9 +4807,7 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="n">
-        <v>32652000</v>
-      </c>
+      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4897,9 +4885,7 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="n">
-        <v>1185144000</v>
-      </c>
+      <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4911,26 +4897,22 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="n">
-        <v>1430969000</v>
-      </c>
+      <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785581548809497</v>
+        <v>0.785</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="n">
-        <v>0.785581548809497</v>
-      </c>
+      <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -70613,9 +70595,7 @@
       <c r="H310" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I310" t="n">
-        <v>13007061000</v>
-      </c>
+      <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70651,9 +70631,7 @@
       <c r="T310" t="n">
         <v>147000000</v>
       </c>
-      <c r="U310" t="n">
-        <v>472174000</v>
-      </c>
+      <c r="U310" t="inlineStr"/>
       <c r="V310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70689,9 +70667,7 @@
       <c r="AF310" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG310" t="n">
-        <v>168261000</v>
-      </c>
+      <c r="AG310" t="inlineStr"/>
       <c r="AH310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70769,9 +70745,7 @@
       <c r="BD310" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE310" t="n">
-        <v>754210000</v>
-      </c>
+      <c r="BE310" t="inlineStr"/>
       <c r="BF310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70783,26 +70757,22 @@
       <c r="BH310" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI310" t="n">
-        <v>2187588000</v>
-      </c>
+      <c r="BI310" t="inlineStr"/>
       <c r="BJ310" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK310" t="n">
-        <v>0.3313848937891653</v>
+        <v>0.331</v>
       </c>
       <c r="BL310" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM310" t="n">
-        <v>0.3313848937891653</v>
-      </c>
+      <c r="BM310" t="inlineStr"/>
       <c r="BN310" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO310" t="n">
@@ -73851,9 +73821,7 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="n">
-        <v>3925672000</v>
-      </c>
+      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73889,9 +73857,7 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="n">
-        <v>351613000</v>
-      </c>
+      <c r="U324" t="inlineStr"/>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73927,9 +73893,7 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="n">
-        <v>173070000</v>
-      </c>
+      <c r="AG324" t="inlineStr"/>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74007,9 +73971,7 @@
       <c r="BD324" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE324" t="n">
-        <v>1844498000</v>
-      </c>
+      <c r="BE324" t="inlineStr"/>
       <c r="BF324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -74021,26 +73983,22 @@
       <c r="BH324" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI324" t="n">
-        <v>1571322000</v>
-      </c>
+      <c r="BI324" t="inlineStr"/>
       <c r="BJ324" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK324" t="n">
-        <v>0.6076252752798235</v>
+        <v>0.608</v>
       </c>
       <c r="BL324" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM324" t="n">
-        <v>0.6076252752798235</v>
-      </c>
+      <c r="BM324" t="inlineStr"/>
       <c r="BN324" t="inlineStr">
         <is>
-          <t>YF</t>
+          <t>JQ</t>
         </is>
       </c>
       <c r="BO324" t="n">
@@ -80577,22 +80535,26 @@
       <c r="BH352" t="n">
         <v>3241000000</v>
       </c>
-      <c r="BI352" t="inlineStr"/>
+      <c r="BI352" t="n">
+        <v>3236552000</v>
+      </c>
       <c r="BJ352" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK352" t="n">
-        <v>0.536</v>
+        <v>0.5339396374976821</v>
       </c>
       <c r="BL352" t="n">
         <v>0.536</v>
       </c>
-      <c r="BM352" t="inlineStr"/>
+      <c r="BM352" t="n">
+        <v>0.5339396374976821</v>
+      </c>
       <c r="BN352" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO352" t="n">

--- a/bi/outputs/yfinance_audit.xlsx
+++ b/bi/outputs/yfinance_audit.xlsx
@@ -3821,7 +3821,9 @@
       <c r="H15" t="n">
         <v>12363000000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>13781848000</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3857,7 +3859,9 @@
       <c r="T15" t="n">
         <v>542000000</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>755967000</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3893,7 +3897,9 @@
       <c r="AF15" t="n">
         <v>320000000</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>454620000</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -3966,7 +3972,7 @@
         <v>2065000000</v>
       </c>
       <c r="BE15" t="n">
-        <v>2038006000</v>
+        <v>2065504000</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -3980,7 +3986,7 @@
         <v>2272000000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1895989000</v>
+        <v>2272296000</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -3988,13 +3994,13 @@
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BL15" t="n">
         <v>0.512</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43940040037581</v>
+        <v>0.5118512364823101</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
@@ -4735,7 +4741,9 @@
       <c r="H19" t="n">
         <v>1957000000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>2006859000</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4771,7 +4779,9 @@
       <c r="T19" t="n">
         <v>231000000</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>123675000</v>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4807,7 +4817,9 @@
       <c r="AF19" t="n">
         <v>156000000</v>
       </c>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>32652000</v>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4885,7 +4897,9 @@
       <c r="BD19" t="n">
         <v>1185000000</v>
       </c>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>1185144000</v>
+      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -4897,22 +4911,26 @@
       <c r="BH19" t="n">
         <v>1430000000</v>
       </c>
-      <c r="BI19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>1430969000</v>
+      </c>
       <c r="BJ19" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>0.785</v>
+        <v>0.785581548809497</v>
       </c>
       <c r="BL19" t="n">
         <v>0.785</v>
       </c>
-      <c r="BM19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.785581548809497</v>
+      </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO19" t="n">
@@ -12630,13 +12648,13 @@
         </is>
       </c>
       <c r="BO53" t="n">
-        <v>15205320</v>
+        <v>14304998</v>
       </c>
       <c r="BP53" t="n">
         <v>15205697</v>
       </c>
       <c r="BQ53" t="n">
-        <v>15205320</v>
+        <v>14304998</v>
       </c>
       <c r="BR53" t="inlineStr">
         <is>
@@ -28580,13 +28598,13 @@
         </is>
       </c>
       <c r="BO124" t="n">
-        <v>1840697</v>
+        <v>1841497</v>
       </c>
       <c r="BP124" t="n">
         <v>1889679</v>
       </c>
       <c r="BQ124" t="n">
-        <v>1840697</v>
+        <v>1841497</v>
       </c>
       <c r="BR124" t="inlineStr">
         <is>
@@ -46038,13 +46056,13 @@
         </is>
       </c>
       <c r="BO203" t="n">
-        <v>15215996</v>
+        <v>15116496</v>
       </c>
       <c r="BP203" t="n">
         <v>15251838</v>
       </c>
       <c r="BQ203" t="n">
-        <v>15215996</v>
+        <v>15116496</v>
       </c>
       <c r="BR203" t="inlineStr">
         <is>
@@ -57406,13 +57424,13 @@
         </is>
       </c>
       <c r="BO252" t="n">
-        <v>11196345</v>
+        <v>11064745</v>
       </c>
       <c r="BP252" t="n">
         <v>11216120</v>
       </c>
       <c r="BQ252" t="n">
-        <v>11196345</v>
+        <v>11064745</v>
       </c>
       <c r="BR252" t="inlineStr">
         <is>
@@ -70595,7 +70613,9 @@
       <c r="H310" t="n">
         <v>10348000000</v>
       </c>
-      <c r="I310" t="inlineStr"/>
+      <c r="I310" t="n">
+        <v>13007061000</v>
+      </c>
       <c r="J310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70631,7 +70651,9 @@
       <c r="T310" t="n">
         <v>147000000</v>
       </c>
-      <c r="U310" t="inlineStr"/>
+      <c r="U310" t="n">
+        <v>472174000</v>
+      </c>
       <c r="V310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70667,7 +70689,9 @@
       <c r="AF310" t="n">
         <v>-88000000</v>
       </c>
-      <c r="AG310" t="inlineStr"/>
+      <c r="AG310" t="n">
+        <v>168261000</v>
+      </c>
       <c r="AH310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70745,7 +70769,9 @@
       <c r="BD310" t="n">
         <v>753000000</v>
       </c>
-      <c r="BE310" t="inlineStr"/>
+      <c r="BE310" t="n">
+        <v>754210000</v>
+      </c>
       <c r="BF310" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -70757,22 +70783,26 @@
       <c r="BH310" t="n">
         <v>2188000000</v>
       </c>
-      <c r="BI310" t="inlineStr"/>
+      <c r="BI310" t="n">
+        <v>2187588000</v>
+      </c>
       <c r="BJ310" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK310" t="n">
-        <v>0.331</v>
+        <v>0.3313848937891653</v>
       </c>
       <c r="BL310" t="n">
         <v>0.331</v>
       </c>
-      <c r="BM310" t="inlineStr"/>
+      <c r="BM310" t="n">
+        <v>0.3313848937891653</v>
+      </c>
       <c r="BN310" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO310" t="n">
@@ -73821,7 +73851,9 @@
       <c r="H324" t="n">
         <v>3957000000</v>
       </c>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="n">
+        <v>3925672000</v>
+      </c>
       <c r="J324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73857,7 +73889,9 @@
       <c r="T324" t="n">
         <v>508000000</v>
       </c>
-      <c r="U324" t="inlineStr"/>
+      <c r="U324" t="n">
+        <v>351613000</v>
+      </c>
       <c r="V324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73893,7 +73927,9 @@
       <c r="AF324" t="n">
         <v>327000000</v>
       </c>
-      <c r="AG324" t="inlineStr"/>
+      <c r="AG324" t="n">
+        <v>173070000</v>
+      </c>
       <c r="AH324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73971,7 +74007,9 @@
       <c r="BD324" t="n">
         <v>1844000000</v>
       </c>
-      <c r="BE324" t="inlineStr"/>
+      <c r="BE324" t="n">
+        <v>1844498000</v>
+      </c>
       <c r="BF324" t="inlineStr">
         <is>
           <t>JQ</t>
@@ -73983,22 +74021,26 @@
       <c r="BH324" t="n">
         <v>1571000000</v>
       </c>
-      <c r="BI324" t="inlineStr"/>
+      <c r="BI324" t="n">
+        <v>1571322000</v>
+      </c>
       <c r="BJ324" t="inlineStr">
         <is>
           <t>JQ</t>
         </is>
       </c>
       <c r="BK324" t="n">
-        <v>0.608</v>
+        <v>0.6076252752798235</v>
       </c>
       <c r="BL324" t="n">
         <v>0.608</v>
       </c>
-      <c r="BM324" t="inlineStr"/>
+      <c r="BM324" t="n">
+        <v>0.6076252752798235</v>
+      </c>
       <c r="BN324" t="inlineStr">
         <is>
-          <t>JQ</t>
+          <t>YF</t>
         </is>
       </c>
       <c r="BO324" t="n">
